--- a/plantillas/1_Contabilidad_y_Finanzas/06_Presupuesto_Anual.xlsx
+++ b/plantillas/1_Contabilidad_y_Finanzas/06_Presupuesto_Anual.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,6 +37,11 @@
     <font>
       <i val="1"/>
       <color rgb="00595959"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00A6A6A6"/>
+      <sz val="8"/>
     </font>
     <font>
       <b val="1"/>
@@ -86,13 +91,45 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color rgb="00A6A6A6"/>
+      </left>
+      <top style="dashed">
+        <color rgb="00A6A6A6"/>
+      </top>
+    </border>
+    <border>
+      <right style="dashed">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <top style="dashed">
+        <color rgb="00A6A6A6"/>
+      </top>
+    </border>
+    <border>
+      <left style="dashed">
+        <color rgb="00A6A6A6"/>
+      </left>
+      <bottom style="dashed">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="dashed">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <bottom style="dashed">
+        <color rgb="00A6A6A6"/>
+      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -112,31 +149,38 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -532,670 +576,694 @@
     <col width="11" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1">
+    <row r="1" ht="38" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>PRESUPUESTO ANUAL: PRESUPUESTADO VS REAL</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>INSERTE SU LOGO
+(clic derecho &gt; Insertar imagen)</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="n"/>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Captura presupuesto y gasto real por mes; la variación se calcula sola</t>
         </is>
       </c>
+      <c r="P2" s="6" t="n"/>
+      <c r="Q2" s="7" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Empresa / Área</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="9" t="n"/>
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Año</t>
         </is>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="9" t="n">
         <v>2026</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>Ene</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>Feb</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>Abr</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr">
         <is>
           <t>Ago</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J7" s="10" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="K7" s="10" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="L7" s="10" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="M7" s="10" t="inlineStr">
         <is>
           <t>Dic</t>
         </is>
       </c>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>Presup. anual</t>
         </is>
       </c>
-      <c r="O7" s="5" t="inlineStr">
+      <c r="O7" s="10" t="inlineStr">
         <is>
           <t>Real anual</t>
         </is>
       </c>
-      <c r="P7" s="5" t="inlineStr">
+      <c r="P7" s="10" t="inlineStr">
         <is>
           <t>Variación</t>
         </is>
       </c>
-      <c r="Q7" s="5" t="inlineStr">
+      <c r="Q7" s="10" t="inlineStr">
         <is>
           <t>% ejec.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Ventas - Presup.</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="7" t="n"/>
-      <c r="I8" s="7" t="n"/>
-      <c r="J8" s="7" t="n"/>
-      <c r="K8" s="7" t="n"/>
-      <c r="L8" s="7" t="n"/>
-      <c r="M8" s="7" t="n"/>
-      <c r="N8" s="8">
+      <c r="B8" s="12" t="n"/>
+      <c r="C8" s="12" t="n"/>
+      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="12" t="n"/>
+      <c r="F8" s="12" t="n"/>
+      <c r="G8" s="12" t="n"/>
+      <c r="H8" s="12" t="n"/>
+      <c r="I8" s="12" t="n"/>
+      <c r="J8" s="12" t="n"/>
+      <c r="K8" s="12" t="n"/>
+      <c r="L8" s="12" t="n"/>
+      <c r="M8" s="12" t="n"/>
+      <c r="N8" s="13">
         <f>SUM(B8:M8)</f>
         <v/>
       </c>
-      <c r="O8" s="8">
+      <c r="O8" s="13">
         <f>SUM(B9:M9)</f>
         <v/>
       </c>
-      <c r="P8" s="8">
+      <c r="P8" s="13">
         <f>O8-N8</f>
         <v/>
       </c>
-      <c r="Q8" s="9">
+      <c r="Q8" s="14">
         <f>IF(N8=0,"",O8/N8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Ventas - Real</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="7" t="n"/>
-      <c r="I9" s="7" t="n"/>
-      <c r="J9" s="7" t="n"/>
-      <c r="K9" s="7" t="n"/>
-      <c r="L9" s="7" t="n"/>
-      <c r="M9" s="7" t="n"/>
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="12" t="n"/>
+      <c r="H9" s="12" t="n"/>
+      <c r="I9" s="12" t="n"/>
+      <c r="J9" s="12" t="n"/>
+      <c r="K9" s="12" t="n"/>
+      <c r="L9" s="12" t="n"/>
+      <c r="M9" s="12" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Costo de ventas - Presup.</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="n"/>
-      <c r="I10" s="7" t="n"/>
-      <c r="J10" s="7" t="n"/>
-      <c r="K10" s="7" t="n"/>
-      <c r="L10" s="7" t="n"/>
-      <c r="M10" s="7" t="n"/>
-      <c r="N10" s="8">
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="12" t="n"/>
+      <c r="D10" s="12" t="n"/>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="12" t="n"/>
+      <c r="G10" s="12" t="n"/>
+      <c r="H10" s="12" t="n"/>
+      <c r="I10" s="12" t="n"/>
+      <c r="J10" s="12" t="n"/>
+      <c r="K10" s="12" t="n"/>
+      <c r="L10" s="12" t="n"/>
+      <c r="M10" s="12" t="n"/>
+      <c r="N10" s="13">
         <f>SUM(B10:M10)</f>
         <v/>
       </c>
-      <c r="O10" s="8">
+      <c r="O10" s="13">
         <f>SUM(B11:M11)</f>
         <v/>
       </c>
-      <c r="P10" s="8">
+      <c r="P10" s="13">
         <f>O10-N10</f>
         <v/>
       </c>
-      <c r="Q10" s="9">
+      <c r="Q10" s="14">
         <f>IF(N10=0,"",O10/N10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Costo de ventas - Real</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
-      <c r="I11" s="7" t="n"/>
-      <c r="J11" s="7" t="n"/>
-      <c r="K11" s="7" t="n"/>
-      <c r="L11" s="7" t="n"/>
-      <c r="M11" s="7" t="n"/>
+      <c r="B11" s="12" t="n"/>
+      <c r="C11" s="12" t="n"/>
+      <c r="D11" s="12" t="n"/>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="12" t="n"/>
+      <c r="G11" s="12" t="n"/>
+      <c r="H11" s="12" t="n"/>
+      <c r="I11" s="12" t="n"/>
+      <c r="J11" s="12" t="n"/>
+      <c r="K11" s="12" t="n"/>
+      <c r="L11" s="12" t="n"/>
+      <c r="M11" s="12" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Sueldos y salarios - Presup.</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="7" t="n"/>
-      <c r="I12" s="7" t="n"/>
-      <c r="J12" s="7" t="n"/>
-      <c r="K12" s="7" t="n"/>
-      <c r="L12" s="7" t="n"/>
-      <c r="M12" s="7" t="n"/>
-      <c r="N12" s="8">
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="12" t="n"/>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="12" t="n"/>
+      <c r="G12" s="12" t="n"/>
+      <c r="H12" s="12" t="n"/>
+      <c r="I12" s="12" t="n"/>
+      <c r="J12" s="12" t="n"/>
+      <c r="K12" s="12" t="n"/>
+      <c r="L12" s="12" t="n"/>
+      <c r="M12" s="12" t="n"/>
+      <c r="N12" s="13">
         <f>SUM(B12:M12)</f>
         <v/>
       </c>
-      <c r="O12" s="8">
+      <c r="O12" s="13">
         <f>SUM(B13:M13)</f>
         <v/>
       </c>
-      <c r="P12" s="8">
+      <c r="P12" s="13">
         <f>O12-N12</f>
         <v/>
       </c>
-      <c r="Q12" s="9">
+      <c r="Q12" s="14">
         <f>IF(N12=0,"",O12/N12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Sueldos y salarios - Real</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
-      <c r="I13" s="7" t="n"/>
-      <c r="J13" s="7" t="n"/>
-      <c r="K13" s="7" t="n"/>
-      <c r="L13" s="7" t="n"/>
-      <c r="M13" s="7" t="n"/>
+      <c r="B13" s="12" t="n"/>
+      <c r="C13" s="12" t="n"/>
+      <c r="D13" s="12" t="n"/>
+      <c r="E13" s="12" t="n"/>
+      <c r="F13" s="12" t="n"/>
+      <c r="G13" s="12" t="n"/>
+      <c r="H13" s="12" t="n"/>
+      <c r="I13" s="12" t="n"/>
+      <c r="J13" s="12" t="n"/>
+      <c r="K13" s="12" t="n"/>
+      <c r="L13" s="12" t="n"/>
+      <c r="M13" s="12" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>Renta - Presup.</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n"/>
-      <c r="I14" s="7" t="n"/>
-      <c r="J14" s="7" t="n"/>
-      <c r="K14" s="7" t="n"/>
-      <c r="L14" s="7" t="n"/>
-      <c r="M14" s="7" t="n"/>
-      <c r="N14" s="8">
+      <c r="B14" s="12" t="n"/>
+      <c r="C14" s="12" t="n"/>
+      <c r="D14" s="12" t="n"/>
+      <c r="E14" s="12" t="n"/>
+      <c r="F14" s="12" t="n"/>
+      <c r="G14" s="12" t="n"/>
+      <c r="H14" s="12" t="n"/>
+      <c r="I14" s="12" t="n"/>
+      <c r="J14" s="12" t="n"/>
+      <c r="K14" s="12" t="n"/>
+      <c r="L14" s="12" t="n"/>
+      <c r="M14" s="12" t="n"/>
+      <c r="N14" s="13">
         <f>SUM(B14:M14)</f>
         <v/>
       </c>
-      <c r="O14" s="8">
+      <c r="O14" s="13">
         <f>SUM(B15:M15)</f>
         <v/>
       </c>
-      <c r="P14" s="8">
+      <c r="P14" s="13">
         <f>O14-N14</f>
         <v/>
       </c>
-      <c r="Q14" s="9">
+      <c r="Q14" s="14">
         <f>IF(N14=0,"",O14/N14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Renta - Real</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="n"/>
-      <c r="I15" s="7" t="n"/>
-      <c r="J15" s="7" t="n"/>
-      <c r="K15" s="7" t="n"/>
-      <c r="L15" s="7" t="n"/>
-      <c r="M15" s="7" t="n"/>
+      <c r="B15" s="12" t="n"/>
+      <c r="C15" s="12" t="n"/>
+      <c r="D15" s="12" t="n"/>
+      <c r="E15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
+      <c r="G15" s="12" t="n"/>
+      <c r="H15" s="12" t="n"/>
+      <c r="I15" s="12" t="n"/>
+      <c r="J15" s="12" t="n"/>
+      <c r="K15" s="12" t="n"/>
+      <c r="L15" s="12" t="n"/>
+      <c r="M15" s="12" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>Servicios - Presup.</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="n"/>
-      <c r="I16" s="7" t="n"/>
-      <c r="J16" s="7" t="n"/>
-      <c r="K16" s="7" t="n"/>
-      <c r="L16" s="7" t="n"/>
-      <c r="M16" s="7" t="n"/>
-      <c r="N16" s="8">
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="12" t="n"/>
+      <c r="G16" s="12" t="n"/>
+      <c r="H16" s="12" t="n"/>
+      <c r="I16" s="12" t="n"/>
+      <c r="J16" s="12" t="n"/>
+      <c r="K16" s="12" t="n"/>
+      <c r="L16" s="12" t="n"/>
+      <c r="M16" s="12" t="n"/>
+      <c r="N16" s="13">
         <f>SUM(B16:M16)</f>
         <v/>
       </c>
-      <c r="O16" s="8">
+      <c r="O16" s="13">
         <f>SUM(B17:M17)</f>
         <v/>
       </c>
-      <c r="P16" s="8">
+      <c r="P16" s="13">
         <f>O16-N16</f>
         <v/>
       </c>
-      <c r="Q16" s="9">
+      <c r="Q16" s="14">
         <f>IF(N16=0,"",O16/N16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Servicios - Real</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="7" t="n"/>
-      <c r="I17" s="7" t="n"/>
-      <c r="J17" s="7" t="n"/>
-      <c r="K17" s="7" t="n"/>
-      <c r="L17" s="7" t="n"/>
-      <c r="M17" s="7" t="n"/>
+      <c r="B17" s="12" t="n"/>
+      <c r="C17" s="12" t="n"/>
+      <c r="D17" s="12" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="12" t="n"/>
+      <c r="G17" s="12" t="n"/>
+      <c r="H17" s="12" t="n"/>
+      <c r="I17" s="12" t="n"/>
+      <c r="J17" s="12" t="n"/>
+      <c r="K17" s="12" t="n"/>
+      <c r="L17" s="12" t="n"/>
+      <c r="M17" s="12" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>Publicidad y mercadotecnia - Presup.</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="7" t="n"/>
-      <c r="F18" s="7" t="n"/>
-      <c r="G18" s="7" t="n"/>
-      <c r="H18" s="7" t="n"/>
-      <c r="I18" s="7" t="n"/>
-      <c r="J18" s="7" t="n"/>
-      <c r="K18" s="7" t="n"/>
-      <c r="L18" s="7" t="n"/>
-      <c r="M18" s="7" t="n"/>
-      <c r="N18" s="8">
+      <c r="B18" s="12" t="n"/>
+      <c r="C18" s="12" t="n"/>
+      <c r="D18" s="12" t="n"/>
+      <c r="E18" s="12" t="n"/>
+      <c r="F18" s="12" t="n"/>
+      <c r="G18" s="12" t="n"/>
+      <c r="H18" s="12" t="n"/>
+      <c r="I18" s="12" t="n"/>
+      <c r="J18" s="12" t="n"/>
+      <c r="K18" s="12" t="n"/>
+      <c r="L18" s="12" t="n"/>
+      <c r="M18" s="12" t="n"/>
+      <c r="N18" s="13">
         <f>SUM(B18:M18)</f>
         <v/>
       </c>
-      <c r="O18" s="8">
+      <c r="O18" s="13">
         <f>SUM(B19:M19)</f>
         <v/>
       </c>
-      <c r="P18" s="8">
+      <c r="P18" s="13">
         <f>O18-N18</f>
         <v/>
       </c>
-      <c r="Q18" s="9">
+      <c r="Q18" s="14">
         <f>IF(N18=0,"",O18/N18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Publicidad y mercadotecnia - Real</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="7" t="n"/>
-      <c r="I19" s="7" t="n"/>
-      <c r="J19" s="7" t="n"/>
-      <c r="K19" s="7" t="n"/>
-      <c r="L19" s="7" t="n"/>
-      <c r="M19" s="7" t="n"/>
+      <c r="B19" s="12" t="n"/>
+      <c r="C19" s="12" t="n"/>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" s="12" t="n"/>
+      <c r="F19" s="12" t="n"/>
+      <c r="G19" s="12" t="n"/>
+      <c r="H19" s="12" t="n"/>
+      <c r="I19" s="12" t="n"/>
+      <c r="J19" s="12" t="n"/>
+      <c r="K19" s="12" t="n"/>
+      <c r="L19" s="12" t="n"/>
+      <c r="M19" s="12" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Mantenimiento - Presup.</t>
         </is>
       </c>
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="7" t="n"/>
-      <c r="I20" s="7" t="n"/>
-      <c r="J20" s="7" t="n"/>
-      <c r="K20" s="7" t="n"/>
-      <c r="L20" s="7" t="n"/>
-      <c r="M20" s="7" t="n"/>
-      <c r="N20" s="8">
+      <c r="B20" s="12" t="n"/>
+      <c r="C20" s="12" t="n"/>
+      <c r="D20" s="12" t="n"/>
+      <c r="E20" s="12" t="n"/>
+      <c r="F20" s="12" t="n"/>
+      <c r="G20" s="12" t="n"/>
+      <c r="H20" s="12" t="n"/>
+      <c r="I20" s="12" t="n"/>
+      <c r="J20" s="12" t="n"/>
+      <c r="K20" s="12" t="n"/>
+      <c r="L20" s="12" t="n"/>
+      <c r="M20" s="12" t="n"/>
+      <c r="N20" s="13">
         <f>SUM(B20:M20)</f>
         <v/>
       </c>
-      <c r="O20" s="8">
+      <c r="O20" s="13">
         <f>SUM(B21:M21)</f>
         <v/>
       </c>
-      <c r="P20" s="8">
+      <c r="P20" s="13">
         <f>O20-N20</f>
         <v/>
       </c>
-      <c r="Q20" s="9">
+      <c r="Q20" s="14">
         <f>IF(N20=0,"",O20/N20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>Mantenimiento - Real</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n"/>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7" t="n"/>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="n"/>
-      <c r="I21" s="7" t="n"/>
-      <c r="J21" s="7" t="n"/>
-      <c r="K21" s="7" t="n"/>
-      <c r="L21" s="7" t="n"/>
-      <c r="M21" s="7" t="n"/>
+      <c r="B21" s="12" t="n"/>
+      <c r="C21" s="12" t="n"/>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="12" t="n"/>
+      <c r="F21" s="12" t="n"/>
+      <c r="G21" s="12" t="n"/>
+      <c r="H21" s="12" t="n"/>
+      <c r="I21" s="12" t="n"/>
+      <c r="J21" s="12" t="n"/>
+      <c r="K21" s="12" t="n"/>
+      <c r="L21" s="12" t="n"/>
+      <c r="M21" s="12" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>Papelería y oficina - Presup.</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="7" t="n"/>
-      <c r="I22" s="7" t="n"/>
-      <c r="J22" s="7" t="n"/>
-      <c r="K22" s="7" t="n"/>
-      <c r="L22" s="7" t="n"/>
-      <c r="M22" s="7" t="n"/>
-      <c r="N22" s="8">
+      <c r="B22" s="12" t="n"/>
+      <c r="C22" s="12" t="n"/>
+      <c r="D22" s="12" t="n"/>
+      <c r="E22" s="12" t="n"/>
+      <c r="F22" s="12" t="n"/>
+      <c r="G22" s="12" t="n"/>
+      <c r="H22" s="12" t="n"/>
+      <c r="I22" s="12" t="n"/>
+      <c r="J22" s="12" t="n"/>
+      <c r="K22" s="12" t="n"/>
+      <c r="L22" s="12" t="n"/>
+      <c r="M22" s="12" t="n"/>
+      <c r="N22" s="13">
         <f>SUM(B22:M22)</f>
         <v/>
       </c>
-      <c r="O22" s="8">
+      <c r="O22" s="13">
         <f>SUM(B23:M23)</f>
         <v/>
       </c>
-      <c r="P22" s="8">
+      <c r="P22" s="13">
         <f>O22-N22</f>
         <v/>
       </c>
-      <c r="Q22" s="9">
+      <c r="Q22" s="14">
         <f>IF(N22=0,"",O22/N22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>Papelería y oficina - Real</t>
         </is>
       </c>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="n"/>
-      <c r="I23" s="7" t="n"/>
-      <c r="J23" s="7" t="n"/>
-      <c r="K23" s="7" t="n"/>
-      <c r="L23" s="7" t="n"/>
-      <c r="M23" s="7" t="n"/>
+      <c r="B23" s="12" t="n"/>
+      <c r="C23" s="12" t="n"/>
+      <c r="D23" s="12" t="n"/>
+      <c r="E23" s="12" t="n"/>
+      <c r="F23" s="12" t="n"/>
+      <c r="G23" s="12" t="n"/>
+      <c r="H23" s="12" t="n"/>
+      <c r="I23" s="12" t="n"/>
+      <c r="J23" s="12" t="n"/>
+      <c r="K23" s="12" t="n"/>
+      <c r="L23" s="12" t="n"/>
+      <c r="M23" s="12" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>Impuestos y derechos - Presup.</t>
         </is>
       </c>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="n"/>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="7" t="n"/>
-      <c r="I24" s="7" t="n"/>
-      <c r="J24" s="7" t="n"/>
-      <c r="K24" s="7" t="n"/>
-      <c r="L24" s="7" t="n"/>
-      <c r="M24" s="7" t="n"/>
-      <c r="N24" s="8">
+      <c r="B24" s="12" t="n"/>
+      <c r="C24" s="12" t="n"/>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="12" t="n"/>
+      <c r="F24" s="12" t="n"/>
+      <c r="G24" s="12" t="n"/>
+      <c r="H24" s="12" t="n"/>
+      <c r="I24" s="12" t="n"/>
+      <c r="J24" s="12" t="n"/>
+      <c r="K24" s="12" t="n"/>
+      <c r="L24" s="12" t="n"/>
+      <c r="M24" s="12" t="n"/>
+      <c r="N24" s="13">
         <f>SUM(B24:M24)</f>
         <v/>
       </c>
-      <c r="O24" s="8">
+      <c r="O24" s="13">
         <f>SUM(B25:M25)</f>
         <v/>
       </c>
-      <c r="P24" s="8">
+      <c r="P24" s="13">
         <f>O24-N24</f>
         <v/>
       </c>
-      <c r="Q24" s="9">
+      <c r="Q24" s="14">
         <f>IF(N24=0,"",O24/N24)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>Impuestos y derechos - Real</t>
         </is>
       </c>
-      <c r="B25" s="7" t="n"/>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="7" t="n"/>
-      <c r="I25" s="7" t="n"/>
-      <c r="J25" s="7" t="n"/>
-      <c r="K25" s="7" t="n"/>
-      <c r="L25" s="7" t="n"/>
-      <c r="M25" s="7" t="n"/>
+      <c r="B25" s="12" t="n"/>
+      <c r="C25" s="12" t="n"/>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="12" t="n"/>
+      <c r="G25" s="12" t="n"/>
+      <c r="H25" s="12" t="n"/>
+      <c r="I25" s="12" t="n"/>
+      <c r="J25" s="12" t="n"/>
+      <c r="K25" s="12" t="n"/>
+      <c r="L25" s="12" t="n"/>
+      <c r="M25" s="12" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>Otros gastos - Presup.</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="n"/>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="7" t="n"/>
-      <c r="I26" s="7" t="n"/>
-      <c r="J26" s="7" t="n"/>
-      <c r="K26" s="7" t="n"/>
-      <c r="L26" s="7" t="n"/>
-      <c r="M26" s="7" t="n"/>
-      <c r="N26" s="8">
+      <c r="B26" s="12" t="n"/>
+      <c r="C26" s="12" t="n"/>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="12" t="n"/>
+      <c r="F26" s="12" t="n"/>
+      <c r="G26" s="12" t="n"/>
+      <c r="H26" s="12" t="n"/>
+      <c r="I26" s="12" t="n"/>
+      <c r="J26" s="12" t="n"/>
+      <c r="K26" s="12" t="n"/>
+      <c r="L26" s="12" t="n"/>
+      <c r="M26" s="12" t="n"/>
+      <c r="N26" s="13">
         <f>SUM(B26:M26)</f>
         <v/>
       </c>
-      <c r="O26" s="8">
+      <c r="O26" s="13">
         <f>SUM(B27:M27)</f>
         <v/>
       </c>
-      <c r="P26" s="8">
+      <c r="P26" s="13">
         <f>O26-N26</f>
         <v/>
       </c>
-      <c r="Q26" s="9">
+      <c r="Q26" s="14">
         <f>IF(N26=0,"",O26/N26)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Otros gastos - Real</t>
         </is>
       </c>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7" t="n"/>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="7" t="n"/>
-      <c r="I27" s="7" t="n"/>
-      <c r="J27" s="7" t="n"/>
-      <c r="K27" s="7" t="n"/>
-      <c r="L27" s="7" t="n"/>
-      <c r="M27" s="7" t="n"/>
+      <c r="B27" s="12" t="n"/>
+      <c r="C27" s="12" t="n"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="12" t="n"/>
+      <c r="F27" s="12" t="n"/>
+      <c r="G27" s="12" t="n"/>
+      <c r="H27" s="12" t="n"/>
+      <c r="I27" s="12" t="n"/>
+      <c r="J27" s="12" t="n"/>
+      <c r="K27" s="12" t="n"/>
+      <c r="L27" s="12" t="n"/>
+      <c r="M27" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="A1:Q1"/>
+  <mergeCells count="4">
+    <mergeCell ref="A1:O1"/>
     <mergeCell ref="B4:D4"/>
+    <mergeCell ref="P1:Q2"/>
+    <mergeCell ref="A2:O2"/>
   </mergeCells>
   <conditionalFormatting sqref="P8:P28">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
@@ -1214,7 +1282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1222,61 +1290,71 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>Presupuesto anual</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>Guía de uso</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="n">
+      <c r="A4" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>Por cada concepto hay dos renglones: Presup. (lo planeado) y Real (lo ejercido).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="n">
+      <c r="A5" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>Captura mes a mes. La columna Variación muestra Real - Presupuesto del primer renglón de cada concepto.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="n">
+      <c r="A6" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>En gastos, una variación positiva (rojo) significa que te pasaste del presupuesto; en ventas, positiva es favorable.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="n">
+      <c r="A7" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>El % de ejecución indica qué parte del presupuesto anual ya se ejerció.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="15" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>Personaliza: en el recuadro punteado de la esquina superior derecha inserta tu logo (Insertar &gt; Imágenes) y captura los datos de tu empresa en las celdas amarillas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>Celdas amarillas = captura · Celdas grises = cálculo automático (no modificar).</t>
         </is>

--- a/plantillas/1_Contabilidad_y_Finanzas/06_Presupuesto_Anual.xlsx
+++ b/plantillas/1_Contabilidad_y_Finanzas/06_Presupuesto_Anual.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formato" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portada" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formato" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,35 +32,77 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="18"/>
+      <sz val="20"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="00595959"/>
+      <color rgb="005B6B78"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <i val="1"/>
       <color rgb="00A6A6A6"/>
       <sz val="8"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="001B6B73"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001F4E78"/>
-      <sz val="16"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001F4E78"/>
+      <color rgb="00C9A227"/>
+      <sz val="10"/>
     </font>
     <font>
-      <i val="1"/>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="26"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00C9D3DB"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001B6B73"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00C9A227"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="002B2B2B"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="005B6B78"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="008A97A3"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="6">
@@ -72,31 +114,45 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="000B2A4A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
+        <fgColor rgb="00E6ECF1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF9E5"/>
+        <fgColor rgb="00FFFCF0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00EEF2F5"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="00C9A227"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="00C9A227"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -133,54 +189,74 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00C9D3DB"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00C9D3DB"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00C9D3DB"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00C9D3DB"/>
       </bottom>
+    </border>
+    <border>
+      <top style="thick">
+        <color rgb="00C9A227"/>
+      </top>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="00C9A227"/>
+      </top>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -188,6 +264,7 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <name val="Calibri"/>
         <b val="1"/>
         <color rgb="00C00000"/>
       </font>
@@ -551,6 +628,190 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C9A227"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="88" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>GRUPO CANVILLE</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="1" t="n"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Presupuesto anual</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="n"/>
+      <c r="D4" s="1" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Formato administrativo editable · México</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="n"/>
+      <c r="D5" s="1" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="1" t="n"/>
+      <c r="C6" s="1" t="n"/>
+      <c r="D6" s="1" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="1" t="n"/>
+      <c r="C7" s="1" t="n"/>
+      <c r="D7" s="1" t="n"/>
+    </row>
+    <row r="8" ht="6" customHeight="1">
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>CÓMO USARLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="21" customHeight="1">
+      <c r="B11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Por cada concepto hay dos renglones: Presup. (lo planeado) y Real (lo ejercido).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="B12" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Captura mes a mes. La columna Variación muestra Real - Presupuesto del primer renglón de cada concepto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="B13" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>En gastos, una variación positiva (rojo) significa que te pasaste del presupuesto; en ventas, positiva es favorable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="21" customHeight="1">
+      <c r="B14" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>El % de ejecución indica qué parte del presupuesto anual ya se ejerció.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="B15" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Personaliza: en el recuadro punteado de la esquina superior derecha inserta tu logo (Insertar &gt; Imágenes) y captura los datos de tu empresa en las celdas de captura.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>LEYENDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="9" t="inlineStr"/>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Celda de captura: escribe aquí.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="11" t="inlineStr"/>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Cálculo automático: no la modifiques.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="12" t="inlineStr"/>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Encabezados y títulos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="n"/>
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="13" t="n"/>
+      <c r="D22" s="13" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>GRUPO CANVILLE · Formatos administrativos · v1.0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="000B2A4A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -576,45 +837,59 @@
     <col width="11" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="44" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>PRESUPUESTO ANUAL: PRESUPUESTADO VS REAL</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="2" t="n"/>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="16" t="inlineStr">
         <is>
           <t>INSERTE SU LOGO
 (clic derecho &gt; Insertar imagen)</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="n"/>
-    </row>
-    <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="Q1" s="17" t="n"/>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>Captura presupuesto y gasto real por mes; la variación se calcula sola</t>
         </is>
       </c>
-      <c r="P2" s="6" t="n"/>
-      <c r="Q2" s="7" t="n"/>
+      <c r="B2" s="19" t="n"/>
+      <c r="C2" s="19" t="n"/>
+      <c r="D2" s="19" t="n"/>
+      <c r="E2" s="19" t="n"/>
+      <c r="F2" s="19" t="n"/>
+      <c r="G2" s="19" t="n"/>
+      <c r="H2" s="19" t="n"/>
+      <c r="I2" s="19" t="n"/>
+      <c r="J2" s="19" t="n"/>
+      <c r="K2" s="19" t="n"/>
+      <c r="L2" s="19" t="n"/>
+      <c r="M2" s="19" t="n"/>
+      <c r="N2" s="19" t="n"/>
+      <c r="O2" s="19" t="n"/>
+      <c r="P2" s="20" t="n"/>
+      <c r="Q2" s="21" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>Empresa / Área</t>
         </is>
@@ -622,7 +897,7 @@
       <c r="B4" s="9" t="n"/>
       <c r="C4" s="9" t="n"/>
       <c r="D4" s="9" t="n"/>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="22" t="inlineStr">
         <is>
           <t>Año</t>
         </is>
@@ -632,631 +907,631 @@
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Ene</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>Feb</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>Abr</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="I7" s="10" t="inlineStr">
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t>Ago</t>
         </is>
       </c>
-      <c r="J7" s="10" t="inlineStr">
+      <c r="J7" s="23" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="K7" s="10" t="inlineStr">
+      <c r="K7" s="23" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="L7" s="10" t="inlineStr">
+      <c r="L7" s="23" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="M7" s="10" t="inlineStr">
+      <c r="M7" s="23" t="inlineStr">
         <is>
           <t>Dic</t>
         </is>
       </c>
-      <c r="N7" s="10" t="inlineStr">
+      <c r="N7" s="23" t="inlineStr">
         <is>
           <t>Presup. anual</t>
         </is>
       </c>
-      <c r="O7" s="10" t="inlineStr">
+      <c r="O7" s="23" t="inlineStr">
         <is>
           <t>Real anual</t>
         </is>
       </c>
-      <c r="P7" s="10" t="inlineStr">
+      <c r="P7" s="23" t="inlineStr">
         <is>
           <t>Variación</t>
         </is>
       </c>
-      <c r="Q7" s="10" t="inlineStr">
+      <c r="Q7" s="23" t="inlineStr">
         <is>
           <t>% ejec.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>Ventas - Presup.</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n"/>
-      <c r="C8" s="12" t="n"/>
-      <c r="D8" s="12" t="n"/>
-      <c r="E8" s="12" t="n"/>
-      <c r="F8" s="12" t="n"/>
-      <c r="G8" s="12" t="n"/>
-      <c r="H8" s="12" t="n"/>
-      <c r="I8" s="12" t="n"/>
-      <c r="J8" s="12" t="n"/>
-      <c r="K8" s="12" t="n"/>
-      <c r="L8" s="12" t="n"/>
-      <c r="M8" s="12" t="n"/>
-      <c r="N8" s="13">
+      <c r="B8" s="25" t="n"/>
+      <c r="C8" s="25" t="n"/>
+      <c r="D8" s="25" t="n"/>
+      <c r="E8" s="25" t="n"/>
+      <c r="F8" s="25" t="n"/>
+      <c r="G8" s="25" t="n"/>
+      <c r="H8" s="25" t="n"/>
+      <c r="I8" s="25" t="n"/>
+      <c r="J8" s="25" t="n"/>
+      <c r="K8" s="25" t="n"/>
+      <c r="L8" s="25" t="n"/>
+      <c r="M8" s="25" t="n"/>
+      <c r="N8" s="26">
         <f>SUM(B8:M8)</f>
         <v/>
       </c>
-      <c r="O8" s="13">
+      <c r="O8" s="26">
         <f>SUM(B9:M9)</f>
         <v/>
       </c>
-      <c r="P8" s="13">
+      <c r="P8" s="26">
         <f>O8-N8</f>
         <v/>
       </c>
-      <c r="Q8" s="14">
+      <c r="Q8" s="27">
         <f>IF(N8=0,"",O8/N8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>Ventas - Real</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n"/>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
-      <c r="H9" s="12" t="n"/>
-      <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
-      <c r="K9" s="12" t="n"/>
-      <c r="L9" s="12" t="n"/>
-      <c r="M9" s="12" t="n"/>
+      <c r="B9" s="25" t="n"/>
+      <c r="C9" s="25" t="n"/>
+      <c r="D9" s="25" t="n"/>
+      <c r="E9" s="25" t="n"/>
+      <c r="F9" s="25" t="n"/>
+      <c r="G9" s="25" t="n"/>
+      <c r="H9" s="25" t="n"/>
+      <c r="I9" s="25" t="n"/>
+      <c r="J9" s="25" t="n"/>
+      <c r="K9" s="25" t="n"/>
+      <c r="L9" s="25" t="n"/>
+      <c r="M9" s="25" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>Costo de ventas - Presup.</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="12" t="n"/>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="12" t="n"/>
-      <c r="F10" s="12" t="n"/>
-      <c r="G10" s="12" t="n"/>
-      <c r="H10" s="12" t="n"/>
-      <c r="I10" s="12" t="n"/>
-      <c r="J10" s="12" t="n"/>
-      <c r="K10" s="12" t="n"/>
-      <c r="L10" s="12" t="n"/>
-      <c r="M10" s="12" t="n"/>
-      <c r="N10" s="13">
+      <c r="B10" s="25" t="n"/>
+      <c r="C10" s="25" t="n"/>
+      <c r="D10" s="25" t="n"/>
+      <c r="E10" s="25" t="n"/>
+      <c r="F10" s="25" t="n"/>
+      <c r="G10" s="25" t="n"/>
+      <c r="H10" s="25" t="n"/>
+      <c r="I10" s="25" t="n"/>
+      <c r="J10" s="25" t="n"/>
+      <c r="K10" s="25" t="n"/>
+      <c r="L10" s="25" t="n"/>
+      <c r="M10" s="25" t="n"/>
+      <c r="N10" s="26">
         <f>SUM(B10:M10)</f>
         <v/>
       </c>
-      <c r="O10" s="13">
+      <c r="O10" s="26">
         <f>SUM(B11:M11)</f>
         <v/>
       </c>
-      <c r="P10" s="13">
+      <c r="P10" s="26">
         <f>O10-N10</f>
         <v/>
       </c>
-      <c r="Q10" s="14">
+      <c r="Q10" s="27">
         <f>IF(N10=0,"",O10/N10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>Costo de ventas - Real</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
-      <c r="G11" s="12" t="n"/>
-      <c r="H11" s="12" t="n"/>
-      <c r="I11" s="12" t="n"/>
-      <c r="J11" s="12" t="n"/>
-      <c r="K11" s="12" t="n"/>
-      <c r="L11" s="12" t="n"/>
-      <c r="M11" s="12" t="n"/>
+      <c r="B11" s="25" t="n"/>
+      <c r="C11" s="25" t="n"/>
+      <c r="D11" s="25" t="n"/>
+      <c r="E11" s="25" t="n"/>
+      <c r="F11" s="25" t="n"/>
+      <c r="G11" s="25" t="n"/>
+      <c r="H11" s="25" t="n"/>
+      <c r="I11" s="25" t="n"/>
+      <c r="J11" s="25" t="n"/>
+      <c r="K11" s="25" t="n"/>
+      <c r="L11" s="25" t="n"/>
+      <c r="M11" s="25" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="24" t="inlineStr">
         <is>
           <t>Sueldos y salarios - Presup.</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="12" t="n"/>
-      <c r="G12" s="12" t="n"/>
-      <c r="H12" s="12" t="n"/>
-      <c r="I12" s="12" t="n"/>
-      <c r="J12" s="12" t="n"/>
-      <c r="K12" s="12" t="n"/>
-      <c r="L12" s="12" t="n"/>
-      <c r="M12" s="12" t="n"/>
-      <c r="N12" s="13">
+      <c r="B12" s="25" t="n"/>
+      <c r="C12" s="25" t="n"/>
+      <c r="D12" s="25" t="n"/>
+      <c r="E12" s="25" t="n"/>
+      <c r="F12" s="25" t="n"/>
+      <c r="G12" s="25" t="n"/>
+      <c r="H12" s="25" t="n"/>
+      <c r="I12" s="25" t="n"/>
+      <c r="J12" s="25" t="n"/>
+      <c r="K12" s="25" t="n"/>
+      <c r="L12" s="25" t="n"/>
+      <c r="M12" s="25" t="n"/>
+      <c r="N12" s="26">
         <f>SUM(B12:M12)</f>
         <v/>
       </c>
-      <c r="O12" s="13">
+      <c r="O12" s="26">
         <f>SUM(B13:M13)</f>
         <v/>
       </c>
-      <c r="P12" s="13">
+      <c r="P12" s="26">
         <f>O12-N12</f>
         <v/>
       </c>
-      <c r="Q12" s="14">
+      <c r="Q12" s="27">
         <f>IF(N12=0,"",O12/N12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="28" t="inlineStr">
         <is>
           <t>Sueldos y salarios - Real</t>
         </is>
       </c>
-      <c r="B13" s="12" t="n"/>
-      <c r="C13" s="12" t="n"/>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="12" t="n"/>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="12" t="n"/>
-      <c r="H13" s="12" t="n"/>
-      <c r="I13" s="12" t="n"/>
-      <c r="J13" s="12" t="n"/>
-      <c r="K13" s="12" t="n"/>
-      <c r="L13" s="12" t="n"/>
-      <c r="M13" s="12" t="n"/>
+      <c r="B13" s="25" t="n"/>
+      <c r="C13" s="25" t="n"/>
+      <c r="D13" s="25" t="n"/>
+      <c r="E13" s="25" t="n"/>
+      <c r="F13" s="25" t="n"/>
+      <c r="G13" s="25" t="n"/>
+      <c r="H13" s="25" t="n"/>
+      <c r="I13" s="25" t="n"/>
+      <c r="J13" s="25" t="n"/>
+      <c r="K13" s="25" t="n"/>
+      <c r="L13" s="25" t="n"/>
+      <c r="M13" s="25" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>Renta - Presup.</t>
         </is>
       </c>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="12" t="n"/>
-      <c r="D14" s="12" t="n"/>
-      <c r="E14" s="12" t="n"/>
-      <c r="F14" s="12" t="n"/>
-      <c r="G14" s="12" t="n"/>
-      <c r="H14" s="12" t="n"/>
-      <c r="I14" s="12" t="n"/>
-      <c r="J14" s="12" t="n"/>
-      <c r="K14" s="12" t="n"/>
-      <c r="L14" s="12" t="n"/>
-      <c r="M14" s="12" t="n"/>
-      <c r="N14" s="13">
+      <c r="B14" s="25" t="n"/>
+      <c r="C14" s="25" t="n"/>
+      <c r="D14" s="25" t="n"/>
+      <c r="E14" s="25" t="n"/>
+      <c r="F14" s="25" t="n"/>
+      <c r="G14" s="25" t="n"/>
+      <c r="H14" s="25" t="n"/>
+      <c r="I14" s="25" t="n"/>
+      <c r="J14" s="25" t="n"/>
+      <c r="K14" s="25" t="n"/>
+      <c r="L14" s="25" t="n"/>
+      <c r="M14" s="25" t="n"/>
+      <c r="N14" s="26">
         <f>SUM(B14:M14)</f>
         <v/>
       </c>
-      <c r="O14" s="13">
+      <c r="O14" s="26">
         <f>SUM(B15:M15)</f>
         <v/>
       </c>
-      <c r="P14" s="13">
+      <c r="P14" s="26">
         <f>O14-N14</f>
         <v/>
       </c>
-      <c r="Q14" s="14">
+      <c r="Q14" s="27">
         <f>IF(N14=0,"",O14/N14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="28" t="inlineStr">
         <is>
           <t>Renta - Real</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12" t="n"/>
-      <c r="G15" s="12" t="n"/>
-      <c r="H15" s="12" t="n"/>
-      <c r="I15" s="12" t="n"/>
-      <c r="J15" s="12" t="n"/>
-      <c r="K15" s="12" t="n"/>
-      <c r="L15" s="12" t="n"/>
-      <c r="M15" s="12" t="n"/>
+      <c r="B15" s="25" t="n"/>
+      <c r="C15" s="25" t="n"/>
+      <c r="D15" s="25" t="n"/>
+      <c r="E15" s="25" t="n"/>
+      <c r="F15" s="25" t="n"/>
+      <c r="G15" s="25" t="n"/>
+      <c r="H15" s="25" t="n"/>
+      <c r="I15" s="25" t="n"/>
+      <c r="J15" s="25" t="n"/>
+      <c r="K15" s="25" t="n"/>
+      <c r="L15" s="25" t="n"/>
+      <c r="M15" s="25" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="24" t="inlineStr">
         <is>
           <t>Servicios - Presup.</t>
         </is>
       </c>
-      <c r="B16" s="12" t="n"/>
-      <c r="C16" s="12" t="n"/>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="12" t="n"/>
-      <c r="F16" s="12" t="n"/>
-      <c r="G16" s="12" t="n"/>
-      <c r="H16" s="12" t="n"/>
-      <c r="I16" s="12" t="n"/>
-      <c r="J16" s="12" t="n"/>
-      <c r="K16" s="12" t="n"/>
-      <c r="L16" s="12" t="n"/>
-      <c r="M16" s="12" t="n"/>
-      <c r="N16" s="13">
+      <c r="B16" s="25" t="n"/>
+      <c r="C16" s="25" t="n"/>
+      <c r="D16" s="25" t="n"/>
+      <c r="E16" s="25" t="n"/>
+      <c r="F16" s="25" t="n"/>
+      <c r="G16" s="25" t="n"/>
+      <c r="H16" s="25" t="n"/>
+      <c r="I16" s="25" t="n"/>
+      <c r="J16" s="25" t="n"/>
+      <c r="K16" s="25" t="n"/>
+      <c r="L16" s="25" t="n"/>
+      <c r="M16" s="25" t="n"/>
+      <c r="N16" s="26">
         <f>SUM(B16:M16)</f>
         <v/>
       </c>
-      <c r="O16" s="13">
+      <c r="O16" s="26">
         <f>SUM(B17:M17)</f>
         <v/>
       </c>
-      <c r="P16" s="13">
+      <c r="P16" s="26">
         <f>O16-N16</f>
         <v/>
       </c>
-      <c r="Q16" s="14">
+      <c r="Q16" s="27">
         <f>IF(N16=0,"",O16/N16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="28" t="inlineStr">
         <is>
           <t>Servicios - Real</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="12" t="n"/>
-      <c r="H17" s="12" t="n"/>
-      <c r="I17" s="12" t="n"/>
-      <c r="J17" s="12" t="n"/>
-      <c r="K17" s="12" t="n"/>
-      <c r="L17" s="12" t="n"/>
-      <c r="M17" s="12" t="n"/>
+      <c r="B17" s="25" t="n"/>
+      <c r="C17" s="25" t="n"/>
+      <c r="D17" s="25" t="n"/>
+      <c r="E17" s="25" t="n"/>
+      <c r="F17" s="25" t="n"/>
+      <c r="G17" s="25" t="n"/>
+      <c r="H17" s="25" t="n"/>
+      <c r="I17" s="25" t="n"/>
+      <c r="J17" s="25" t="n"/>
+      <c r="K17" s="25" t="n"/>
+      <c r="L17" s="25" t="n"/>
+      <c r="M17" s="25" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="24" t="inlineStr">
         <is>
           <t>Publicidad y mercadotecnia - Presup.</t>
         </is>
       </c>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12" t="n"/>
-      <c r="G18" s="12" t="n"/>
-      <c r="H18" s="12" t="n"/>
-      <c r="I18" s="12" t="n"/>
-      <c r="J18" s="12" t="n"/>
-      <c r="K18" s="12" t="n"/>
-      <c r="L18" s="12" t="n"/>
-      <c r="M18" s="12" t="n"/>
-      <c r="N18" s="13">
+      <c r="B18" s="25" t="n"/>
+      <c r="C18" s="25" t="n"/>
+      <c r="D18" s="25" t="n"/>
+      <c r="E18" s="25" t="n"/>
+      <c r="F18" s="25" t="n"/>
+      <c r="G18" s="25" t="n"/>
+      <c r="H18" s="25" t="n"/>
+      <c r="I18" s="25" t="n"/>
+      <c r="J18" s="25" t="n"/>
+      <c r="K18" s="25" t="n"/>
+      <c r="L18" s="25" t="n"/>
+      <c r="M18" s="25" t="n"/>
+      <c r="N18" s="26">
         <f>SUM(B18:M18)</f>
         <v/>
       </c>
-      <c r="O18" s="13">
+      <c r="O18" s="26">
         <f>SUM(B19:M19)</f>
         <v/>
       </c>
-      <c r="P18" s="13">
+      <c r="P18" s="26">
         <f>O18-N18</f>
         <v/>
       </c>
-      <c r="Q18" s="14">
+      <c r="Q18" s="27">
         <f>IF(N18=0,"",O18/N18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="28" t="inlineStr">
         <is>
           <t>Publicidad y mercadotecnia - Real</t>
         </is>
       </c>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" s="12" t="n"/>
-      <c r="F19" s="12" t="n"/>
-      <c r="G19" s="12" t="n"/>
-      <c r="H19" s="12" t="n"/>
-      <c r="I19" s="12" t="n"/>
-      <c r="J19" s="12" t="n"/>
-      <c r="K19" s="12" t="n"/>
-      <c r="L19" s="12" t="n"/>
-      <c r="M19" s="12" t="n"/>
+      <c r="B19" s="25" t="n"/>
+      <c r="C19" s="25" t="n"/>
+      <c r="D19" s="25" t="n"/>
+      <c r="E19" s="25" t="n"/>
+      <c r="F19" s="25" t="n"/>
+      <c r="G19" s="25" t="n"/>
+      <c r="H19" s="25" t="n"/>
+      <c r="I19" s="25" t="n"/>
+      <c r="J19" s="25" t="n"/>
+      <c r="K19" s="25" t="n"/>
+      <c r="L19" s="25" t="n"/>
+      <c r="M19" s="25" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="24" t="inlineStr">
         <is>
           <t>Mantenimiento - Presup.</t>
         </is>
       </c>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="12" t="n"/>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="12" t="n"/>
-      <c r="F20" s="12" t="n"/>
-      <c r="G20" s="12" t="n"/>
-      <c r="H20" s="12" t="n"/>
-      <c r="I20" s="12" t="n"/>
-      <c r="J20" s="12" t="n"/>
-      <c r="K20" s="12" t="n"/>
-      <c r="L20" s="12" t="n"/>
-      <c r="M20" s="12" t="n"/>
-      <c r="N20" s="13">
+      <c r="B20" s="25" t="n"/>
+      <c r="C20" s="25" t="n"/>
+      <c r="D20" s="25" t="n"/>
+      <c r="E20" s="25" t="n"/>
+      <c r="F20" s="25" t="n"/>
+      <c r="G20" s="25" t="n"/>
+      <c r="H20" s="25" t="n"/>
+      <c r="I20" s="25" t="n"/>
+      <c r="J20" s="25" t="n"/>
+      <c r="K20" s="25" t="n"/>
+      <c r="L20" s="25" t="n"/>
+      <c r="M20" s="25" t="n"/>
+      <c r="N20" s="26">
         <f>SUM(B20:M20)</f>
         <v/>
       </c>
-      <c r="O20" s="13">
+      <c r="O20" s="26">
         <f>SUM(B21:M21)</f>
         <v/>
       </c>
-      <c r="P20" s="13">
+      <c r="P20" s="26">
         <f>O20-N20</f>
         <v/>
       </c>
-      <c r="Q20" s="14">
+      <c r="Q20" s="27">
         <f>IF(N20=0,"",O20/N20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="28" t="inlineStr">
         <is>
           <t>Mantenimiento - Real</t>
         </is>
       </c>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="12" t="n"/>
-      <c r="D21" s="12" t="n"/>
-      <c r="E21" s="12" t="n"/>
-      <c r="F21" s="12" t="n"/>
-      <c r="G21" s="12" t="n"/>
-      <c r="H21" s="12" t="n"/>
-      <c r="I21" s="12" t="n"/>
-      <c r="J21" s="12" t="n"/>
-      <c r="K21" s="12" t="n"/>
-      <c r="L21" s="12" t="n"/>
-      <c r="M21" s="12" t="n"/>
+      <c r="B21" s="25" t="n"/>
+      <c r="C21" s="25" t="n"/>
+      <c r="D21" s="25" t="n"/>
+      <c r="E21" s="25" t="n"/>
+      <c r="F21" s="25" t="n"/>
+      <c r="G21" s="25" t="n"/>
+      <c r="H21" s="25" t="n"/>
+      <c r="I21" s="25" t="n"/>
+      <c r="J21" s="25" t="n"/>
+      <c r="K21" s="25" t="n"/>
+      <c r="L21" s="25" t="n"/>
+      <c r="M21" s="25" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="24" t="inlineStr">
         <is>
           <t>Papelería y oficina - Presup.</t>
         </is>
       </c>
-      <c r="B22" s="12" t="n"/>
-      <c r="C22" s="12" t="n"/>
-      <c r="D22" s="12" t="n"/>
-      <c r="E22" s="12" t="n"/>
-      <c r="F22" s="12" t="n"/>
-      <c r="G22" s="12" t="n"/>
-      <c r="H22" s="12" t="n"/>
-      <c r="I22" s="12" t="n"/>
-      <c r="J22" s="12" t="n"/>
-      <c r="K22" s="12" t="n"/>
-      <c r="L22" s="12" t="n"/>
-      <c r="M22" s="12" t="n"/>
-      <c r="N22" s="13">
+      <c r="B22" s="25" t="n"/>
+      <c r="C22" s="25" t="n"/>
+      <c r="D22" s="25" t="n"/>
+      <c r="E22" s="25" t="n"/>
+      <c r="F22" s="25" t="n"/>
+      <c r="G22" s="25" t="n"/>
+      <c r="H22" s="25" t="n"/>
+      <c r="I22" s="25" t="n"/>
+      <c r="J22" s="25" t="n"/>
+      <c r="K22" s="25" t="n"/>
+      <c r="L22" s="25" t="n"/>
+      <c r="M22" s="25" t="n"/>
+      <c r="N22" s="26">
         <f>SUM(B22:M22)</f>
         <v/>
       </c>
-      <c r="O22" s="13">
+      <c r="O22" s="26">
         <f>SUM(B23:M23)</f>
         <v/>
       </c>
-      <c r="P22" s="13">
+      <c r="P22" s="26">
         <f>O22-N22</f>
         <v/>
       </c>
-      <c r="Q22" s="14">
+      <c r="Q22" s="27">
         <f>IF(N22=0,"",O22/N22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="28" t="inlineStr">
         <is>
           <t>Papelería y oficina - Real</t>
         </is>
       </c>
-      <c r="B23" s="12" t="n"/>
-      <c r="C23" s="12" t="n"/>
-      <c r="D23" s="12" t="n"/>
-      <c r="E23" s="12" t="n"/>
-      <c r="F23" s="12" t="n"/>
-      <c r="G23" s="12" t="n"/>
-      <c r="H23" s="12" t="n"/>
-      <c r="I23" s="12" t="n"/>
-      <c r="J23" s="12" t="n"/>
-      <c r="K23" s="12" t="n"/>
-      <c r="L23" s="12" t="n"/>
-      <c r="M23" s="12" t="n"/>
+      <c r="B23" s="25" t="n"/>
+      <c r="C23" s="25" t="n"/>
+      <c r="D23" s="25" t="n"/>
+      <c r="E23" s="25" t="n"/>
+      <c r="F23" s="25" t="n"/>
+      <c r="G23" s="25" t="n"/>
+      <c r="H23" s="25" t="n"/>
+      <c r="I23" s="25" t="n"/>
+      <c r="J23" s="25" t="n"/>
+      <c r="K23" s="25" t="n"/>
+      <c r="L23" s="25" t="n"/>
+      <c r="M23" s="25" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="24" t="inlineStr">
         <is>
           <t>Impuestos y derechos - Presup.</t>
         </is>
       </c>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="12" t="n"/>
-      <c r="F24" s="12" t="n"/>
-      <c r="G24" s="12" t="n"/>
-      <c r="H24" s="12" t="n"/>
-      <c r="I24" s="12" t="n"/>
-      <c r="J24" s="12" t="n"/>
-      <c r="K24" s="12" t="n"/>
-      <c r="L24" s="12" t="n"/>
-      <c r="M24" s="12" t="n"/>
-      <c r="N24" s="13">
+      <c r="B24" s="25" t="n"/>
+      <c r="C24" s="25" t="n"/>
+      <c r="D24" s="25" t="n"/>
+      <c r="E24" s="25" t="n"/>
+      <c r="F24" s="25" t="n"/>
+      <c r="G24" s="25" t="n"/>
+      <c r="H24" s="25" t="n"/>
+      <c r="I24" s="25" t="n"/>
+      <c r="J24" s="25" t="n"/>
+      <c r="K24" s="25" t="n"/>
+      <c r="L24" s="25" t="n"/>
+      <c r="M24" s="25" t="n"/>
+      <c r="N24" s="26">
         <f>SUM(B24:M24)</f>
         <v/>
       </c>
-      <c r="O24" s="13">
+      <c r="O24" s="26">
         <f>SUM(B25:M25)</f>
         <v/>
       </c>
-      <c r="P24" s="13">
+      <c r="P24" s="26">
         <f>O24-N24</f>
         <v/>
       </c>
-      <c r="Q24" s="14">
+      <c r="Q24" s="27">
         <f>IF(N24=0,"",O24/N24)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="28" t="inlineStr">
         <is>
           <t>Impuestos y derechos - Real</t>
         </is>
       </c>
-      <c r="B25" s="12" t="n"/>
-      <c r="C25" s="12" t="n"/>
-      <c r="D25" s="12" t="n"/>
-      <c r="E25" s="12" t="n"/>
-      <c r="F25" s="12" t="n"/>
-      <c r="G25" s="12" t="n"/>
-      <c r="H25" s="12" t="n"/>
-      <c r="I25" s="12" t="n"/>
-      <c r="J25" s="12" t="n"/>
-      <c r="K25" s="12" t="n"/>
-      <c r="L25" s="12" t="n"/>
-      <c r="M25" s="12" t="n"/>
+      <c r="B25" s="25" t="n"/>
+      <c r="C25" s="25" t="n"/>
+      <c r="D25" s="25" t="n"/>
+      <c r="E25" s="25" t="n"/>
+      <c r="F25" s="25" t="n"/>
+      <c r="G25" s="25" t="n"/>
+      <c r="H25" s="25" t="n"/>
+      <c r="I25" s="25" t="n"/>
+      <c r="J25" s="25" t="n"/>
+      <c r="K25" s="25" t="n"/>
+      <c r="L25" s="25" t="n"/>
+      <c r="M25" s="25" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="24" t="inlineStr">
         <is>
           <t>Otros gastos - Presup.</t>
         </is>
       </c>
-      <c r="B26" s="12" t="n"/>
-      <c r="C26" s="12" t="n"/>
-      <c r="D26" s="12" t="n"/>
-      <c r="E26" s="12" t="n"/>
-      <c r="F26" s="12" t="n"/>
-      <c r="G26" s="12" t="n"/>
-      <c r="H26" s="12" t="n"/>
-      <c r="I26" s="12" t="n"/>
-      <c r="J26" s="12" t="n"/>
-      <c r="K26" s="12" t="n"/>
-      <c r="L26" s="12" t="n"/>
-      <c r="M26" s="12" t="n"/>
-      <c r="N26" s="13">
+      <c r="B26" s="25" t="n"/>
+      <c r="C26" s="25" t="n"/>
+      <c r="D26" s="25" t="n"/>
+      <c r="E26" s="25" t="n"/>
+      <c r="F26" s="25" t="n"/>
+      <c r="G26" s="25" t="n"/>
+      <c r="H26" s="25" t="n"/>
+      <c r="I26" s="25" t="n"/>
+      <c r="J26" s="25" t="n"/>
+      <c r="K26" s="25" t="n"/>
+      <c r="L26" s="25" t="n"/>
+      <c r="M26" s="25" t="n"/>
+      <c r="N26" s="26">
         <f>SUM(B26:M26)</f>
         <v/>
       </c>
-      <c r="O26" s="13">
+      <c r="O26" s="26">
         <f>SUM(B27:M27)</f>
         <v/>
       </c>
-      <c r="P26" s="13">
+      <c r="P26" s="26">
         <f>O26-N26</f>
         <v/>
       </c>
-      <c r="Q26" s="14">
+      <c r="Q26" s="27">
         <f>IF(N26=0,"",O26/N26)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="28" t="inlineStr">
         <is>
           <t>Otros gastos - Real</t>
         </is>
       </c>
-      <c r="B27" s="12" t="n"/>
-      <c r="C27" s="12" t="n"/>
-      <c r="D27" s="12" t="n"/>
-      <c r="E27" s="12" t="n"/>
-      <c r="F27" s="12" t="n"/>
-      <c r="G27" s="12" t="n"/>
-      <c r="H27" s="12" t="n"/>
-      <c r="I27" s="12" t="n"/>
-      <c r="J27" s="12" t="n"/>
-      <c r="K27" s="12" t="n"/>
-      <c r="L27" s="12" t="n"/>
-      <c r="M27" s="12" t="n"/>
+      <c r="B27" s="25" t="n"/>
+      <c r="C27" s="25" t="n"/>
+      <c r="D27" s="25" t="n"/>
+      <c r="E27" s="25" t="n"/>
+      <c r="F27" s="25" t="n"/>
+      <c r="G27" s="25" t="n"/>
+      <c r="H27" s="25" t="n"/>
+      <c r="I27" s="25" t="n"/>
+      <c r="J27" s="25" t="n"/>
+      <c r="K27" s="25" t="n"/>
+      <c r="L27" s="25" t="n"/>
+      <c r="M27" s="25" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1272,95 +1547,14 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="B1" s="16" t="inlineStr">
-        <is>
-          <t>Presupuesto anual</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="17" t="inlineStr">
-        <is>
-          <t>Guía de uso</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>Por cada concepto hay dos renglones: Presup. (lo planeado) y Real (lo ejercido).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="19" t="inlineStr">
-        <is>
-          <t>Captura mes a mes. La columna Variación muestra Real - Presupuesto del primer renglón de cada concepto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>En gastos, una variación positiva (rojo) significa que te pasaste del presupuesto; en ventas, positiva es favorable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>El % de ejecución indica qué parte del presupuesto anual ya se ejerció.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>Personaliza: en el recuadro punteado de la esquina superior derecha inserta tu logo (Insertar &gt; Imágenes) y captura los datos de tu empresa en las celdas amarillas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="20" t="inlineStr">
-        <is>
-          <t>Celdas amarillas = captura · Celdas grises = cálculo automático (no modificar).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 Página &amp;P&amp;R&amp;8 Impreso: &amp;D</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/plantillas/1_Contabilidad_y_Finanzas/06_Presupuesto_Anual.xlsx
+++ b/plantillas/1_Contabilidad_y_Finanzas/06_Presupuesto_Anual.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portada" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formato" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,6 +60,18 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001B6B73"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000B2A4A"/>
+      <sz val="18"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -105,7 +118,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -132,8 +145,13 @@
         <fgColor rgb="00EEF2F5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -202,6 +220,48 @@
       </bottom>
     </border>
     <border>
+      <top style="dashed">
+        <color rgb="00A6A6A6"/>
+      </top>
+    </border>
+    <border>
+      <bottom style="dashed">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9D3DB"/>
+      </left>
+      <top style="medium">
+        <color rgb="00C9A227"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00C9D3DB"/>
+      </right>
+      <top style="medium">
+        <color rgb="00C9A227"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9D3DB"/>
+      </left>
+      <bottom style="thin">
+        <color rgb="00C9D3DB"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00C9D3DB"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="00C9D3DB"/>
+      </bottom>
+    </border>
+    <border>
       <top style="thick">
         <color rgb="00C9A227"/>
       </top>
@@ -215,26 +275,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -253,10 +315,22 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -340,6 +414,153 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Presupuesto vs. real por concepto</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Resumen'!C8</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="0B2A4A"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="0B2A4A"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Resumen'!$B$9:$B$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Resumen'!$C$9:$C$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Resumen'!D8</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="C9A227"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="C9A227"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Resumen'!$B$9:$B$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Resumen'!$D$9:$D$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <numFmt formatCode="&quot;$&quot;#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8460000" cy="3060000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -701,6 +922,7 @@
       <c r="C8" s="5" t="n"/>
       <c r="D8" s="5" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="B10" s="6" t="inlineStr">
         <is>
@@ -758,6 +980,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
@@ -789,6 +1012,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="13" t="n"/>
       <c r="B22" s="13" t="n"/>
@@ -803,6 +1027,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
@@ -888,6 +1113,7 @@
       <c r="P2" s="20" t="n"/>
       <c r="Q2" s="21" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="22" t="inlineStr">
         <is>
@@ -906,6 +1132,8 @@
         <v>2026</v>
       </c>
     </row>
+    <row r="5"/>
+    <row r="6"/>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="23" t="inlineStr">
         <is>
@@ -1534,6 +1762,7 @@
       <c r="M27" s="25" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="4">
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="B4:D4"/>
@@ -1557,4 +1786,401 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C9A227"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="2" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="44" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>RESUMEN DEL PRESUPUESTO</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="16" t="inlineStr">
+        <is>
+          <t>INSERTE SU LOGO
+(clic derecho &gt; Insertar imagen)</t>
+        </is>
+      </c>
+      <c r="I1" s="29" t="n"/>
+      <c r="J1" s="17" t="n"/>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>Presupuestado vs. real por concepto</t>
+        </is>
+      </c>
+      <c r="B2" s="19" t="n"/>
+      <c r="C2" s="19" t="n"/>
+      <c r="D2" s="19" t="n"/>
+      <c r="E2" s="19" t="n"/>
+      <c r="F2" s="19" t="n"/>
+      <c r="G2" s="19" t="n"/>
+      <c r="H2" s="20" t="n"/>
+      <c r="I2" s="30" t="n"/>
+      <c r="J2" s="21" t="n"/>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="20" customHeight="1">
+      <c r="B4" s="31" t="inlineStr">
+        <is>
+          <t>VENTAS PRESUPUESTADAS</t>
+        </is>
+      </c>
+      <c r="C4" s="32" t="n"/>
+      <c r="D4" s="31" t="inlineStr">
+        <is>
+          <t>VENTAS REALES</t>
+        </is>
+      </c>
+      <c r="E4" s="32" t="n"/>
+      <c r="F4" s="31" t="inlineStr">
+        <is>
+          <t>GASTO PRESUPUESTADO</t>
+        </is>
+      </c>
+      <c r="G4" s="32" t="n"/>
+      <c r="H4" s="31" t="inlineStr">
+        <is>
+          <t>GASTO REAL</t>
+        </is>
+      </c>
+      <c r="I4" s="32" t="n"/>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="B5" s="33">
+        <f>C9</f>
+        <v/>
+      </c>
+      <c r="C5" s="34" t="n"/>
+      <c r="D5" s="33">
+        <f>D9</f>
+        <v/>
+      </c>
+      <c r="E5" s="34" t="n"/>
+      <c r="F5" s="33">
+        <f>SUM(C10:C18)</f>
+        <v/>
+      </c>
+      <c r="G5" s="34" t="n"/>
+      <c r="H5" s="33">
+        <f>SUM(D10:D18)</f>
+        <v/>
+      </c>
+      <c r="I5" s="34" t="n"/>
+    </row>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>Concepto</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>Presupuesto</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>Real</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>Variación</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>% ejec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="C9" s="26">
+        <f>Formato!N8</f>
+        <v/>
+      </c>
+      <c r="D9" s="26">
+        <f>Formato!O8</f>
+        <v/>
+      </c>
+      <c r="E9" s="26">
+        <f>D9-C9</f>
+        <v/>
+      </c>
+      <c r="F9" s="27">
+        <f>IF(C9=0,"",D9/C9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>Costo de ventas</t>
+        </is>
+      </c>
+      <c r="C10" s="26">
+        <f>Formato!N10</f>
+        <v/>
+      </c>
+      <c r="D10" s="26">
+        <f>Formato!O10</f>
+        <v/>
+      </c>
+      <c r="E10" s="26">
+        <f>D10-C10</f>
+        <v/>
+      </c>
+      <c r="F10" s="27">
+        <f>IF(C10=0,"",D10/C10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="28" t="inlineStr">
+        <is>
+          <t>Sueldos y salarios</t>
+        </is>
+      </c>
+      <c r="C11" s="26">
+        <f>Formato!N12</f>
+        <v/>
+      </c>
+      <c r="D11" s="26">
+        <f>Formato!O12</f>
+        <v/>
+      </c>
+      <c r="E11" s="26">
+        <f>D11-C11</f>
+        <v/>
+      </c>
+      <c r="F11" s="27">
+        <f>IF(C11=0,"",D11/C11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>Renta</t>
+        </is>
+      </c>
+      <c r="C12" s="26">
+        <f>Formato!N14</f>
+        <v/>
+      </c>
+      <c r="D12" s="26">
+        <f>Formato!O14</f>
+        <v/>
+      </c>
+      <c r="E12" s="26">
+        <f>D12-C12</f>
+        <v/>
+      </c>
+      <c r="F12" s="27">
+        <f>IF(C12=0,"",D12/C12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="28" t="inlineStr">
+        <is>
+          <t>Servicios</t>
+        </is>
+      </c>
+      <c r="C13" s="26">
+        <f>Formato!N16</f>
+        <v/>
+      </c>
+      <c r="D13" s="26">
+        <f>Formato!O16</f>
+        <v/>
+      </c>
+      <c r="E13" s="26">
+        <f>D13-C13</f>
+        <v/>
+      </c>
+      <c r="F13" s="27">
+        <f>IF(C13=0,"",D13/C13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>Publicidad y mercadotecnia</t>
+        </is>
+      </c>
+      <c r="C14" s="26">
+        <f>Formato!N18</f>
+        <v/>
+      </c>
+      <c r="D14" s="26">
+        <f>Formato!O18</f>
+        <v/>
+      </c>
+      <c r="E14" s="26">
+        <f>D14-C14</f>
+        <v/>
+      </c>
+      <c r="F14" s="27">
+        <f>IF(C14=0,"",D14/C14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="28" t="inlineStr">
+        <is>
+          <t>Mantenimiento</t>
+        </is>
+      </c>
+      <c r="C15" s="26">
+        <f>Formato!N20</f>
+        <v/>
+      </c>
+      <c r="D15" s="26">
+        <f>Formato!O20</f>
+        <v/>
+      </c>
+      <c r="E15" s="26">
+        <f>D15-C15</f>
+        <v/>
+      </c>
+      <c r="F15" s="27">
+        <f>IF(C15=0,"",D15/C15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t>Papelería y oficina</t>
+        </is>
+      </c>
+      <c r="C16" s="26">
+        <f>Formato!N22</f>
+        <v/>
+      </c>
+      <c r="D16" s="26">
+        <f>Formato!O22</f>
+        <v/>
+      </c>
+      <c r="E16" s="26">
+        <f>D16-C16</f>
+        <v/>
+      </c>
+      <c r="F16" s="27">
+        <f>IF(C16=0,"",D16/C16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="28" t="inlineStr">
+        <is>
+          <t>Impuestos y derechos</t>
+        </is>
+      </c>
+      <c r="C17" s="26">
+        <f>Formato!N24</f>
+        <v/>
+      </c>
+      <c r="D17" s="26">
+        <f>Formato!O24</f>
+        <v/>
+      </c>
+      <c r="E17" s="26">
+        <f>D17-C17</f>
+        <v/>
+      </c>
+      <c r="F17" s="27">
+        <f>IF(C17=0,"",D17/C17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="28" t="inlineStr">
+        <is>
+          <t>Otros gastos</t>
+        </is>
+      </c>
+      <c r="C18" s="26">
+        <f>Formato!N26</f>
+        <v/>
+      </c>
+      <c r="D18" s="26">
+        <f>Formato!O26</f>
+        <v/>
+      </c>
+      <c r="E18" s="26">
+        <f>D18-C18</f>
+        <v/>
+      </c>
+      <c r="F18" s="27">
+        <f>IF(C18=0,"",D18/C18)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <mergeCells count="11">
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H1:J2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="B4:C4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 Página &amp;P&amp;R&amp;8 Impreso: &amp;D</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/plantillas/1_Contabilidad_y_Finanzas/06_Presupuesto_Anual.xlsx
+++ b/plantillas/1_Contabilidad_y_Finanzas/06_Presupuesto_Anual.xlsx
@@ -7,9 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portada" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formato" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PORTADA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FORMATO" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RESUMEN" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYUDA" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,92 +31,145 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="20"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <i val="1"/>
       <color rgb="005B6B78"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <i val="1"/>
       <color rgb="00A6A6A6"/>
       <sz val="8"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <b val="1"/>
       <color rgb="001B6B73"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <b val="1"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <b val="1"/>
       <color rgb="001B6B73"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <b val="1"/>
       <color rgb="000B2A4A"/>
       <sz val="18"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="00C9A227"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="00C9D3DB"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="30"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <i val="1"/>
+      <color rgb="00C9D3DB"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="00C9A227"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="001B6B73"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="000B2A4A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <color rgb="002B2B2B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="00C9A227"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="001B6B73"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <color rgb="005B6B78"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <color rgb="00C9D3DB"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
       <b val="1"/>
       <color rgb="00C9A227"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="26"/>
+      <color rgb="001B6B73"/>
+      <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <color rgb="00C9D3DB"/>
+      <name val="Abadi"/>
+      <color rgb="000B2A4A"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="001B6B73"/>
+      <name val="Abadi"/>
+      <color theme="1"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00C9A227"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="002B2B2B"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="005B6B78"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="008A97A3"/>
-      <sz val="9"/>
     </font>
   </fonts>
   <fills count="7">
@@ -151,7 +205,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -262,75 +316,129 @@
       </bottom>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="00C9A227"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C9A227"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9A227"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9A227"/>
+      </bottom>
+    </border>
+    <border>
       <top style="thick">
         <color rgb="00C9A227"/>
       </top>
     </border>
     <border>
-      <top style="thin">
-        <color rgb="00C9A227"/>
-      </top>
+      <bottom style="thin">
+        <color rgb="00C9D3DB"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="25" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="25" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="25" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -338,7 +446,7 @@
   <dxfs count="1">
     <dxf>
       <font>
-        <name val="Calibri"/>
+        <name val="Abadi"/>
         <b val="1"/>
         <color rgb="00C00000"/>
       </font>
@@ -443,7 +551,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Resumen'!C8</f>
+              <f>'RESUMEN'!C8</f>
             </strRef>
           </tx>
           <spPr>
@@ -459,12 +567,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Resumen'!$B$9:$B$18</f>
+              <f>'RESUMEN'!$B$9:$B$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Resumen'!$C$9:$C$18</f>
+              <f>'RESUMEN'!$C$9:$C$18</f>
             </numRef>
           </val>
         </ser>
@@ -473,7 +581,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Resumen'!D8</f>
+              <f>'RESUMEN'!D8</f>
             </strRef>
           </tx>
           <spPr>
@@ -489,12 +597,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Resumen'!$B$9:$B$18</f>
+              <f>'RESUMEN'!$B$9:$B$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Resumen'!$D$9:$D$18</f>
+              <f>'RESUMEN'!$D$9:$D$18</f>
             </numRef>
           </val>
         </ser>
@@ -853,22 +961,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="5" customWidth="1" min="2" max="2"/>
-    <col width="88" customWidth="1" min="3" max="3"/>
-    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="8" customHeight="1">
       <c r="A1" s="1" t="n"/>
       <c r="B1" s="1" t="n"/>
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
-    </row>
-    <row r="2" ht="20" customHeight="1">
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -877,157 +991,513 @@
       </c>
       <c r="C2" s="1" t="n"/>
       <c r="D2" s="1" t="n"/>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>VERSIÓN 2.0  ·  MÉXICO</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="1" t="n"/>
       <c r="C3" s="1" t="n"/>
       <c r="D3" s="1" t="n"/>
-    </row>
-    <row r="4" ht="40" customHeight="1">
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="1" t="n"/>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Presupuesto anual</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="n"/>
-      <c r="D4" s="1" t="n"/>
-    </row>
-    <row r="5">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>PRESUPUESTO ANUAL</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="1" t="n"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="1" t="n"/>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Formato administrativo editable · México</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="n"/>
-      <c r="D5" s="1" t="n"/>
-    </row>
-    <row r="6">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="1" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
       <c r="A6" s="1" t="n"/>
-      <c r="B6" s="1" t="n"/>
-      <c r="C6" s="1" t="n"/>
-      <c r="D6" s="1" t="n"/>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Formato administrativo profesional · editable · listo para imprimir</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="1" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="1" t="n"/>
       <c r="C7" s="1" t="n"/>
       <c r="D7" s="1" t="n"/>
-    </row>
-    <row r="8" ht="6" customHeight="1">
-      <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-    </row>
-    <row r="9"/>
+      <c r="E7" s="1" t="n"/>
+      <c r="F7" s="1" t="n"/>
+      <c r="G7" s="1" t="n"/>
+    </row>
+    <row r="8" ht="4" customHeight="1">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="1" t="n"/>
+      <c r="C8" s="1" t="n"/>
+      <c r="D8" s="1" t="n"/>
+      <c r="E8" s="1" t="n"/>
+      <c r="F8" s="1" t="n"/>
+      <c r="G8" s="1" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="1" t="n"/>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>FÓRMULAS AUTOMÁTICAS</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>LISTAS DESPLEGABLES</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>HOJAS PROTEGIDAS</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>LISTO PARA IMPRIMIR</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="n"/>
+    </row>
     <row r="10">
-      <c r="B10" s="6" t="inlineStr">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="1" t="n"/>
+      <c r="C10" s="1" t="n"/>
+      <c r="D10" s="1" t="n"/>
+      <c r="E10" s="1" t="n"/>
+      <c r="F10" s="1" t="n"/>
+      <c r="G10" s="1" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="1" t="n"/>
+      <c r="C11" s="1" t="n"/>
+      <c r="D11" s="1" t="n"/>
+      <c r="E11" s="1" t="n"/>
+      <c r="F11" s="1" t="n"/>
+      <c r="G11" s="1" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="1" t="n"/>
+      <c r="C12" s="1" t="n"/>
+      <c r="D12" s="1" t="n"/>
+      <c r="E12" s="1" t="n"/>
+      <c r="F12" s="1" t="n"/>
+      <c r="G12" s="1" t="n"/>
+    </row>
+    <row r="13" ht="6" customHeight="1">
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>¿QUÉ INCLUYE ESTE ARCHIVO?</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
+      <c r="G15" s="4" t="n"/>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>▸</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>FORMATO</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>Hoja principal de captura. Aquí registras tu información; las celdas grises calculan solas.</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>▸</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>RESUMEN</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>Tablero con indicadores y gráficas que se actualizan automáticamente con tus datos.</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="21" customHeight="1">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>▸</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>AYUDA</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>Preguntas frecuentes, glosario y lista de verificación para cerrar tu periodo.</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>CÓMO USARLO</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="21" customHeight="1">
-      <c r="B11" s="7" t="n">
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="10" t="n"/>
+      <c r="F20" s="10" t="n"/>
+      <c r="G20" s="4" t="n"/>
+    </row>
+    <row r="21" ht="21" customHeight="1">
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C21" s="13" t="inlineStr">
         <is>
           <t>Por cada concepto hay dos renglones: Presup. (lo planeado) y Real (lo ejercido).</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="B12" s="7" t="n">
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+    </row>
+    <row r="22" ht="21" customHeight="1">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>Captura mes a mes. La columna Variación muestra Real - Presupuesto del primer renglón de cada concepto.</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="36" customHeight="1">
-      <c r="B13" s="7" t="n">
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>En gastos, una variación positiva (rojo) significa que te pasaste del presupuesto; en ventas, positiva es favorable.</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="21" customHeight="1">
-      <c r="B14" s="7" t="n">
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
+    </row>
+    <row r="24" ht="21" customHeight="1">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t>El % de ejecución indica qué parte del presupuesto anual ya se ejerció.</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="B15" s="7" t="n">
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Personaliza: en el recuadro punteado de la esquina superior derecha inserta tu logo (Insertar &gt; Imágenes) y captura los datos de tu empresa en las celdas de captura.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>LEYENDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="9" t="inlineStr"/>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>Celda de captura: escribe aquí.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="11" t="inlineStr"/>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>Cálculo automático: no la modifiques.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="12" t="inlineStr"/>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>Encabezados y títulos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="13" t="n"/>
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="13" t="n"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="14" t="inlineStr">
-        <is>
-          <t>GRUPO CANVILLE · Formatos administrativos · v1.0</t>
-        </is>
-      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Personaliza: inserta tu logotipo en el recuadro punteado de la esquina superior derecha (Insertar &gt; Imágenes) y captura los datos de tu empresa en las celdas de captura.</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n"/>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="4" t="n"/>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>RECOMENDACIONES DE USO</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="10" t="n"/>
+      <c r="F27" s="10" t="n"/>
+      <c r="G27" s="4" t="n"/>
+    </row>
+    <row r="28" ht="21" customHeight="1">
+      <c r="A28" s="4" t="n"/>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Parte de los resultados del año anterior y ajusta por inflación y metas de ventas.</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+    </row>
+    <row r="29" ht="21" customHeight="1">
+      <c r="A29" s="4" t="n"/>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Revisa la variación cada mes y toma acciones si pasa del 10%.</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="n"/>
+    </row>
+    <row r="30" ht="21" customHeight="1">
+      <c r="A30" s="4" t="n"/>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Separa gastos fijos y variables para identificar dónde puedes ahorrar.</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="4" t="n"/>
+    </row>
+    <row r="31" ht="21" customHeight="1">
+      <c r="A31" s="4" t="n"/>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>Actualiza la proyección trimestralmente (reforecast).</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n"/>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="4" t="n"/>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>LEYENDA DE COLORES</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
+      <c r="G33" s="4" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n"/>
+      <c r="B34" s="17" t="inlineStr"/>
+      <c r="C34" s="18" t="inlineStr">
+        <is>
+          <t>CELDA DE CAPTURA: escribe aquí.</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n"/>
+      <c r="B35" s="19" t="inlineStr"/>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>CÁLCULO AUTOMÁTICO: no la modifiques.</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="n"/>
+      <c r="G35" s="4" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n"/>
+      <c r="B36" s="20" t="inlineStr"/>
+      <c r="C36" s="18" t="inlineStr">
+        <is>
+          <t>ENCABEZADOS Y TÍTULOS.</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n"/>
+      <c r="B37" s="4" t="n"/>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="1" t="n"/>
+      <c r="B38" s="21" t="inlineStr">
+        <is>
+          <t>GRUPO CANVILLE  ·  Formatos administrativos  ·  Para uso interno de tu empresa</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="1" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <mergeCells count="16">
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="B4:F5"/>
+    <mergeCell ref="C28:F28"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
@@ -1063,7 +1533,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="44" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>PRESUPUESTO ANUAL: PRESUPUESTADO VS REAL</t>
         </is>
@@ -1082,684 +1552,789 @@
       <c r="M1" s="1" t="n"/>
       <c r="N1" s="1" t="n"/>
       <c r="O1" s="1" t="n"/>
-      <c r="P1" s="16" t="inlineStr">
+      <c r="P1" s="23" t="inlineStr">
         <is>
           <t>INSERTE SU LOGO
 (clic derecho &gt; Insertar imagen)</t>
         </is>
       </c>
-      <c r="Q1" s="17" t="n"/>
+      <c r="Q1" s="24" t="n"/>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="25" t="inlineStr">
         <is>
           <t>Captura presupuesto y gasto real por mes; la variación se calcula sola</t>
         </is>
       </c>
-      <c r="B2" s="19" t="n"/>
-      <c r="C2" s="19" t="n"/>
-      <c r="D2" s="19" t="n"/>
-      <c r="E2" s="19" t="n"/>
-      <c r="F2" s="19" t="n"/>
-      <c r="G2" s="19" t="n"/>
-      <c r="H2" s="19" t="n"/>
-      <c r="I2" s="19" t="n"/>
-      <c r="J2" s="19" t="n"/>
-      <c r="K2" s="19" t="n"/>
-      <c r="L2" s="19" t="n"/>
-      <c r="M2" s="19" t="n"/>
-      <c r="N2" s="19" t="n"/>
-      <c r="O2" s="19" t="n"/>
-      <c r="P2" s="20" t="n"/>
-      <c r="Q2" s="21" t="n"/>
-    </row>
-    <row r="3"/>
+      <c r="B2" s="26" t="n"/>
+      <c r="C2" s="26" t="n"/>
+      <c r="D2" s="26" t="n"/>
+      <c r="E2" s="26" t="n"/>
+      <c r="F2" s="26" t="n"/>
+      <c r="G2" s="26" t="n"/>
+      <c r="H2" s="26" t="n"/>
+      <c r="I2" s="26" t="n"/>
+      <c r="J2" s="26" t="n"/>
+      <c r="K2" s="26" t="n"/>
+      <c r="L2" s="26" t="n"/>
+      <c r="M2" s="26" t="n"/>
+      <c r="N2" s="26" t="n"/>
+      <c r="O2" s="26" t="n"/>
+      <c r="P2" s="27" t="n"/>
+      <c r="Q2" s="28" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n"/>
+      <c r="O3" s="4" t="n"/>
+      <c r="P3" s="4" t="n"/>
+      <c r="Q3" s="4" t="n"/>
+    </row>
     <row r="4">
-      <c r="A4" s="22" t="inlineStr">
-        <is>
-          <t>Empresa / Área</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="n"/>
-      <c r="C4" s="9" t="n"/>
-      <c r="D4" s="9" t="n"/>
-      <c r="F4" s="22" t="inlineStr">
-        <is>
-          <t>Año</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="n">
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t>EMPRESA / ÁREA</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="29" t="inlineStr">
+        <is>
+          <t>AÑO</t>
+        </is>
+      </c>
+      <c r="G4" s="17" t="n">
         <v>2026</v>
       </c>
-    </row>
-    <row r="5"/>
-    <row r="6"/>
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="4" t="n"/>
+      <c r="O4" s="4" t="n"/>
+      <c r="P4" s="4" t="n"/>
+      <c r="Q4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="n"/>
+      <c r="P5" s="4" t="n"/>
+      <c r="Q5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="4" t="n"/>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n"/>
+      <c r="P6" s="4" t="n"/>
+      <c r="Q6" s="4" t="n"/>
+    </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="23" t="inlineStr">
-        <is>
-          <t>Concepto</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>Ene</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
-        <is>
-          <t>Feb</t>
-        </is>
-      </c>
-      <c r="D7" s="23" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="E7" s="23" t="inlineStr">
-        <is>
-          <t>Abr</t>
-        </is>
-      </c>
-      <c r="F7" s="23" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="G7" s="23" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="H7" s="23" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="I7" s="23" t="inlineStr">
-        <is>
-          <t>Ago</t>
-        </is>
-      </c>
-      <c r="J7" s="23" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="K7" s="23" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="L7" s="23" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="M7" s="23" t="inlineStr">
-        <is>
-          <t>Dic</t>
-        </is>
-      </c>
-      <c r="N7" s="23" t="inlineStr">
-        <is>
-          <t>Presup. anual</t>
-        </is>
-      </c>
-      <c r="O7" s="23" t="inlineStr">
-        <is>
-          <t>Real anual</t>
-        </is>
-      </c>
-      <c r="P7" s="23" t="inlineStr">
-        <is>
-          <t>Variación</t>
-        </is>
-      </c>
-      <c r="Q7" s="23" t="inlineStr">
-        <is>
-          <t>% ejec.</t>
+      <c r="A7" s="30" t="inlineStr">
+        <is>
+          <t>CONCEPTO</t>
+        </is>
+      </c>
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>ENE</t>
+        </is>
+      </c>
+      <c r="C7" s="30" t="inlineStr">
+        <is>
+          <t>FEB</t>
+        </is>
+      </c>
+      <c r="D7" s="30" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="E7" s="30" t="inlineStr">
+        <is>
+          <t>ABR</t>
+        </is>
+      </c>
+      <c r="F7" s="30" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+      <c r="G7" s="30" t="inlineStr">
+        <is>
+          <t>JUN</t>
+        </is>
+      </c>
+      <c r="H7" s="30" t="inlineStr">
+        <is>
+          <t>JUL</t>
+        </is>
+      </c>
+      <c r="I7" s="30" t="inlineStr">
+        <is>
+          <t>AGO</t>
+        </is>
+      </c>
+      <c r="J7" s="30" t="inlineStr">
+        <is>
+          <t>SEP</t>
+        </is>
+      </c>
+      <c r="K7" s="30" t="inlineStr">
+        <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="L7" s="30" t="inlineStr">
+        <is>
+          <t>NOV</t>
+        </is>
+      </c>
+      <c r="M7" s="30" t="inlineStr">
+        <is>
+          <t>DIC</t>
+        </is>
+      </c>
+      <c r="N7" s="30" t="inlineStr">
+        <is>
+          <t>PRESUP. ANUAL</t>
+        </is>
+      </c>
+      <c r="O7" s="30" t="inlineStr">
+        <is>
+          <t>REAL ANUAL</t>
+        </is>
+      </c>
+      <c r="P7" s="30" t="inlineStr">
+        <is>
+          <t>VARIACIÓN</t>
+        </is>
+      </c>
+      <c r="Q7" s="30" t="inlineStr">
+        <is>
+          <t>% EJEC.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
-        <is>
-          <t>Ventas - Presup.</t>
-        </is>
-      </c>
-      <c r="B8" s="25" t="n"/>
-      <c r="C8" s="25" t="n"/>
-      <c r="D8" s="25" t="n"/>
-      <c r="E8" s="25" t="n"/>
-      <c r="F8" s="25" t="n"/>
-      <c r="G8" s="25" t="n"/>
-      <c r="H8" s="25" t="n"/>
-      <c r="I8" s="25" t="n"/>
-      <c r="J8" s="25" t="n"/>
-      <c r="K8" s="25" t="n"/>
-      <c r="L8" s="25" t="n"/>
-      <c r="M8" s="25" t="n"/>
-      <c r="N8" s="26">
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>VENTAS - PRESUP.</t>
+        </is>
+      </c>
+      <c r="B8" s="32" t="n"/>
+      <c r="C8" s="32" t="n"/>
+      <c r="D8" s="32" t="n"/>
+      <c r="E8" s="32" t="n"/>
+      <c r="F8" s="32" t="n"/>
+      <c r="G8" s="32" t="n"/>
+      <c r="H8" s="32" t="n"/>
+      <c r="I8" s="32" t="n"/>
+      <c r="J8" s="32" t="n"/>
+      <c r="K8" s="32" t="n"/>
+      <c r="L8" s="32" t="n"/>
+      <c r="M8" s="32" t="n"/>
+      <c r="N8" s="33">
         <f>SUM(B8:M8)</f>
         <v/>
       </c>
-      <c r="O8" s="26">
+      <c r="O8" s="33">
         <f>SUM(B9:M9)</f>
         <v/>
       </c>
-      <c r="P8" s="26">
+      <c r="P8" s="33">
         <f>O8-N8</f>
         <v/>
       </c>
-      <c r="Q8" s="27">
+      <c r="Q8" s="34">
         <f>IF(N8=0,"",O8/N8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="28" t="inlineStr">
-        <is>
-          <t>Ventas - Real</t>
-        </is>
-      </c>
-      <c r="B9" s="25" t="n"/>
-      <c r="C9" s="25" t="n"/>
-      <c r="D9" s="25" t="n"/>
-      <c r="E9" s="25" t="n"/>
-      <c r="F9" s="25" t="n"/>
-      <c r="G9" s="25" t="n"/>
-      <c r="H9" s="25" t="n"/>
-      <c r="I9" s="25" t="n"/>
-      <c r="J9" s="25" t="n"/>
-      <c r="K9" s="25" t="n"/>
-      <c r="L9" s="25" t="n"/>
-      <c r="M9" s="25" t="n"/>
+      <c r="A9" s="35" t="inlineStr">
+        <is>
+          <t>VENTAS - REAL</t>
+        </is>
+      </c>
+      <c r="B9" s="32" t="n"/>
+      <c r="C9" s="32" t="n"/>
+      <c r="D9" s="32" t="n"/>
+      <c r="E9" s="32" t="n"/>
+      <c r="F9" s="32" t="n"/>
+      <c r="G9" s="32" t="n"/>
+      <c r="H9" s="32" t="n"/>
+      <c r="I9" s="32" t="n"/>
+      <c r="J9" s="32" t="n"/>
+      <c r="K9" s="32" t="n"/>
+      <c r="L9" s="32" t="n"/>
+      <c r="M9" s="32" t="n"/>
+      <c r="N9" s="4" t="n"/>
+      <c r="O9" s="4" t="n"/>
+      <c r="P9" s="4" t="n"/>
+      <c r="Q9" s="4" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
-        <is>
-          <t>Costo de ventas - Presup.</t>
-        </is>
-      </c>
-      <c r="B10" s="25" t="n"/>
-      <c r="C10" s="25" t="n"/>
-      <c r="D10" s="25" t="n"/>
-      <c r="E10" s="25" t="n"/>
-      <c r="F10" s="25" t="n"/>
-      <c r="G10" s="25" t="n"/>
-      <c r="H10" s="25" t="n"/>
-      <c r="I10" s="25" t="n"/>
-      <c r="J10" s="25" t="n"/>
-      <c r="K10" s="25" t="n"/>
-      <c r="L10" s="25" t="n"/>
-      <c r="M10" s="25" t="n"/>
-      <c r="N10" s="26">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>COSTO DE VENTAS - PRESUP.</t>
+        </is>
+      </c>
+      <c r="B10" s="32" t="n"/>
+      <c r="C10" s="32" t="n"/>
+      <c r="D10" s="32" t="n"/>
+      <c r="E10" s="32" t="n"/>
+      <c r="F10" s="32" t="n"/>
+      <c r="G10" s="32" t="n"/>
+      <c r="H10" s="32" t="n"/>
+      <c r="I10" s="32" t="n"/>
+      <c r="J10" s="32" t="n"/>
+      <c r="K10" s="32" t="n"/>
+      <c r="L10" s="32" t="n"/>
+      <c r="M10" s="32" t="n"/>
+      <c r="N10" s="33">
         <f>SUM(B10:M10)</f>
         <v/>
       </c>
-      <c r="O10" s="26">
+      <c r="O10" s="33">
         <f>SUM(B11:M11)</f>
         <v/>
       </c>
-      <c r="P10" s="26">
+      <c r="P10" s="33">
         <f>O10-N10</f>
         <v/>
       </c>
-      <c r="Q10" s="27">
+      <c r="Q10" s="34">
         <f>IF(N10=0,"",O10/N10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="inlineStr">
-        <is>
-          <t>Costo de ventas - Real</t>
-        </is>
-      </c>
-      <c r="B11" s="25" t="n"/>
-      <c r="C11" s="25" t="n"/>
-      <c r="D11" s="25" t="n"/>
-      <c r="E11" s="25" t="n"/>
-      <c r="F11" s="25" t="n"/>
-      <c r="G11" s="25" t="n"/>
-      <c r="H11" s="25" t="n"/>
-      <c r="I11" s="25" t="n"/>
-      <c r="J11" s="25" t="n"/>
-      <c r="K11" s="25" t="n"/>
-      <c r="L11" s="25" t="n"/>
-      <c r="M11" s="25" t="n"/>
+      <c r="A11" s="35" t="inlineStr">
+        <is>
+          <t>COSTO DE VENTAS - REAL</t>
+        </is>
+      </c>
+      <c r="B11" s="32" t="n"/>
+      <c r="C11" s="32" t="n"/>
+      <c r="D11" s="32" t="n"/>
+      <c r="E11" s="32" t="n"/>
+      <c r="F11" s="32" t="n"/>
+      <c r="G11" s="32" t="n"/>
+      <c r="H11" s="32" t="n"/>
+      <c r="I11" s="32" t="n"/>
+      <c r="J11" s="32" t="n"/>
+      <c r="K11" s="32" t="n"/>
+      <c r="L11" s="32" t="n"/>
+      <c r="M11" s="32" t="n"/>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="n"/>
+      <c r="P11" s="4" t="n"/>
+      <c r="Q11" s="4" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="inlineStr">
-        <is>
-          <t>Sueldos y salarios - Presup.</t>
-        </is>
-      </c>
-      <c r="B12" s="25" t="n"/>
-      <c r="C12" s="25" t="n"/>
-      <c r="D12" s="25" t="n"/>
-      <c r="E12" s="25" t="n"/>
-      <c r="F12" s="25" t="n"/>
-      <c r="G12" s="25" t="n"/>
-      <c r="H12" s="25" t="n"/>
-      <c r="I12" s="25" t="n"/>
-      <c r="J12" s="25" t="n"/>
-      <c r="K12" s="25" t="n"/>
-      <c r="L12" s="25" t="n"/>
-      <c r="M12" s="25" t="n"/>
-      <c r="N12" s="26">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>SUELDOS Y SALARIOS - PRESUP.</t>
+        </is>
+      </c>
+      <c r="B12" s="32" t="n"/>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="32" t="n"/>
+      <c r="E12" s="32" t="n"/>
+      <c r="F12" s="32" t="n"/>
+      <c r="G12" s="32" t="n"/>
+      <c r="H12" s="32" t="n"/>
+      <c r="I12" s="32" t="n"/>
+      <c r="J12" s="32" t="n"/>
+      <c r="K12" s="32" t="n"/>
+      <c r="L12" s="32" t="n"/>
+      <c r="M12" s="32" t="n"/>
+      <c r="N12" s="33">
         <f>SUM(B12:M12)</f>
         <v/>
       </c>
-      <c r="O12" s="26">
+      <c r="O12" s="33">
         <f>SUM(B13:M13)</f>
         <v/>
       </c>
-      <c r="P12" s="26">
+      <c r="P12" s="33">
         <f>O12-N12</f>
         <v/>
       </c>
-      <c r="Q12" s="27">
+      <c r="Q12" s="34">
         <f>IF(N12=0,"",O12/N12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="28" t="inlineStr">
-        <is>
-          <t>Sueldos y salarios - Real</t>
-        </is>
-      </c>
-      <c r="B13" s="25" t="n"/>
-      <c r="C13" s="25" t="n"/>
-      <c r="D13" s="25" t="n"/>
-      <c r="E13" s="25" t="n"/>
-      <c r="F13" s="25" t="n"/>
-      <c r="G13" s="25" t="n"/>
-      <c r="H13" s="25" t="n"/>
-      <c r="I13" s="25" t="n"/>
-      <c r="J13" s="25" t="n"/>
-      <c r="K13" s="25" t="n"/>
-      <c r="L13" s="25" t="n"/>
-      <c r="M13" s="25" t="n"/>
+      <c r="A13" s="35" t="inlineStr">
+        <is>
+          <t>SUELDOS Y SALARIOS - REAL</t>
+        </is>
+      </c>
+      <c r="B13" s="32" t="n"/>
+      <c r="C13" s="32" t="n"/>
+      <c r="D13" s="32" t="n"/>
+      <c r="E13" s="32" t="n"/>
+      <c r="F13" s="32" t="n"/>
+      <c r="G13" s="32" t="n"/>
+      <c r="H13" s="32" t="n"/>
+      <c r="I13" s="32" t="n"/>
+      <c r="J13" s="32" t="n"/>
+      <c r="K13" s="32" t="n"/>
+      <c r="L13" s="32" t="n"/>
+      <c r="M13" s="32" t="n"/>
+      <c r="N13" s="4" t="n"/>
+      <c r="O13" s="4" t="n"/>
+      <c r="P13" s="4" t="n"/>
+      <c r="Q13" s="4" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="24" t="inlineStr">
-        <is>
-          <t>Renta - Presup.</t>
-        </is>
-      </c>
-      <c r="B14" s="25" t="n"/>
-      <c r="C14" s="25" t="n"/>
-      <c r="D14" s="25" t="n"/>
-      <c r="E14" s="25" t="n"/>
-      <c r="F14" s="25" t="n"/>
-      <c r="G14" s="25" t="n"/>
-      <c r="H14" s="25" t="n"/>
-      <c r="I14" s="25" t="n"/>
-      <c r="J14" s="25" t="n"/>
-      <c r="K14" s="25" t="n"/>
-      <c r="L14" s="25" t="n"/>
-      <c r="M14" s="25" t="n"/>
-      <c r="N14" s="26">
+      <c r="A14" s="31" t="inlineStr">
+        <is>
+          <t>RENTA - PRESUP.</t>
+        </is>
+      </c>
+      <c r="B14" s="32" t="n"/>
+      <c r="C14" s="32" t="n"/>
+      <c r="D14" s="32" t="n"/>
+      <c r="E14" s="32" t="n"/>
+      <c r="F14" s="32" t="n"/>
+      <c r="G14" s="32" t="n"/>
+      <c r="H14" s="32" t="n"/>
+      <c r="I14" s="32" t="n"/>
+      <c r="J14" s="32" t="n"/>
+      <c r="K14" s="32" t="n"/>
+      <c r="L14" s="32" t="n"/>
+      <c r="M14" s="32" t="n"/>
+      <c r="N14" s="33">
         <f>SUM(B14:M14)</f>
         <v/>
       </c>
-      <c r="O14" s="26">
+      <c r="O14" s="33">
         <f>SUM(B15:M15)</f>
         <v/>
       </c>
-      <c r="P14" s="26">
+      <c r="P14" s="33">
         <f>O14-N14</f>
         <v/>
       </c>
-      <c r="Q14" s="27">
+      <c r="Q14" s="34">
         <f>IF(N14=0,"",O14/N14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="28" t="inlineStr">
-        <is>
-          <t>Renta - Real</t>
-        </is>
-      </c>
-      <c r="B15" s="25" t="n"/>
-      <c r="C15" s="25" t="n"/>
-      <c r="D15" s="25" t="n"/>
-      <c r="E15" s="25" t="n"/>
-      <c r="F15" s="25" t="n"/>
-      <c r="G15" s="25" t="n"/>
-      <c r="H15" s="25" t="n"/>
-      <c r="I15" s="25" t="n"/>
-      <c r="J15" s="25" t="n"/>
-      <c r="K15" s="25" t="n"/>
-      <c r="L15" s="25" t="n"/>
-      <c r="M15" s="25" t="n"/>
+      <c r="A15" s="35" t="inlineStr">
+        <is>
+          <t>RENTA - REAL</t>
+        </is>
+      </c>
+      <c r="B15" s="32" t="n"/>
+      <c r="C15" s="32" t="n"/>
+      <c r="D15" s="32" t="n"/>
+      <c r="E15" s="32" t="n"/>
+      <c r="F15" s="32" t="n"/>
+      <c r="G15" s="32" t="n"/>
+      <c r="H15" s="32" t="n"/>
+      <c r="I15" s="32" t="n"/>
+      <c r="J15" s="32" t="n"/>
+      <c r="K15" s="32" t="n"/>
+      <c r="L15" s="32" t="n"/>
+      <c r="M15" s="32" t="n"/>
+      <c r="N15" s="4" t="n"/>
+      <c r="O15" s="4" t="n"/>
+      <c r="P15" s="4" t="n"/>
+      <c r="Q15" s="4" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="inlineStr">
-        <is>
-          <t>Servicios - Presup.</t>
-        </is>
-      </c>
-      <c r="B16" s="25" t="n"/>
-      <c r="C16" s="25" t="n"/>
-      <c r="D16" s="25" t="n"/>
-      <c r="E16" s="25" t="n"/>
-      <c r="F16" s="25" t="n"/>
-      <c r="G16" s="25" t="n"/>
-      <c r="H16" s="25" t="n"/>
-      <c r="I16" s="25" t="n"/>
-      <c r="J16" s="25" t="n"/>
-      <c r="K16" s="25" t="n"/>
-      <c r="L16" s="25" t="n"/>
-      <c r="M16" s="25" t="n"/>
-      <c r="N16" s="26">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>SERVICIOS - PRESUP.</t>
+        </is>
+      </c>
+      <c r="B16" s="32" t="n"/>
+      <c r="C16" s="32" t="n"/>
+      <c r="D16" s="32" t="n"/>
+      <c r="E16" s="32" t="n"/>
+      <c r="F16" s="32" t="n"/>
+      <c r="G16" s="32" t="n"/>
+      <c r="H16" s="32" t="n"/>
+      <c r="I16" s="32" t="n"/>
+      <c r="J16" s="32" t="n"/>
+      <c r="K16" s="32" t="n"/>
+      <c r="L16" s="32" t="n"/>
+      <c r="M16" s="32" t="n"/>
+      <c r="N16" s="33">
         <f>SUM(B16:M16)</f>
         <v/>
       </c>
-      <c r="O16" s="26">
+      <c r="O16" s="33">
         <f>SUM(B17:M17)</f>
         <v/>
       </c>
-      <c r="P16" s="26">
+      <c r="P16" s="33">
         <f>O16-N16</f>
         <v/>
       </c>
-      <c r="Q16" s="27">
+      <c r="Q16" s="34">
         <f>IF(N16=0,"",O16/N16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="28" t="inlineStr">
-        <is>
-          <t>Servicios - Real</t>
-        </is>
-      </c>
-      <c r="B17" s="25" t="n"/>
-      <c r="C17" s="25" t="n"/>
-      <c r="D17" s="25" t="n"/>
-      <c r="E17" s="25" t="n"/>
-      <c r="F17" s="25" t="n"/>
-      <c r="G17" s="25" t="n"/>
-      <c r="H17" s="25" t="n"/>
-      <c r="I17" s="25" t="n"/>
-      <c r="J17" s="25" t="n"/>
-      <c r="K17" s="25" t="n"/>
-      <c r="L17" s="25" t="n"/>
-      <c r="M17" s="25" t="n"/>
+      <c r="A17" s="35" t="inlineStr">
+        <is>
+          <t>SERVICIOS - REAL</t>
+        </is>
+      </c>
+      <c r="B17" s="32" t="n"/>
+      <c r="C17" s="32" t="n"/>
+      <c r="D17" s="32" t="n"/>
+      <c r="E17" s="32" t="n"/>
+      <c r="F17" s="32" t="n"/>
+      <c r="G17" s="32" t="n"/>
+      <c r="H17" s="32" t="n"/>
+      <c r="I17" s="32" t="n"/>
+      <c r="J17" s="32" t="n"/>
+      <c r="K17" s="32" t="n"/>
+      <c r="L17" s="32" t="n"/>
+      <c r="M17" s="32" t="n"/>
+      <c r="N17" s="4" t="n"/>
+      <c r="O17" s="4" t="n"/>
+      <c r="P17" s="4" t="n"/>
+      <c r="Q17" s="4" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="inlineStr">
-        <is>
-          <t>Publicidad y mercadotecnia - Presup.</t>
-        </is>
-      </c>
-      <c r="B18" s="25" t="n"/>
-      <c r="C18" s="25" t="n"/>
-      <c r="D18" s="25" t="n"/>
-      <c r="E18" s="25" t="n"/>
-      <c r="F18" s="25" t="n"/>
-      <c r="G18" s="25" t="n"/>
-      <c r="H18" s="25" t="n"/>
-      <c r="I18" s="25" t="n"/>
-      <c r="J18" s="25" t="n"/>
-      <c r="K18" s="25" t="n"/>
-      <c r="L18" s="25" t="n"/>
-      <c r="M18" s="25" t="n"/>
-      <c r="N18" s="26">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>PUBLICIDAD Y MERCADOTECNIA - PRESUP.</t>
+        </is>
+      </c>
+      <c r="B18" s="32" t="n"/>
+      <c r="C18" s="32" t="n"/>
+      <c r="D18" s="32" t="n"/>
+      <c r="E18" s="32" t="n"/>
+      <c r="F18" s="32" t="n"/>
+      <c r="G18" s="32" t="n"/>
+      <c r="H18" s="32" t="n"/>
+      <c r="I18" s="32" t="n"/>
+      <c r="J18" s="32" t="n"/>
+      <c r="K18" s="32" t="n"/>
+      <c r="L18" s="32" t="n"/>
+      <c r="M18" s="32" t="n"/>
+      <c r="N18" s="33">
         <f>SUM(B18:M18)</f>
         <v/>
       </c>
-      <c r="O18" s="26">
+      <c r="O18" s="33">
         <f>SUM(B19:M19)</f>
         <v/>
       </c>
-      <c r="P18" s="26">
+      <c r="P18" s="33">
         <f>O18-N18</f>
         <v/>
       </c>
-      <c r="Q18" s="27">
+      <c r="Q18" s="34">
         <f>IF(N18=0,"",O18/N18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="28" t="inlineStr">
-        <is>
-          <t>Publicidad y mercadotecnia - Real</t>
-        </is>
-      </c>
-      <c r="B19" s="25" t="n"/>
-      <c r="C19" s="25" t="n"/>
-      <c r="D19" s="25" t="n"/>
-      <c r="E19" s="25" t="n"/>
-      <c r="F19" s="25" t="n"/>
-      <c r="G19" s="25" t="n"/>
-      <c r="H19" s="25" t="n"/>
-      <c r="I19" s="25" t="n"/>
-      <c r="J19" s="25" t="n"/>
-      <c r="K19" s="25" t="n"/>
-      <c r="L19" s="25" t="n"/>
-      <c r="M19" s="25" t="n"/>
+      <c r="A19" s="35" t="inlineStr">
+        <is>
+          <t>PUBLICIDAD Y MERCADOTECNIA - REAL</t>
+        </is>
+      </c>
+      <c r="B19" s="32" t="n"/>
+      <c r="C19" s="32" t="n"/>
+      <c r="D19" s="32" t="n"/>
+      <c r="E19" s="32" t="n"/>
+      <c r="F19" s="32" t="n"/>
+      <c r="G19" s="32" t="n"/>
+      <c r="H19" s="32" t="n"/>
+      <c r="I19" s="32" t="n"/>
+      <c r="J19" s="32" t="n"/>
+      <c r="K19" s="32" t="n"/>
+      <c r="L19" s="32" t="n"/>
+      <c r="M19" s="32" t="n"/>
+      <c r="N19" s="4" t="n"/>
+      <c r="O19" s="4" t="n"/>
+      <c r="P19" s="4" t="n"/>
+      <c r="Q19" s="4" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="24" t="inlineStr">
-        <is>
-          <t>Mantenimiento - Presup.</t>
-        </is>
-      </c>
-      <c r="B20" s="25" t="n"/>
-      <c r="C20" s="25" t="n"/>
-      <c r="D20" s="25" t="n"/>
-      <c r="E20" s="25" t="n"/>
-      <c r="F20" s="25" t="n"/>
-      <c r="G20" s="25" t="n"/>
-      <c r="H20" s="25" t="n"/>
-      <c r="I20" s="25" t="n"/>
-      <c r="J20" s="25" t="n"/>
-      <c r="K20" s="25" t="n"/>
-      <c r="L20" s="25" t="n"/>
-      <c r="M20" s="25" t="n"/>
-      <c r="N20" s="26">
+      <c r="A20" s="31" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO - PRESUP.</t>
+        </is>
+      </c>
+      <c r="B20" s="32" t="n"/>
+      <c r="C20" s="32" t="n"/>
+      <c r="D20" s="32" t="n"/>
+      <c r="E20" s="32" t="n"/>
+      <c r="F20" s="32" t="n"/>
+      <c r="G20" s="32" t="n"/>
+      <c r="H20" s="32" t="n"/>
+      <c r="I20" s="32" t="n"/>
+      <c r="J20" s="32" t="n"/>
+      <c r="K20" s="32" t="n"/>
+      <c r="L20" s="32" t="n"/>
+      <c r="M20" s="32" t="n"/>
+      <c r="N20" s="33">
         <f>SUM(B20:M20)</f>
         <v/>
       </c>
-      <c r="O20" s="26">
+      <c r="O20" s="33">
         <f>SUM(B21:M21)</f>
         <v/>
       </c>
-      <c r="P20" s="26">
+      <c r="P20" s="33">
         <f>O20-N20</f>
         <v/>
       </c>
-      <c r="Q20" s="27">
+      <c r="Q20" s="34">
         <f>IF(N20=0,"",O20/N20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="28" t="inlineStr">
-        <is>
-          <t>Mantenimiento - Real</t>
-        </is>
-      </c>
-      <c r="B21" s="25" t="n"/>
-      <c r="C21" s="25" t="n"/>
-      <c r="D21" s="25" t="n"/>
-      <c r="E21" s="25" t="n"/>
-      <c r="F21" s="25" t="n"/>
-      <c r="G21" s="25" t="n"/>
-      <c r="H21" s="25" t="n"/>
-      <c r="I21" s="25" t="n"/>
-      <c r="J21" s="25" t="n"/>
-      <c r="K21" s="25" t="n"/>
-      <c r="L21" s="25" t="n"/>
-      <c r="M21" s="25" t="n"/>
+      <c r="A21" s="35" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO - REAL</t>
+        </is>
+      </c>
+      <c r="B21" s="32" t="n"/>
+      <c r="C21" s="32" t="n"/>
+      <c r="D21" s="32" t="n"/>
+      <c r="E21" s="32" t="n"/>
+      <c r="F21" s="32" t="n"/>
+      <c r="G21" s="32" t="n"/>
+      <c r="H21" s="32" t="n"/>
+      <c r="I21" s="32" t="n"/>
+      <c r="J21" s="32" t="n"/>
+      <c r="K21" s="32" t="n"/>
+      <c r="L21" s="32" t="n"/>
+      <c r="M21" s="32" t="n"/>
+      <c r="N21" s="4" t="n"/>
+      <c r="O21" s="4" t="n"/>
+      <c r="P21" s="4" t="n"/>
+      <c r="Q21" s="4" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="24" t="inlineStr">
-        <is>
-          <t>Papelería y oficina - Presup.</t>
-        </is>
-      </c>
-      <c r="B22" s="25" t="n"/>
-      <c r="C22" s="25" t="n"/>
-      <c r="D22" s="25" t="n"/>
-      <c r="E22" s="25" t="n"/>
-      <c r="F22" s="25" t="n"/>
-      <c r="G22" s="25" t="n"/>
-      <c r="H22" s="25" t="n"/>
-      <c r="I22" s="25" t="n"/>
-      <c r="J22" s="25" t="n"/>
-      <c r="K22" s="25" t="n"/>
-      <c r="L22" s="25" t="n"/>
-      <c r="M22" s="25" t="n"/>
-      <c r="N22" s="26">
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>PAPELERÍA Y OFICINA - PRESUP.</t>
+        </is>
+      </c>
+      <c r="B22" s="32" t="n"/>
+      <c r="C22" s="32" t="n"/>
+      <c r="D22" s="32" t="n"/>
+      <c r="E22" s="32" t="n"/>
+      <c r="F22" s="32" t="n"/>
+      <c r="G22" s="32" t="n"/>
+      <c r="H22" s="32" t="n"/>
+      <c r="I22" s="32" t="n"/>
+      <c r="J22" s="32" t="n"/>
+      <c r="K22" s="32" t="n"/>
+      <c r="L22" s="32" t="n"/>
+      <c r="M22" s="32" t="n"/>
+      <c r="N22" s="33">
         <f>SUM(B22:M22)</f>
         <v/>
       </c>
-      <c r="O22" s="26">
+      <c r="O22" s="33">
         <f>SUM(B23:M23)</f>
         <v/>
       </c>
-      <c r="P22" s="26">
+      <c r="P22" s="33">
         <f>O22-N22</f>
         <v/>
       </c>
-      <c r="Q22" s="27">
+      <c r="Q22" s="34">
         <f>IF(N22=0,"",O22/N22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="28" t="inlineStr">
-        <is>
-          <t>Papelería y oficina - Real</t>
-        </is>
-      </c>
-      <c r="B23" s="25" t="n"/>
-      <c r="C23" s="25" t="n"/>
-      <c r="D23" s="25" t="n"/>
-      <c r="E23" s="25" t="n"/>
-      <c r="F23" s="25" t="n"/>
-      <c r="G23" s="25" t="n"/>
-      <c r="H23" s="25" t="n"/>
-      <c r="I23" s="25" t="n"/>
-      <c r="J23" s="25" t="n"/>
-      <c r="K23" s="25" t="n"/>
-      <c r="L23" s="25" t="n"/>
-      <c r="M23" s="25" t="n"/>
+      <c r="A23" s="35" t="inlineStr">
+        <is>
+          <t>PAPELERÍA Y OFICINA - REAL</t>
+        </is>
+      </c>
+      <c r="B23" s="32" t="n"/>
+      <c r="C23" s="32" t="n"/>
+      <c r="D23" s="32" t="n"/>
+      <c r="E23" s="32" t="n"/>
+      <c r="F23" s="32" t="n"/>
+      <c r="G23" s="32" t="n"/>
+      <c r="H23" s="32" t="n"/>
+      <c r="I23" s="32" t="n"/>
+      <c r="J23" s="32" t="n"/>
+      <c r="K23" s="32" t="n"/>
+      <c r="L23" s="32" t="n"/>
+      <c r="M23" s="32" t="n"/>
+      <c r="N23" s="4" t="n"/>
+      <c r="O23" s="4" t="n"/>
+      <c r="P23" s="4" t="n"/>
+      <c r="Q23" s="4" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="24" t="inlineStr">
-        <is>
-          <t>Impuestos y derechos - Presup.</t>
-        </is>
-      </c>
-      <c r="B24" s="25" t="n"/>
-      <c r="C24" s="25" t="n"/>
-      <c r="D24" s="25" t="n"/>
-      <c r="E24" s="25" t="n"/>
-      <c r="F24" s="25" t="n"/>
-      <c r="G24" s="25" t="n"/>
-      <c r="H24" s="25" t="n"/>
-      <c r="I24" s="25" t="n"/>
-      <c r="J24" s="25" t="n"/>
-      <c r="K24" s="25" t="n"/>
-      <c r="L24" s="25" t="n"/>
-      <c r="M24" s="25" t="n"/>
-      <c r="N24" s="26">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>IMPUESTOS Y DERECHOS - PRESUP.</t>
+        </is>
+      </c>
+      <c r="B24" s="32" t="n"/>
+      <c r="C24" s="32" t="n"/>
+      <c r="D24" s="32" t="n"/>
+      <c r="E24" s="32" t="n"/>
+      <c r="F24" s="32" t="n"/>
+      <c r="G24" s="32" t="n"/>
+      <c r="H24" s="32" t="n"/>
+      <c r="I24" s="32" t="n"/>
+      <c r="J24" s="32" t="n"/>
+      <c r="K24" s="32" t="n"/>
+      <c r="L24" s="32" t="n"/>
+      <c r="M24" s="32" t="n"/>
+      <c r="N24" s="33">
         <f>SUM(B24:M24)</f>
         <v/>
       </c>
-      <c r="O24" s="26">
+      <c r="O24" s="33">
         <f>SUM(B25:M25)</f>
         <v/>
       </c>
-      <c r="P24" s="26">
+      <c r="P24" s="33">
         <f>O24-N24</f>
         <v/>
       </c>
-      <c r="Q24" s="27">
+      <c r="Q24" s="34">
         <f>IF(N24=0,"",O24/N24)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="28" t="inlineStr">
-        <is>
-          <t>Impuestos y derechos - Real</t>
-        </is>
-      </c>
-      <c r="B25" s="25" t="n"/>
-      <c r="C25" s="25" t="n"/>
-      <c r="D25" s="25" t="n"/>
-      <c r="E25" s="25" t="n"/>
-      <c r="F25" s="25" t="n"/>
-      <c r="G25" s="25" t="n"/>
-      <c r="H25" s="25" t="n"/>
-      <c r="I25" s="25" t="n"/>
-      <c r="J25" s="25" t="n"/>
-      <c r="K25" s="25" t="n"/>
-      <c r="L25" s="25" t="n"/>
-      <c r="M25" s="25" t="n"/>
+      <c r="A25" s="35" t="inlineStr">
+        <is>
+          <t>IMPUESTOS Y DERECHOS - REAL</t>
+        </is>
+      </c>
+      <c r="B25" s="32" t="n"/>
+      <c r="C25" s="32" t="n"/>
+      <c r="D25" s="32" t="n"/>
+      <c r="E25" s="32" t="n"/>
+      <c r="F25" s="32" t="n"/>
+      <c r="G25" s="32" t="n"/>
+      <c r="H25" s="32" t="n"/>
+      <c r="I25" s="32" t="n"/>
+      <c r="J25" s="32" t="n"/>
+      <c r="K25" s="32" t="n"/>
+      <c r="L25" s="32" t="n"/>
+      <c r="M25" s="32" t="n"/>
+      <c r="N25" s="4" t="n"/>
+      <c r="O25" s="4" t="n"/>
+      <c r="P25" s="4" t="n"/>
+      <c r="Q25" s="4" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="24" t="inlineStr">
-        <is>
-          <t>Otros gastos - Presup.</t>
-        </is>
-      </c>
-      <c r="B26" s="25" t="n"/>
-      <c r="C26" s="25" t="n"/>
-      <c r="D26" s="25" t="n"/>
-      <c r="E26" s="25" t="n"/>
-      <c r="F26" s="25" t="n"/>
-      <c r="G26" s="25" t="n"/>
-      <c r="H26" s="25" t="n"/>
-      <c r="I26" s="25" t="n"/>
-      <c r="J26" s="25" t="n"/>
-      <c r="K26" s="25" t="n"/>
-      <c r="L26" s="25" t="n"/>
-      <c r="M26" s="25" t="n"/>
-      <c r="N26" s="26">
+      <c r="A26" s="31" t="inlineStr">
+        <is>
+          <t>OTROS GASTOS - PRESUP.</t>
+        </is>
+      </c>
+      <c r="B26" s="32" t="n"/>
+      <c r="C26" s="32" t="n"/>
+      <c r="D26" s="32" t="n"/>
+      <c r="E26" s="32" t="n"/>
+      <c r="F26" s="32" t="n"/>
+      <c r="G26" s="32" t="n"/>
+      <c r="H26" s="32" t="n"/>
+      <c r="I26" s="32" t="n"/>
+      <c r="J26" s="32" t="n"/>
+      <c r="K26" s="32" t="n"/>
+      <c r="L26" s="32" t="n"/>
+      <c r="M26" s="32" t="n"/>
+      <c r="N26" s="33">
         <f>SUM(B26:M26)</f>
         <v/>
       </c>
-      <c r="O26" s="26">
+      <c r="O26" s="33">
         <f>SUM(B27:M27)</f>
         <v/>
       </c>
-      <c r="P26" s="26">
+      <c r="P26" s="33">
         <f>O26-N26</f>
         <v/>
       </c>
-      <c r="Q26" s="27">
+      <c r="Q26" s="34">
         <f>IF(N26=0,"",O26/N26)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="28" t="inlineStr">
-        <is>
-          <t>Otros gastos - Real</t>
-        </is>
-      </c>
-      <c r="B27" s="25" t="n"/>
-      <c r="C27" s="25" t="n"/>
-      <c r="D27" s="25" t="n"/>
-      <c r="E27" s="25" t="n"/>
-      <c r="F27" s="25" t="n"/>
-      <c r="G27" s="25" t="n"/>
-      <c r="H27" s="25" t="n"/>
-      <c r="I27" s="25" t="n"/>
-      <c r="J27" s="25" t="n"/>
-      <c r="K27" s="25" t="n"/>
-      <c r="L27" s="25" t="n"/>
-      <c r="M27" s="25" t="n"/>
+      <c r="A27" s="35" t="inlineStr">
+        <is>
+          <t>OTROS GASTOS - REAL</t>
+        </is>
+      </c>
+      <c r="B27" s="32" t="n"/>
+      <c r="C27" s="32" t="n"/>
+      <c r="D27" s="32" t="n"/>
+      <c r="E27" s="32" t="n"/>
+      <c r="F27" s="32" t="n"/>
+      <c r="G27" s="32" t="n"/>
+      <c r="H27" s="32" t="n"/>
+      <c r="I27" s="32" t="n"/>
+      <c r="J27" s="32" t="n"/>
+      <c r="K27" s="32" t="n"/>
+      <c r="L27" s="32" t="n"/>
+      <c r="M27" s="32" t="n"/>
+      <c r="N27" s="4" t="n"/>
+      <c r="O27" s="4" t="n"/>
+      <c r="P27" s="4" t="n"/>
+      <c r="Q27" s="4" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
@@ -1799,7 +2374,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
@@ -1811,7 +2386,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="44" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>RESUMEN DEL PRESUPUESTO</t>
         </is>
@@ -1822,338 +2397,430 @@
       <c r="E1" s="1" t="n"/>
       <c r="F1" s="1" t="n"/>
       <c r="G1" s="1" t="n"/>
-      <c r="H1" s="16" t="inlineStr">
+      <c r="H1" s="23" t="inlineStr">
         <is>
           <t>INSERTE SU LOGO
 (clic derecho &gt; Insertar imagen)</t>
         </is>
       </c>
-      <c r="I1" s="29" t="n"/>
-      <c r="J1" s="17" t="n"/>
+      <c r="I1" s="36" t="n"/>
+      <c r="J1" s="24" t="n"/>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="25" t="inlineStr">
         <is>
           <t>Presupuestado vs. real por concepto</t>
         </is>
       </c>
-      <c r="B2" s="19" t="n"/>
-      <c r="C2" s="19" t="n"/>
-      <c r="D2" s="19" t="n"/>
-      <c r="E2" s="19" t="n"/>
-      <c r="F2" s="19" t="n"/>
-      <c r="G2" s="19" t="n"/>
-      <c r="H2" s="20" t="n"/>
-      <c r="I2" s="30" t="n"/>
-      <c r="J2" s="21" t="n"/>
-    </row>
-    <row r="3"/>
+      <c r="B2" s="26" t="n"/>
+      <c r="C2" s="26" t="n"/>
+      <c r="D2" s="26" t="n"/>
+      <c r="E2" s="26" t="n"/>
+      <c r="F2" s="26" t="n"/>
+      <c r="G2" s="26" t="n"/>
+      <c r="H2" s="27" t="n"/>
+      <c r="I2" s="37" t="n"/>
+      <c r="J2" s="28" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+    </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="B4" s="31" t="inlineStr">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="38" t="inlineStr">
         <is>
           <t>VENTAS PRESUPUESTADAS</t>
         </is>
       </c>
-      <c r="C4" s="32" t="n"/>
-      <c r="D4" s="31" t="inlineStr">
+      <c r="C4" s="39" t="n"/>
+      <c r="D4" s="38" t="inlineStr">
         <is>
           <t>VENTAS REALES</t>
         </is>
       </c>
-      <c r="E4" s="32" t="n"/>
-      <c r="F4" s="31" t="inlineStr">
+      <c r="E4" s="39" t="n"/>
+      <c r="F4" s="38" t="inlineStr">
         <is>
           <t>GASTO PRESUPUESTADO</t>
         </is>
       </c>
-      <c r="G4" s="32" t="n"/>
-      <c r="H4" s="31" t="inlineStr">
+      <c r="G4" s="39" t="n"/>
+      <c r="H4" s="38" t="inlineStr">
         <is>
           <t>GASTO REAL</t>
         </is>
       </c>
-      <c r="I4" s="32" t="n"/>
+      <c r="I4" s="39" t="n"/>
+      <c r="J4" s="4" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
-      <c r="B5" s="33">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="40">
         <f>C9</f>
         <v/>
       </c>
-      <c r="C5" s="34" t="n"/>
-      <c r="D5" s="33">
+      <c r="C5" s="41" t="n"/>
+      <c r="D5" s="40">
         <f>D9</f>
         <v/>
       </c>
-      <c r="E5" s="34" t="n"/>
-      <c r="F5" s="33">
+      <c r="E5" s="41" t="n"/>
+      <c r="F5" s="40">
         <f>SUM(C10:C18)</f>
         <v/>
       </c>
-      <c r="G5" s="34" t="n"/>
-      <c r="H5" s="33">
+      <c r="G5" s="41" t="n"/>
+      <c r="H5" s="40">
         <f>SUM(D10:D18)</f>
         <v/>
       </c>
-      <c r="I5" s="34" t="n"/>
-    </row>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8" ht="22" customHeight="1">
-      <c r="B8" s="23" t="inlineStr">
-        <is>
-          <t>Concepto</t>
-        </is>
-      </c>
-      <c r="C8" s="23" t="inlineStr">
-        <is>
-          <t>Presupuesto</t>
-        </is>
-      </c>
-      <c r="D8" s="23" t="inlineStr">
-        <is>
-          <t>Real</t>
-        </is>
-      </c>
-      <c r="E8" s="23" t="inlineStr">
-        <is>
-          <t>Variación</t>
-        </is>
-      </c>
-      <c r="F8" s="23" t="inlineStr">
-        <is>
-          <t>% ejec.</t>
-        </is>
-      </c>
+      <c r="I5" s="41" t="n"/>
+      <c r="J5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="n"/>
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="n"/>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="4" t="n"/>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>CONCEPTO</t>
+        </is>
+      </c>
+      <c r="C8" s="30" t="inlineStr">
+        <is>
+          <t>PRESUPUESTO</t>
+        </is>
+      </c>
+      <c r="D8" s="30" t="inlineStr">
+        <is>
+          <t>REAL</t>
+        </is>
+      </c>
+      <c r="E8" s="30" t="inlineStr">
+        <is>
+          <t>VARIACIÓN</t>
+        </is>
+      </c>
+      <c r="F8" s="30" t="inlineStr">
+        <is>
+          <t>% EJEC.</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="4" t="n"/>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="4" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="28" t="inlineStr">
-        <is>
-          <t>Ventas</t>
-        </is>
-      </c>
-      <c r="C9" s="26">
-        <f>Formato!N8</f>
-        <v/>
-      </c>
-      <c r="D9" s="26">
-        <f>Formato!O8</f>
-        <v/>
-      </c>
-      <c r="E9" s="26">
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="35" t="inlineStr">
+        <is>
+          <t>VENTAS</t>
+        </is>
+      </c>
+      <c r="C9" s="33">
+        <f>FORMATO!N8</f>
+        <v/>
+      </c>
+      <c r="D9" s="33">
+        <f>FORMATO!O8</f>
+        <v/>
+      </c>
+      <c r="E9" s="33">
         <f>D9-C9</f>
         <v/>
       </c>
-      <c r="F9" s="27">
+      <c r="F9" s="34">
         <f>IF(C9=0,"",D9/C9)</f>
         <v/>
       </c>
+      <c r="G9" s="4" t="n"/>
+      <c r="H9" s="4" t="n"/>
+      <c r="I9" s="4" t="n"/>
+      <c r="J9" s="4" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="28" t="inlineStr">
-        <is>
-          <t>Costo de ventas</t>
-        </is>
-      </c>
-      <c r="C10" s="26">
-        <f>Formato!N10</f>
-        <v/>
-      </c>
-      <c r="D10" s="26">
-        <f>Formato!O10</f>
-        <v/>
-      </c>
-      <c r="E10" s="26">
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="35" t="inlineStr">
+        <is>
+          <t>COSTO DE VENTAS</t>
+        </is>
+      </c>
+      <c r="C10" s="33">
+        <f>FORMATO!N10</f>
+        <v/>
+      </c>
+      <c r="D10" s="33">
+        <f>FORMATO!O10</f>
+        <v/>
+      </c>
+      <c r="E10" s="33">
         <f>D10-C10</f>
         <v/>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="34">
         <f>IF(C10=0,"",D10/C10)</f>
         <v/>
       </c>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="4" t="n"/>
+      <c r="I10" s="4" t="n"/>
+      <c r="J10" s="4" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="28" t="inlineStr">
-        <is>
-          <t>Sueldos y salarios</t>
-        </is>
-      </c>
-      <c r="C11" s="26">
-        <f>Formato!N12</f>
-        <v/>
-      </c>
-      <c r="D11" s="26">
-        <f>Formato!O12</f>
-        <v/>
-      </c>
-      <c r="E11" s="26">
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>SUELDOS Y SALARIOS</t>
+        </is>
+      </c>
+      <c r="C11" s="33">
+        <f>FORMATO!N12</f>
+        <v/>
+      </c>
+      <c r="D11" s="33">
+        <f>FORMATO!O12</f>
+        <v/>
+      </c>
+      <c r="E11" s="33">
         <f>D11-C11</f>
         <v/>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="34">
         <f>IF(C11=0,"",D11/C11)</f>
         <v/>
       </c>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="4" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="28" t="inlineStr">
-        <is>
-          <t>Renta</t>
-        </is>
-      </c>
-      <c r="C12" s="26">
-        <f>Formato!N14</f>
-        <v/>
-      </c>
-      <c r="D12" s="26">
-        <f>Formato!O14</f>
-        <v/>
-      </c>
-      <c r="E12" s="26">
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="35" t="inlineStr">
+        <is>
+          <t>RENTA</t>
+        </is>
+      </c>
+      <c r="C12" s="33">
+        <f>FORMATO!N14</f>
+        <v/>
+      </c>
+      <c r="D12" s="33">
+        <f>FORMATO!O14</f>
+        <v/>
+      </c>
+      <c r="E12" s="33">
         <f>D12-C12</f>
         <v/>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="34">
         <f>IF(C12=0,"",D12/C12)</f>
         <v/>
       </c>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="n"/>
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="4" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="28" t="inlineStr">
-        <is>
-          <t>Servicios</t>
-        </is>
-      </c>
-      <c r="C13" s="26">
-        <f>Formato!N16</f>
-        <v/>
-      </c>
-      <c r="D13" s="26">
-        <f>Formato!O16</f>
-        <v/>
-      </c>
-      <c r="E13" s="26">
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="35" t="inlineStr">
+        <is>
+          <t>SERVICIOS</t>
+        </is>
+      </c>
+      <c r="C13" s="33">
+        <f>FORMATO!N16</f>
+        <v/>
+      </c>
+      <c r="D13" s="33">
+        <f>FORMATO!O16</f>
+        <v/>
+      </c>
+      <c r="E13" s="33">
         <f>D13-C13</f>
         <v/>
       </c>
-      <c r="F13" s="27">
+      <c r="F13" s="34">
         <f>IF(C13=0,"",D13/C13)</f>
         <v/>
       </c>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="4" t="n"/>
+      <c r="I13" s="4" t="n"/>
+      <c r="J13" s="4" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="28" t="inlineStr">
-        <is>
-          <t>Publicidad y mercadotecnia</t>
-        </is>
-      </c>
-      <c r="C14" s="26">
-        <f>Formato!N18</f>
-        <v/>
-      </c>
-      <c r="D14" s="26">
-        <f>Formato!O18</f>
-        <v/>
-      </c>
-      <c r="E14" s="26">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="35" t="inlineStr">
+        <is>
+          <t>PUBLICIDAD Y MERCADOTECNIA</t>
+        </is>
+      </c>
+      <c r="C14" s="33">
+        <f>FORMATO!N18</f>
+        <v/>
+      </c>
+      <c r="D14" s="33">
+        <f>FORMATO!O18</f>
+        <v/>
+      </c>
+      <c r="E14" s="33">
         <f>D14-C14</f>
         <v/>
       </c>
-      <c r="F14" s="27">
+      <c r="F14" s="34">
         <f>IF(C14=0,"",D14/C14)</f>
         <v/>
       </c>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="n"/>
+      <c r="I14" s="4" t="n"/>
+      <c r="J14" s="4" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="28" t="inlineStr">
-        <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
-      <c r="C15" s="26">
-        <f>Formato!N20</f>
-        <v/>
-      </c>
-      <c r="D15" s="26">
-        <f>Formato!O20</f>
-        <v/>
-      </c>
-      <c r="E15" s="26">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="35" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="C15" s="33">
+        <f>FORMATO!N20</f>
+        <v/>
+      </c>
+      <c r="D15" s="33">
+        <f>FORMATO!O20</f>
+        <v/>
+      </c>
+      <c r="E15" s="33">
         <f>D15-C15</f>
         <v/>
       </c>
-      <c r="F15" s="27">
+      <c r="F15" s="34">
         <f>IF(C15=0,"",D15/C15)</f>
         <v/>
       </c>
+      <c r="G15" s="4" t="n"/>
+      <c r="H15" s="4" t="n"/>
+      <c r="I15" s="4" t="n"/>
+      <c r="J15" s="4" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="28" t="inlineStr">
-        <is>
-          <t>Papelería y oficina</t>
-        </is>
-      </c>
-      <c r="C16" s="26">
-        <f>Formato!N22</f>
-        <v/>
-      </c>
-      <c r="D16" s="26">
-        <f>Formato!O22</f>
-        <v/>
-      </c>
-      <c r="E16" s="26">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="35" t="inlineStr">
+        <is>
+          <t>PAPELERÍA Y OFICINA</t>
+        </is>
+      </c>
+      <c r="C16" s="33">
+        <f>FORMATO!N22</f>
+        <v/>
+      </c>
+      <c r="D16" s="33">
+        <f>FORMATO!O22</f>
+        <v/>
+      </c>
+      <c r="E16" s="33">
         <f>D16-C16</f>
         <v/>
       </c>
-      <c r="F16" s="27">
+      <c r="F16" s="34">
         <f>IF(C16=0,"",D16/C16)</f>
         <v/>
       </c>
+      <c r="G16" s="4" t="n"/>
+      <c r="H16" s="4" t="n"/>
+      <c r="I16" s="4" t="n"/>
+      <c r="J16" s="4" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="28" t="inlineStr">
-        <is>
-          <t>Impuestos y derechos</t>
-        </is>
-      </c>
-      <c r="C17" s="26">
-        <f>Formato!N24</f>
-        <v/>
-      </c>
-      <c r="D17" s="26">
-        <f>Formato!O24</f>
-        <v/>
-      </c>
-      <c r="E17" s="26">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>IMPUESTOS Y DERECHOS</t>
+        </is>
+      </c>
+      <c r="C17" s="33">
+        <f>FORMATO!N24</f>
+        <v/>
+      </c>
+      <c r="D17" s="33">
+        <f>FORMATO!O24</f>
+        <v/>
+      </c>
+      <c r="E17" s="33">
         <f>D17-C17</f>
         <v/>
       </c>
-      <c r="F17" s="27">
+      <c r="F17" s="34">
         <f>IF(C17=0,"",D17/C17)</f>
         <v/>
       </c>
+      <c r="G17" s="4" t="n"/>
+      <c r="H17" s="4" t="n"/>
+      <c r="I17" s="4" t="n"/>
+      <c r="J17" s="4" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="28" t="inlineStr">
-        <is>
-          <t>Otros gastos</t>
-        </is>
-      </c>
-      <c r="C18" s="26">
-        <f>Formato!N26</f>
-        <v/>
-      </c>
-      <c r="D18" s="26">
-        <f>Formato!O26</f>
-        <v/>
-      </c>
-      <c r="E18" s="26">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="35" t="inlineStr">
+        <is>
+          <t>OTROS GASTOS</t>
+        </is>
+      </c>
+      <c r="C18" s="33">
+        <f>FORMATO!N26</f>
+        <v/>
+      </c>
+      <c r="D18" s="33">
+        <f>FORMATO!O26</f>
+        <v/>
+      </c>
+      <c r="E18" s="33">
         <f>D18-C18</f>
         <v/>
       </c>
-      <c r="F18" s="27">
+      <c r="F18" s="34">
         <f>IF(C18=0,"",D18/C18)</f>
         <v/>
       </c>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="4" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
@@ -2183,4 +2850,349 @@
   </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001B6B73"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="42" t="inlineStr">
+        <is>
+          <t>AYUDA Y PREGUNTAS FRECUENTES</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="n"/>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="43" t="inlineStr">
+        <is>
+          <t>PRESUPUESTO ANUAL</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="1" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>PREGUNTAS FRECUENTES</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="44" t="inlineStr">
+        <is>
+          <t>¿Cómo leo la variación?</t>
+        </is>
+      </c>
+      <c r="D6" s="45" t="inlineStr">
+        <is>
+          <t>Real - Presupuesto. En gastos, positiva significa que te pasaste; en ventas, positiva es favorable.</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="44" t="inlineStr">
+        <is>
+          <t>¿Puedo agregar conceptos?</t>
+        </is>
+      </c>
+      <c r="D7" s="45" t="inlineStr">
+        <is>
+          <t>Cambia el nombre de uno de los 10 conceptos disponibles.</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n"/>
+    </row>
+    <row r="8" ht="53" customHeight="1">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="44" t="inlineStr">
+        <is>
+          <t>¿Por qué no puedo escribir en algunas celdas?</t>
+        </is>
+      </c>
+      <c r="D8" s="45" t="inlineStr">
+        <is>
+          <t>La hoja está protegida para que no se borren fórmulas por accidente. Solo se editan las celdas de captura (color crema). Si necesitas modificar algo más: pestaña Revisar &gt; Desproteger hoja (no tiene contraseña).</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n"/>
+    </row>
+    <row r="9" ht="38" customHeight="1">
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="44" t="inlineStr">
+        <is>
+          <t>¿Cómo agrego mi logotipo?</t>
+        </is>
+      </c>
+      <c r="D9" s="45" t="inlineStr">
+        <is>
+          <t>Haz clic en el recuadro punteado de la esquina superior derecha del formato y usa Insertar &gt; Imágenes. Ajusta el tamaño sin salirte del recuadro.</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n"/>
+    </row>
+    <row r="10" ht="38" customHeight="1">
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="44" t="inlineStr">
+        <is>
+          <t>¿Cómo lo imprimo o lo convierto a PDF?</t>
+        </is>
+      </c>
+      <c r="D10" s="45" t="inlineStr">
+        <is>
+          <t>Archivo &gt; Imprimir (ya está ajustado a una hoja de ancho). Para PDF elige 'Microsoft Print to PDF' o Archivo &gt; Exportar &gt; PDF.</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n"/>
+    </row>
+    <row r="11" ht="38" customHeight="1">
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="44" t="inlineStr">
+        <is>
+          <t>¿Con qué versiones de Excel funciona?</t>
+        </is>
+      </c>
+      <c r="D11" s="45" t="inlineStr">
+        <is>
+          <t>Excel 2016, 2019, 2021 y Microsoft 365 (Windows y Mac). Funciona en LibreOffice y Google Sheets, aunque algunas gráficas y formatos pueden verse distintos.</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n"/>
+    </row>
+    <row r="12" ht="38" customHeight="1">
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="44" t="inlineStr">
+        <is>
+          <t>¿Por qué la letra se ve diferente?</t>
+        </is>
+      </c>
+      <c r="D12" s="45" t="inlineStr">
+        <is>
+          <t>El diseño usa la fuente Abadi, incluida en Microsoft 365. Si tu versión no la tiene, Excel la sustituye por otra; no afecta el funcionamiento.</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n"/>
+    </row>
+    <row r="13" ht="38" customHeight="1">
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="44" t="inlineStr">
+        <is>
+          <t>¿Puedo usarlo en varias empresas o por varios años?</t>
+        </is>
+      </c>
+      <c r="D13" s="45" t="inlineStr">
+        <is>
+          <t>Sí. Guarda una copia del archivo por empresa o por periodo (Archivo &gt; Guardar como) y deja el original en blanco como plantilla maestra.</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>GLOSARIO</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="4" t="n"/>
+    </row>
+    <row r="16" ht="21" customHeight="1">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="46" t="inlineStr">
+        <is>
+          <t>PRESUPUESTO</t>
+        </is>
+      </c>
+      <c r="D16" s="47" t="inlineStr">
+        <is>
+          <t>Plan de ingresos y gastos.</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n"/>
+    </row>
+    <row r="17" ht="21" customHeight="1">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="46" t="inlineStr">
+        <is>
+          <t>VARIACIÓN</t>
+        </is>
+      </c>
+      <c r="D17" s="47" t="inlineStr">
+        <is>
+          <t>Diferencia entre lo real y lo presupuestado.</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="21" customHeight="1">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="46" t="inlineStr">
+        <is>
+          <t>% DE EJECUCIÓN</t>
+        </is>
+      </c>
+      <c r="D18" s="47" t="inlineStr">
+        <is>
+          <t>Real / presupuesto.</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>LISTA DE VERIFICACIÓN (marca ☑ al completar)</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="4" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="inlineStr">
+        <is>
+          <t>Presupuesto aprobado</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="inlineStr">
+        <is>
+          <t>Real capturado al cierre de cada mes</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="inlineStr">
+        <is>
+          <t>Variaciones &gt;10% explicadas</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="inlineStr">
+        <is>
+          <t>Reforecast trimestral</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <mergeCells count="6">
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="B21 B22 B23 B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"☐,☑"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/plantillas/1_Contabilidad_y_Finanzas/06_Presupuesto_Anual.xlsx
+++ b/plantillas/1_Contabilidad_y_Finanzas/06_Presupuesto_Anual.xlsx
@@ -51,7 +51,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
     </font>
     <font>
       <name val="Abadi"/>
@@ -65,7 +65,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
       <sz val="9"/>
     </font>
     <font>
@@ -107,7 +107,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
       <sz val="12"/>
     </font>
     <font>
@@ -130,7 +130,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
       <sz val="11"/>
     </font>
     <font>
@@ -158,7 +158,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
       <sz val="10"/>
     </font>
     <font>
@@ -2855,7 +2855,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001B6B73"/>
+    <tabColor rgb="000E7C8B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>

--- a/plantillas/1_Contabilidad_y_Finanzas/06_Presupuesto_Anual.xlsx
+++ b/plantillas/1_Contabilidad_y_Finanzas/06_Presupuesto_Anual.xlsx
@@ -986,7 +986,7 @@
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>GRUPO CANVILLE</t>
+          <t>FORMATOS ADMINISTRATIVOS</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>
@@ -1468,7 +1468,7 @@
       <c r="A38" s="1" t="n"/>
       <c r="B38" s="21" t="inlineStr">
         <is>
-          <t>GRUPO CANVILLE  ·  Formatos administrativos  ·  Para uso interno de tu empresa</t>
+          <t>Formatos administrativos  ·  Para uso interno de tu empresa</t>
         </is>
       </c>
       <c r="C38" s="4" t="n"/>

--- a/plantillas/1_Contabilidad_y_Finanzas/06_Presupuesto_Anual.xlsx
+++ b/plantillas/1_Contabilidad_y_Finanzas/06_Presupuesto_Anual.xlsx
@@ -12,7 +12,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RESUMEN" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYUDA" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'FORMATO'!$7:$7</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -22,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="28">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,148 +33,161 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="20"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <i val="1"/>
       <color rgb="005B6B78"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <i val="1"/>
       <color rgb="00A6A6A6"/>
       <sz val="8"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000E7C8B"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000E7C8B"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000B2A4A"/>
-      <sz val="18"/>
+      <sz val="24"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="000B2A4A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C9A227"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C9D3DB"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="30"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <i val="1"/>
       <color rgb="00C9D3DB"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C9A227"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000E7C8B"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000E7C8B"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="002B2B2B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000B2A4A"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Abadi"/>
-      <color rgb="002B2B2B"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C9A227"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000E7C8B"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <color rgb="005B6B78"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <color rgb="00C9D3DB"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="18"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C9A227"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000E7C8B"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <color rgb="000B2A4A"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -195,6 +210,16 @@
       </patternFill>
     </fill>
     <fill>
+      <gradientFill type="linear" degree="90">
+        <stop position="0">
+          <color rgb="0017426B"/>
+        </stop>
+        <stop position="1">
+          <color rgb="000B2A4A"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EEF2F5"/>
       </patternFill>
@@ -204,8 +229,13 @@
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="17">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -274,6 +304,20 @@
       </bottom>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="00C9D3DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C9D3DB"/>
+      </right>
+      <top style="medium">
+        <color rgb="00C9A227"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9D3DB"/>
+      </bottom>
+    </border>
+    <border>
       <top style="dashed">
         <color rgb="00A6A6A6"/>
       </top>
@@ -316,6 +360,11 @@
       </bottom>
     </border>
     <border>
+      <left style="thick">
+        <color rgb="00C9A227"/>
+      </left>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="00C9A227"/>
       </left>
@@ -336,6 +385,11 @@
     </border>
     <border>
       <bottom style="thin">
+        <color rgb="00E3E8ED"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
         <color rgb="00C9D3DB"/>
       </bottom>
     </border>
@@ -343,47 +397,55 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -392,53 +454,57 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="25" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="27" fillId="4" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="25" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="27" fillId="6" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="27" fillId="6" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,7 +512,7 @@
   <dxfs count="1">
     <dxf>
       <font>
-        <name val="Abadi"/>
+        <name val="Arial"/>
         <b val="1"/>
         <color rgb="00C00000"/>
       </font>
@@ -526,6 +592,7 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
   <chart>
     <title>
       <tx>
@@ -556,11 +623,11 @@
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="0B2A4A"/>
+              <a:srgbClr val="2A6FBA"/>
             </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:solidFill>
-                <a:srgbClr val="0B2A4A"/>
+                <a:srgbClr val="2A6FBA"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -586,11 +653,11 @@
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="C9A227"/>
+              <a:srgbClr val="E69F00"/>
             </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:solidFill>
-                <a:srgbClr val="C9A227"/>
+                <a:srgbClr val="E69F00"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -606,7 +673,7 @@
             </numRef>
           </val>
         </ser>
-        <gapWidth val="150"/>
+        <gapWidth val="70"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -629,6 +696,16 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+              <a:solidFill>
+                <a:srgbClr val="E3E8ED"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <numFmt formatCode="&quot;$&quot;#,##0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -641,6 +718,12 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -961,7 +1044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1220,7 +1303,7 @@
       <c r="A20" s="4" t="n"/>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>CÓMO USARLO</t>
+          <t>FICHA TÉCNICA</t>
         </is>
       </c>
       <c r="C20" s="10" t="n"/>
@@ -1231,77 +1314,87 @@
     </row>
     <row r="21" ht="21" customHeight="1">
       <c r="A21" s="4" t="n"/>
-      <c r="B21" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>Por cada concepto hay dos renglones: Presup. (lo planeado) y Real (lo ejercido).</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Capacidad</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>10 conceptos x 12 meses</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="17" t="n"/>
       <c r="G21" s="4" t="n"/>
     </row>
     <row r="22" ht="21" customHeight="1">
       <c r="A22" s="4" t="n"/>
-      <c r="B22" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>Captura mes a mes. La columna Variación muestra Real - Presupuesto del primer renglón de cada concepto.</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n"/>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Compatibilidad</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>Excel 2016, 2019, 2021 y Microsoft 365 (Windows y Mac)</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="17" t="n"/>
       <c r="G22" s="4" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="21" customHeight="1">
       <c r="A23" s="4" t="n"/>
-      <c r="B23" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="C23" s="13" t="inlineStr">
-        <is>
-          <t>En gastos, una variación positiva (rojo) significa que te pasaste del presupuesto; en ventas, positiva es favorable.</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n"/>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Idioma y moneda</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>Español (México) · Pesos mexicanos (MXN) · IVA 16%</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="n"/>
+      <c r="F23" s="17" t="n"/>
       <c r="G23" s="4" t="n"/>
     </row>
     <row r="24" ht="21" customHeight="1">
       <c r="A24" s="4" t="n"/>
-      <c r="B24" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>El % de ejecución indica qué parte del presupuesto anual ya se ejerció.</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="4" t="n"/>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Protección</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>Hojas protegidas sin contraseña (Revisar &gt; Desproteger hoja)</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="n"/>
+      <c r="F24" s="17" t="n"/>
       <c r="G24" s="4" t="n"/>
     </row>
-    <row r="25" ht="36" customHeight="1">
+    <row r="25" ht="21" customHeight="1">
       <c r="A25" s="4" t="n"/>
-      <c r="B25" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>Personaliza: inserta tu logotipo en el recuadro punteado de la esquina superior derecha (Insertar &gt; Imágenes) y captura los datos de tu empresa en las celdas de captura.</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="4" t="n"/>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>Arial (disponible en Windows, Mac y Google Sheets)</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="17" t="n"/>
       <c r="G25" s="4" t="n"/>
     </row>
     <row r="26">
@@ -1317,7 +1410,7 @@
       <c r="A27" s="4" t="n"/>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>RECOMENDACIONES DE USO</t>
+          <t>CÓMO USARLO</t>
         </is>
       </c>
       <c r="C27" s="10" t="n"/>
@@ -1328,14 +1421,12 @@
     </row>
     <row r="28" ht="21" customHeight="1">
       <c r="A28" s="4" t="n"/>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="B28" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>Parte de los resultados del año anterior y ajusta por inflación y metas de ventas.</t>
+          <t>Por cada concepto hay dos renglones: Presup. (lo planeado) y Real (lo ejercido).</t>
         </is>
       </c>
       <c r="D28" s="4" t="n"/>
@@ -1345,14 +1436,12 @@
     </row>
     <row r="29" ht="21" customHeight="1">
       <c r="A29" s="4" t="n"/>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="B29" s="18" t="n">
+        <v>2</v>
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>Revisa la variación cada mes y toma acciones si pasa del 10%.</t>
+          <t>Captura mes a mes. La columna Variación muestra Real - Presupuesto del primer renglón de cada concepto.</t>
         </is>
       </c>
       <c r="D29" s="4" t="n"/>
@@ -1360,16 +1449,14 @@
       <c r="F29" s="4" t="n"/>
       <c r="G29" s="4" t="n"/>
     </row>
-    <row r="30" ht="21" customHeight="1">
+    <row r="30" ht="36" customHeight="1">
       <c r="A30" s="4" t="n"/>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="B30" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>Separa gastos fijos y variables para identificar dónde puedes ahorrar.</t>
+          <t>En gastos, una variación positiva (rojo) significa que te pasaste del presupuesto; en ventas, positiva es favorable.</t>
         </is>
       </c>
       <c r="D30" s="4" t="n"/>
@@ -1379,14 +1466,12 @@
     </row>
     <row r="31" ht="21" customHeight="1">
       <c r="A31" s="4" t="n"/>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="B31" s="18" t="n">
+        <v>4</v>
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>Actualiza la proyección trimestralmente (reforecast).</t>
+          <t>El % de ejecución indica qué parte del presupuesto anual ya se ejerció.</t>
         </is>
       </c>
       <c r="D31" s="4" t="n"/>
@@ -1394,47 +1479,53 @@
       <c r="F31" s="4" t="n"/>
       <c r="G31" s="4" t="n"/>
     </row>
-    <row r="32">
+    <row r="32" ht="36" customHeight="1">
       <c r="A32" s="4" t="n"/>
-      <c r="B32" s="4" t="n"/>
-      <c r="C32" s="4" t="n"/>
+      <c r="B32" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>Personaliza: inserta tu logotipo en el recuadro punteado de la esquina superior derecha (Insertar &gt; Imágenes) y captura los datos de tu empresa en las celdas de captura.</t>
+        </is>
+      </c>
       <c r="D32" s="4" t="n"/>
       <c r="E32" s="4" t="n"/>
       <c r="F32" s="4" t="n"/>
       <c r="G32" s="4" t="n"/>
     </row>
-    <row r="33" ht="24" customHeight="1">
+    <row r="33">
       <c r="A33" s="4" t="n"/>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>LEYENDA DE COLORES</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="n"/>
-      <c r="D33" s="10" t="n"/>
-      <c r="E33" s="10" t="n"/>
-      <c r="F33" s="10" t="n"/>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
       <c r="G33" s="4" t="n"/>
     </row>
-    <row r="34">
+    <row r="34" ht="24" customHeight="1">
       <c r="A34" s="4" t="n"/>
-      <c r="B34" s="17" t="inlineStr"/>
-      <c r="C34" s="18" t="inlineStr">
-        <is>
-          <t>CELDA DE CAPTURA: escribe aquí.</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="n"/>
-      <c r="E34" s="4" t="n"/>
-      <c r="F34" s="4" t="n"/>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>RECOMENDACIONES DE USO</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
       <c r="G34" s="4" t="n"/>
     </row>
-    <row r="35">
+    <row r="35" ht="21" customHeight="1">
       <c r="A35" s="4" t="n"/>
-      <c r="B35" s="19" t="inlineStr"/>
-      <c r="C35" s="18" t="inlineStr">
-        <is>
-          <t>CÁLCULO AUTOMÁTICO: no la modifiques.</t>
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>Parte de los resultados del año anterior y ajusta por inflación y metas de ventas.</t>
         </is>
       </c>
       <c r="D35" s="4" t="n"/>
@@ -1442,12 +1533,16 @@
       <c r="F35" s="4" t="n"/>
       <c r="G35" s="4" t="n"/>
     </row>
-    <row r="36">
+    <row r="36" ht="21" customHeight="1">
       <c r="A36" s="4" t="n"/>
-      <c r="B36" s="20" t="inlineStr"/>
-      <c r="C36" s="18" t="inlineStr">
-        <is>
-          <t>ENCABEZADOS Y TÍTULOS.</t>
+      <c r="B36" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>Revisa la variación cada mes y toma acciones si pasa del 10%.</t>
         </is>
       </c>
       <c r="D36" s="4" t="n"/>
@@ -1455,48 +1550,166 @@
       <c r="F36" s="4" t="n"/>
       <c r="G36" s="4" t="n"/>
     </row>
-    <row r="37">
+    <row r="37" ht="21" customHeight="1">
       <c r="A37" s="4" t="n"/>
-      <c r="B37" s="4" t="n"/>
-      <c r="C37" s="4" t="n"/>
+      <c r="B37" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="inlineStr">
+        <is>
+          <t>Separa gastos fijos y variables para identificar dónde puedes ahorrar.</t>
+        </is>
+      </c>
       <c r="D37" s="4" t="n"/>
       <c r="E37" s="4" t="n"/>
       <c r="F37" s="4" t="n"/>
       <c r="G37" s="4" t="n"/>
     </row>
-    <row r="38" ht="26" customHeight="1">
-      <c r="A38" s="1" t="n"/>
-      <c r="B38" s="21" t="inlineStr">
-        <is>
-          <t>Formatos administrativos  ·  Para uso interno de tu empresa</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="n"/>
+    <row r="38" ht="21" customHeight="1">
+      <c r="A38" s="4" t="n"/>
+      <c r="B38" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>Actualiza la proyección trimestralmente (reforecast).</t>
+        </is>
+      </c>
       <c r="D38" s="4" t="n"/>
       <c r="E38" s="4" t="n"/>
       <c r="F38" s="4" t="n"/>
-      <c r="G38" s="1" t="n"/>
+      <c r="G38" s="4" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n"/>
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="4" t="n"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="4" t="n"/>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>LEYENDA DE COLORES</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
+      <c r="G40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n"/>
+      <c r="B41" s="20" t="inlineStr"/>
+      <c r="C41" s="21" t="inlineStr">
+        <is>
+          <t>CELDA DE CAPTURA: escribe aquí.</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="4" t="n"/>
+      <c r="G41" s="4" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n"/>
+      <c r="B42" s="22" t="inlineStr"/>
+      <c r="C42" s="21" t="inlineStr">
+        <is>
+          <t>CÁLCULO AUTOMÁTICO: no la modifiques.</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="n"/>
+      <c r="E42" s="4" t="n"/>
+      <c r="F42" s="4" t="n"/>
+      <c r="G42" s="4" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n"/>
+      <c r="B43" s="23" t="inlineStr"/>
+      <c r="C43" s="21" t="inlineStr">
+        <is>
+          <t>ENCABEZADOS Y TÍTULOS.</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="4" t="n"/>
+      <c r="G43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n"/>
+      <c r="B44" s="24" t="inlineStr"/>
+      <c r="C44" s="21" t="inlineStr">
+        <is>
+          <t>* CAMPO OBLIGATORIO: complétalo antes de imprimir o enviar.</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="n"/>
+      <c r="E44" s="4" t="n"/>
+      <c r="F44" s="4" t="n"/>
+      <c r="G44" s="4" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n"/>
+      <c r="B45" s="4" t="n"/>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="n"/>
+    </row>
+    <row r="46" ht="26" customHeight="1">
+      <c r="A46" s="1" t="n"/>
+      <c r="B46" s="25" t="inlineStr">
+        <is>
+          <t>Formatos administrativos  ·  Para uso interno de tu empresa</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="n"/>
+      <c r="D46" s="4" t="n"/>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="n"/>
+      <c r="G46" s="1" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <mergeCells count="16">
-    <mergeCell ref="C22:F22"/>
+  <mergeCells count="21">
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="B4:F5"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="C29:F29"/>
     <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C23:F23"/>
     <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="B4:F5"/>
-    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="C36:F36"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId3"/>
+  </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="1" fitToWidth="1"/>
@@ -1533,7 +1746,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="44" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>PRESUPUESTO ANUAL: PRESUPUESTADO VS REAL</t>
         </is>
@@ -1552,36 +1765,36 @@
       <c r="M1" s="1" t="n"/>
       <c r="N1" s="1" t="n"/>
       <c r="O1" s="1" t="n"/>
-      <c r="P1" s="23" t="inlineStr">
+      <c r="P1" s="27" t="inlineStr">
         <is>
           <t>INSERTE SU LOGO
 (clic derecho &gt; Insertar imagen)</t>
         </is>
       </c>
-      <c r="Q1" s="24" t="n"/>
+      <c r="Q1" s="28" t="n"/>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="29" t="inlineStr">
         <is>
           <t>Captura presupuesto y gasto real por mes; la variación se calcula sola</t>
         </is>
       </c>
-      <c r="B2" s="26" t="n"/>
-      <c r="C2" s="26" t="n"/>
-      <c r="D2" s="26" t="n"/>
-      <c r="E2" s="26" t="n"/>
-      <c r="F2" s="26" t="n"/>
-      <c r="G2" s="26" t="n"/>
-      <c r="H2" s="26" t="n"/>
-      <c r="I2" s="26" t="n"/>
-      <c r="J2" s="26" t="n"/>
-      <c r="K2" s="26" t="n"/>
-      <c r="L2" s="26" t="n"/>
-      <c r="M2" s="26" t="n"/>
-      <c r="N2" s="26" t="n"/>
-      <c r="O2" s="26" t="n"/>
-      <c r="P2" s="27" t="n"/>
-      <c r="Q2" s="28" t="n"/>
+      <c r="B2" s="30" t="n"/>
+      <c r="C2" s="30" t="n"/>
+      <c r="D2" s="30" t="n"/>
+      <c r="E2" s="30" t="n"/>
+      <c r="F2" s="30" t="n"/>
+      <c r="G2" s="30" t="n"/>
+      <c r="H2" s="30" t="n"/>
+      <c r="I2" s="30" t="n"/>
+      <c r="J2" s="30" t="n"/>
+      <c r="K2" s="30" t="n"/>
+      <c r="L2" s="30" t="n"/>
+      <c r="M2" s="30" t="n"/>
+      <c r="N2" s="30" t="n"/>
+      <c r="O2" s="30" t="n"/>
+      <c r="P2" s="31" t="n"/>
+      <c r="Q2" s="32" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n"/>
@@ -1603,21 +1816,21 @@
       <c r="Q3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>EMPRESA / ÁREA</t>
         </is>
       </c>
-      <c r="B4" s="17" t="n"/>
-      <c r="C4" s="17" t="n"/>
-      <c r="D4" s="17" t="n"/>
+      <c r="B4" s="20" t="n"/>
+      <c r="C4" s="20" t="n"/>
+      <c r="D4" s="20" t="n"/>
       <c r="E4" s="4" t="n"/>
-      <c r="F4" s="29" t="inlineStr">
+      <c r="F4" s="33" t="inlineStr">
         <is>
           <t>AÑO</t>
         </is>
       </c>
-      <c r="G4" s="17" t="n">
+      <c r="G4" s="20" t="n">
         <v>2026</v>
       </c>
       <c r="H4" s="4" t="n"/>
@@ -1669,668 +1882,668 @@
       <c r="P6" s="4" t="n"/>
       <c r="Q6" s="4" t="n"/>
     </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="30" t="inlineStr">
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>CONCEPTO</t>
         </is>
       </c>
-      <c r="B7" s="30" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>ENE</t>
         </is>
       </c>
-      <c r="C7" s="30" t="inlineStr">
+      <c r="C7" s="34" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="D7" s="30" t="inlineStr">
+      <c r="D7" s="34" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="E7" s="30" t="inlineStr">
+      <c r="E7" s="34" t="inlineStr">
         <is>
           <t>ABR</t>
         </is>
       </c>
-      <c r="F7" s="30" t="inlineStr">
+      <c r="F7" s="34" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
-      <c r="G7" s="30" t="inlineStr">
+      <c r="G7" s="34" t="inlineStr">
         <is>
           <t>JUN</t>
         </is>
       </c>
-      <c r="H7" s="30" t="inlineStr">
+      <c r="H7" s="34" t="inlineStr">
         <is>
           <t>JUL</t>
         </is>
       </c>
-      <c r="I7" s="30" t="inlineStr">
+      <c r="I7" s="34" t="inlineStr">
         <is>
           <t>AGO</t>
         </is>
       </c>
-      <c r="J7" s="30" t="inlineStr">
+      <c r="J7" s="34" t="inlineStr">
         <is>
           <t>SEP</t>
         </is>
       </c>
-      <c r="K7" s="30" t="inlineStr">
+      <c r="K7" s="34" t="inlineStr">
         <is>
           <t>OCT</t>
         </is>
       </c>
-      <c r="L7" s="30" t="inlineStr">
+      <c r="L7" s="34" t="inlineStr">
         <is>
           <t>NOV</t>
         </is>
       </c>
-      <c r="M7" s="30" t="inlineStr">
+      <c r="M7" s="34" t="inlineStr">
         <is>
           <t>DIC</t>
         </is>
       </c>
-      <c r="N7" s="30" t="inlineStr">
+      <c r="N7" s="34" t="inlineStr">
         <is>
           <t>PRESUP. ANUAL</t>
         </is>
       </c>
-      <c r="O7" s="30" t="inlineStr">
+      <c r="O7" s="34" t="inlineStr">
         <is>
           <t>REAL ANUAL</t>
         </is>
       </c>
-      <c r="P7" s="30" t="inlineStr">
+      <c r="P7" s="34" t="inlineStr">
         <is>
           <t>VARIACIÓN</t>
         </is>
       </c>
-      <c r="Q7" s="30" t="inlineStr">
+      <c r="Q7" s="34" t="inlineStr">
         <is>
           <t>% EJEC.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="31" t="inlineStr">
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>VENTAS - PRESUP.</t>
         </is>
       </c>
-      <c r="B8" s="32" t="n"/>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="32" t="n"/>
-      <c r="E8" s="32" t="n"/>
-      <c r="F8" s="32" t="n"/>
-      <c r="G8" s="32" t="n"/>
-      <c r="H8" s="32" t="n"/>
-      <c r="I8" s="32" t="n"/>
-      <c r="J8" s="32" t="n"/>
-      <c r="K8" s="32" t="n"/>
-      <c r="L8" s="32" t="n"/>
-      <c r="M8" s="32" t="n"/>
-      <c r="N8" s="33">
+      <c r="B8" s="36" t="n"/>
+      <c r="C8" s="36" t="n"/>
+      <c r="D8" s="36" t="n"/>
+      <c r="E8" s="36" t="n"/>
+      <c r="F8" s="36" t="n"/>
+      <c r="G8" s="36" t="n"/>
+      <c r="H8" s="36" t="n"/>
+      <c r="I8" s="36" t="n"/>
+      <c r="J8" s="36" t="n"/>
+      <c r="K8" s="36" t="n"/>
+      <c r="L8" s="36" t="n"/>
+      <c r="M8" s="36" t="n"/>
+      <c r="N8" s="37">
         <f>SUM(B8:M8)</f>
         <v/>
       </c>
-      <c r="O8" s="33">
+      <c r="O8" s="37">
         <f>SUM(B9:M9)</f>
         <v/>
       </c>
-      <c r="P8" s="33">
+      <c r="P8" s="37">
         <f>O8-N8</f>
         <v/>
       </c>
-      <c r="Q8" s="34">
+      <c r="Q8" s="38">
         <f>IF(N8=0,"",O8/N8)</f>
         <v/>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="35" t="inlineStr">
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="39" t="inlineStr">
         <is>
           <t>VENTAS - REAL</t>
         </is>
       </c>
-      <c r="B9" s="32" t="n"/>
-      <c r="C9" s="32" t="n"/>
-      <c r="D9" s="32" t="n"/>
-      <c r="E9" s="32" t="n"/>
-      <c r="F9" s="32" t="n"/>
-      <c r="G9" s="32" t="n"/>
-      <c r="H9" s="32" t="n"/>
-      <c r="I9" s="32" t="n"/>
-      <c r="J9" s="32" t="n"/>
-      <c r="K9" s="32" t="n"/>
-      <c r="L9" s="32" t="n"/>
-      <c r="M9" s="32" t="n"/>
+      <c r="B9" s="36" t="n"/>
+      <c r="C9" s="36" t="n"/>
+      <c r="D9" s="36" t="n"/>
+      <c r="E9" s="36" t="n"/>
+      <c r="F9" s="36" t="n"/>
+      <c r="G9" s="36" t="n"/>
+      <c r="H9" s="36" t="n"/>
+      <c r="I9" s="36" t="n"/>
+      <c r="J9" s="36" t="n"/>
+      <c r="K9" s="36" t="n"/>
+      <c r="L9" s="36" t="n"/>
+      <c r="M9" s="36" t="n"/>
       <c r="N9" s="4" t="n"/>
       <c r="O9" s="4" t="n"/>
       <c r="P9" s="4" t="n"/>
       <c r="Q9" s="4" t="n"/>
     </row>
-    <row r="10">
-      <c r="A10" s="31" t="inlineStr">
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>COSTO DE VENTAS - PRESUP.</t>
         </is>
       </c>
-      <c r="B10" s="32" t="n"/>
-      <c r="C10" s="32" t="n"/>
-      <c r="D10" s="32" t="n"/>
-      <c r="E10" s="32" t="n"/>
-      <c r="F10" s="32" t="n"/>
-      <c r="G10" s="32" t="n"/>
-      <c r="H10" s="32" t="n"/>
-      <c r="I10" s="32" t="n"/>
-      <c r="J10" s="32" t="n"/>
-      <c r="K10" s="32" t="n"/>
-      <c r="L10" s="32" t="n"/>
-      <c r="M10" s="32" t="n"/>
-      <c r="N10" s="33">
+      <c r="B10" s="36" t="n"/>
+      <c r="C10" s="36" t="n"/>
+      <c r="D10" s="36" t="n"/>
+      <c r="E10" s="36" t="n"/>
+      <c r="F10" s="36" t="n"/>
+      <c r="G10" s="36" t="n"/>
+      <c r="H10" s="36" t="n"/>
+      <c r="I10" s="36" t="n"/>
+      <c r="J10" s="36" t="n"/>
+      <c r="K10" s="36" t="n"/>
+      <c r="L10" s="36" t="n"/>
+      <c r="M10" s="36" t="n"/>
+      <c r="N10" s="37">
         <f>SUM(B10:M10)</f>
         <v/>
       </c>
-      <c r="O10" s="33">
+      <c r="O10" s="37">
         <f>SUM(B11:M11)</f>
         <v/>
       </c>
-      <c r="P10" s="33">
+      <c r="P10" s="37">
         <f>O10-N10</f>
         <v/>
       </c>
-      <c r="Q10" s="34">
+      <c r="Q10" s="38">
         <f>IF(N10=0,"",O10/N10)</f>
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="35" t="inlineStr">
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="39" t="inlineStr">
         <is>
           <t>COSTO DE VENTAS - REAL</t>
         </is>
       </c>
-      <c r="B11" s="32" t="n"/>
-      <c r="C11" s="32" t="n"/>
-      <c r="D11" s="32" t="n"/>
-      <c r="E11" s="32" t="n"/>
-      <c r="F11" s="32" t="n"/>
-      <c r="G11" s="32" t="n"/>
-      <c r="H11" s="32" t="n"/>
-      <c r="I11" s="32" t="n"/>
-      <c r="J11" s="32" t="n"/>
-      <c r="K11" s="32" t="n"/>
-      <c r="L11" s="32" t="n"/>
-      <c r="M11" s="32" t="n"/>
+      <c r="B11" s="36" t="n"/>
+      <c r="C11" s="36" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="36" t="n"/>
+      <c r="F11" s="36" t="n"/>
+      <c r="G11" s="36" t="n"/>
+      <c r="H11" s="36" t="n"/>
+      <c r="I11" s="36" t="n"/>
+      <c r="J11" s="36" t="n"/>
+      <c r="K11" s="36" t="n"/>
+      <c r="L11" s="36" t="n"/>
+      <c r="M11" s="36" t="n"/>
       <c r="N11" s="4" t="n"/>
       <c r="O11" s="4" t="n"/>
       <c r="P11" s="4" t="n"/>
       <c r="Q11" s="4" t="n"/>
     </row>
-    <row r="12">
-      <c r="A12" s="31" t="inlineStr">
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>SUELDOS Y SALARIOS - PRESUP.</t>
         </is>
       </c>
-      <c r="B12" s="32" t="n"/>
-      <c r="C12" s="32" t="n"/>
-      <c r="D12" s="32" t="n"/>
-      <c r="E12" s="32" t="n"/>
-      <c r="F12" s="32" t="n"/>
-      <c r="G12" s="32" t="n"/>
-      <c r="H12" s="32" t="n"/>
-      <c r="I12" s="32" t="n"/>
-      <c r="J12" s="32" t="n"/>
-      <c r="K12" s="32" t="n"/>
-      <c r="L12" s="32" t="n"/>
-      <c r="M12" s="32" t="n"/>
-      <c r="N12" s="33">
+      <c r="B12" s="36" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="36" t="n"/>
+      <c r="G12" s="36" t="n"/>
+      <c r="H12" s="36" t="n"/>
+      <c r="I12" s="36" t="n"/>
+      <c r="J12" s="36" t="n"/>
+      <c r="K12" s="36" t="n"/>
+      <c r="L12" s="36" t="n"/>
+      <c r="M12" s="36" t="n"/>
+      <c r="N12" s="37">
         <f>SUM(B12:M12)</f>
         <v/>
       </c>
-      <c r="O12" s="33">
+      <c r="O12" s="37">
         <f>SUM(B13:M13)</f>
         <v/>
       </c>
-      <c r="P12" s="33">
+      <c r="P12" s="37">
         <f>O12-N12</f>
         <v/>
       </c>
-      <c r="Q12" s="34">
+      <c r="Q12" s="38">
         <f>IF(N12=0,"",O12/N12)</f>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="35" t="inlineStr">
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="39" t="inlineStr">
         <is>
           <t>SUELDOS Y SALARIOS - REAL</t>
         </is>
       </c>
-      <c r="B13" s="32" t="n"/>
-      <c r="C13" s="32" t="n"/>
-      <c r="D13" s="32" t="n"/>
-      <c r="E13" s="32" t="n"/>
-      <c r="F13" s="32" t="n"/>
-      <c r="G13" s="32" t="n"/>
-      <c r="H13" s="32" t="n"/>
-      <c r="I13" s="32" t="n"/>
-      <c r="J13" s="32" t="n"/>
-      <c r="K13" s="32" t="n"/>
-      <c r="L13" s="32" t="n"/>
-      <c r="M13" s="32" t="n"/>
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="36" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="36" t="n"/>
+      <c r="F13" s="36" t="n"/>
+      <c r="G13" s="36" t="n"/>
+      <c r="H13" s="36" t="n"/>
+      <c r="I13" s="36" t="n"/>
+      <c r="J13" s="36" t="n"/>
+      <c r="K13" s="36" t="n"/>
+      <c r="L13" s="36" t="n"/>
+      <c r="M13" s="36" t="n"/>
       <c r="N13" s="4" t="n"/>
       <c r="O13" s="4" t="n"/>
       <c r="P13" s="4" t="n"/>
       <c r="Q13" s="4" t="n"/>
     </row>
-    <row r="14">
-      <c r="A14" s="31" t="inlineStr">
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="35" t="inlineStr">
         <is>
           <t>RENTA - PRESUP.</t>
         </is>
       </c>
-      <c r="B14" s="32" t="n"/>
-      <c r="C14" s="32" t="n"/>
-      <c r="D14" s="32" t="n"/>
-      <c r="E14" s="32" t="n"/>
-      <c r="F14" s="32" t="n"/>
-      <c r="G14" s="32" t="n"/>
-      <c r="H14" s="32" t="n"/>
-      <c r="I14" s="32" t="n"/>
-      <c r="J14" s="32" t="n"/>
-      <c r="K14" s="32" t="n"/>
-      <c r="L14" s="32" t="n"/>
-      <c r="M14" s="32" t="n"/>
-      <c r="N14" s="33">
+      <c r="B14" s="36" t="n"/>
+      <c r="C14" s="36" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="36" t="n"/>
+      <c r="F14" s="36" t="n"/>
+      <c r="G14" s="36" t="n"/>
+      <c r="H14" s="36" t="n"/>
+      <c r="I14" s="36" t="n"/>
+      <c r="J14" s="36" t="n"/>
+      <c r="K14" s="36" t="n"/>
+      <c r="L14" s="36" t="n"/>
+      <c r="M14" s="36" t="n"/>
+      <c r="N14" s="37">
         <f>SUM(B14:M14)</f>
         <v/>
       </c>
-      <c r="O14" s="33">
+      <c r="O14" s="37">
         <f>SUM(B15:M15)</f>
         <v/>
       </c>
-      <c r="P14" s="33">
+      <c r="P14" s="37">
         <f>O14-N14</f>
         <v/>
       </c>
-      <c r="Q14" s="34">
+      <c r="Q14" s="38">
         <f>IF(N14=0,"",O14/N14)</f>
         <v/>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="35" t="inlineStr">
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="39" t="inlineStr">
         <is>
           <t>RENTA - REAL</t>
         </is>
       </c>
-      <c r="B15" s="32" t="n"/>
-      <c r="C15" s="32" t="n"/>
-      <c r="D15" s="32" t="n"/>
-      <c r="E15" s="32" t="n"/>
-      <c r="F15" s="32" t="n"/>
-      <c r="G15" s="32" t="n"/>
-      <c r="H15" s="32" t="n"/>
-      <c r="I15" s="32" t="n"/>
-      <c r="J15" s="32" t="n"/>
-      <c r="K15" s="32" t="n"/>
-      <c r="L15" s="32" t="n"/>
-      <c r="M15" s="32" t="n"/>
+      <c r="B15" s="36" t="n"/>
+      <c r="C15" s="36" t="n"/>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="36" t="n"/>
+      <c r="F15" s="36" t="n"/>
+      <c r="G15" s="36" t="n"/>
+      <c r="H15" s="36" t="n"/>
+      <c r="I15" s="36" t="n"/>
+      <c r="J15" s="36" t="n"/>
+      <c r="K15" s="36" t="n"/>
+      <c r="L15" s="36" t="n"/>
+      <c r="M15" s="36" t="n"/>
       <c r="N15" s="4" t="n"/>
       <c r="O15" s="4" t="n"/>
       <c r="P15" s="4" t="n"/>
       <c r="Q15" s="4" t="n"/>
     </row>
-    <row r="16">
-      <c r="A16" s="31" t="inlineStr">
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="35" t="inlineStr">
         <is>
           <t>SERVICIOS - PRESUP.</t>
         </is>
       </c>
-      <c r="B16" s="32" t="n"/>
-      <c r="C16" s="32" t="n"/>
-      <c r="D16" s="32" t="n"/>
-      <c r="E16" s="32" t="n"/>
-      <c r="F16" s="32" t="n"/>
-      <c r="G16" s="32" t="n"/>
-      <c r="H16" s="32" t="n"/>
-      <c r="I16" s="32" t="n"/>
-      <c r="J16" s="32" t="n"/>
-      <c r="K16" s="32" t="n"/>
-      <c r="L16" s="32" t="n"/>
-      <c r="M16" s="32" t="n"/>
-      <c r="N16" s="33">
+      <c r="B16" s="36" t="n"/>
+      <c r="C16" s="36" t="n"/>
+      <c r="D16" s="36" t="n"/>
+      <c r="E16" s="36" t="n"/>
+      <c r="F16" s="36" t="n"/>
+      <c r="G16" s="36" t="n"/>
+      <c r="H16" s="36" t="n"/>
+      <c r="I16" s="36" t="n"/>
+      <c r="J16" s="36" t="n"/>
+      <c r="K16" s="36" t="n"/>
+      <c r="L16" s="36" t="n"/>
+      <c r="M16" s="36" t="n"/>
+      <c r="N16" s="37">
         <f>SUM(B16:M16)</f>
         <v/>
       </c>
-      <c r="O16" s="33">
+      <c r="O16" s="37">
         <f>SUM(B17:M17)</f>
         <v/>
       </c>
-      <c r="P16" s="33">
+      <c r="P16" s="37">
         <f>O16-N16</f>
         <v/>
       </c>
-      <c r="Q16" s="34">
+      <c r="Q16" s="38">
         <f>IF(N16=0,"",O16/N16)</f>
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="35" t="inlineStr">
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="39" t="inlineStr">
         <is>
           <t>SERVICIOS - REAL</t>
         </is>
       </c>
-      <c r="B17" s="32" t="n"/>
-      <c r="C17" s="32" t="n"/>
-      <c r="D17" s="32" t="n"/>
-      <c r="E17" s="32" t="n"/>
-      <c r="F17" s="32" t="n"/>
-      <c r="G17" s="32" t="n"/>
-      <c r="H17" s="32" t="n"/>
-      <c r="I17" s="32" t="n"/>
-      <c r="J17" s="32" t="n"/>
-      <c r="K17" s="32" t="n"/>
-      <c r="L17" s="32" t="n"/>
-      <c r="M17" s="32" t="n"/>
+      <c r="B17" s="36" t="n"/>
+      <c r="C17" s="36" t="n"/>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="36" t="n"/>
+      <c r="F17" s="36" t="n"/>
+      <c r="G17" s="36" t="n"/>
+      <c r="H17" s="36" t="n"/>
+      <c r="I17" s="36" t="n"/>
+      <c r="J17" s="36" t="n"/>
+      <c r="K17" s="36" t="n"/>
+      <c r="L17" s="36" t="n"/>
+      <c r="M17" s="36" t="n"/>
       <c r="N17" s="4" t="n"/>
       <c r="O17" s="4" t="n"/>
       <c r="P17" s="4" t="n"/>
       <c r="Q17" s="4" t="n"/>
     </row>
-    <row r="18">
-      <c r="A18" s="31" t="inlineStr">
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="35" t="inlineStr">
         <is>
           <t>PUBLICIDAD Y MERCADOTECNIA - PRESUP.</t>
         </is>
       </c>
-      <c r="B18" s="32" t="n"/>
-      <c r="C18" s="32" t="n"/>
-      <c r="D18" s="32" t="n"/>
-      <c r="E18" s="32" t="n"/>
-      <c r="F18" s="32" t="n"/>
-      <c r="G18" s="32" t="n"/>
-      <c r="H18" s="32" t="n"/>
-      <c r="I18" s="32" t="n"/>
-      <c r="J18" s="32" t="n"/>
-      <c r="K18" s="32" t="n"/>
-      <c r="L18" s="32" t="n"/>
-      <c r="M18" s="32" t="n"/>
-      <c r="N18" s="33">
+      <c r="B18" s="36" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
+      <c r="F18" s="36" t="n"/>
+      <c r="G18" s="36" t="n"/>
+      <c r="H18" s="36" t="n"/>
+      <c r="I18" s="36" t="n"/>
+      <c r="J18" s="36" t="n"/>
+      <c r="K18" s="36" t="n"/>
+      <c r="L18" s="36" t="n"/>
+      <c r="M18" s="36" t="n"/>
+      <c r="N18" s="37">
         <f>SUM(B18:M18)</f>
         <v/>
       </c>
-      <c r="O18" s="33">
+      <c r="O18" s="37">
         <f>SUM(B19:M19)</f>
         <v/>
       </c>
-      <c r="P18" s="33">
+      <c r="P18" s="37">
         <f>O18-N18</f>
         <v/>
       </c>
-      <c r="Q18" s="34">
+      <c r="Q18" s="38">
         <f>IF(N18=0,"",O18/N18)</f>
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="35" t="inlineStr">
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="39" t="inlineStr">
         <is>
           <t>PUBLICIDAD Y MERCADOTECNIA - REAL</t>
         </is>
       </c>
-      <c r="B19" s="32" t="n"/>
-      <c r="C19" s="32" t="n"/>
-      <c r="D19" s="32" t="n"/>
-      <c r="E19" s="32" t="n"/>
-      <c r="F19" s="32" t="n"/>
-      <c r="G19" s="32" t="n"/>
-      <c r="H19" s="32" t="n"/>
-      <c r="I19" s="32" t="n"/>
-      <c r="J19" s="32" t="n"/>
-      <c r="K19" s="32" t="n"/>
-      <c r="L19" s="32" t="n"/>
-      <c r="M19" s="32" t="n"/>
+      <c r="B19" s="36" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="36" t="n"/>
+      <c r="F19" s="36" t="n"/>
+      <c r="G19" s="36" t="n"/>
+      <c r="H19" s="36" t="n"/>
+      <c r="I19" s="36" t="n"/>
+      <c r="J19" s="36" t="n"/>
+      <c r="K19" s="36" t="n"/>
+      <c r="L19" s="36" t="n"/>
+      <c r="M19" s="36" t="n"/>
       <c r="N19" s="4" t="n"/>
       <c r="O19" s="4" t="n"/>
       <c r="P19" s="4" t="n"/>
       <c r="Q19" s="4" t="n"/>
     </row>
-    <row r="20">
-      <c r="A20" s="31" t="inlineStr">
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="35" t="inlineStr">
         <is>
           <t>MANTENIMIENTO - PRESUP.</t>
         </is>
       </c>
-      <c r="B20" s="32" t="n"/>
-      <c r="C20" s="32" t="n"/>
-      <c r="D20" s="32" t="n"/>
-      <c r="E20" s="32" t="n"/>
-      <c r="F20" s="32" t="n"/>
-      <c r="G20" s="32" t="n"/>
-      <c r="H20" s="32" t="n"/>
-      <c r="I20" s="32" t="n"/>
-      <c r="J20" s="32" t="n"/>
-      <c r="K20" s="32" t="n"/>
-      <c r="L20" s="32" t="n"/>
-      <c r="M20" s="32" t="n"/>
-      <c r="N20" s="33">
+      <c r="B20" s="36" t="n"/>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="36" t="n"/>
+      <c r="F20" s="36" t="n"/>
+      <c r="G20" s="36" t="n"/>
+      <c r="H20" s="36" t="n"/>
+      <c r="I20" s="36" t="n"/>
+      <c r="J20" s="36" t="n"/>
+      <c r="K20" s="36" t="n"/>
+      <c r="L20" s="36" t="n"/>
+      <c r="M20" s="36" t="n"/>
+      <c r="N20" s="37">
         <f>SUM(B20:M20)</f>
         <v/>
       </c>
-      <c r="O20" s="33">
+      <c r="O20" s="37">
         <f>SUM(B21:M21)</f>
         <v/>
       </c>
-      <c r="P20" s="33">
+      <c r="P20" s="37">
         <f>O20-N20</f>
         <v/>
       </c>
-      <c r="Q20" s="34">
+      <c r="Q20" s="38">
         <f>IF(N20=0,"",O20/N20)</f>
         <v/>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="35" t="inlineStr">
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="39" t="inlineStr">
         <is>
           <t>MANTENIMIENTO - REAL</t>
         </is>
       </c>
-      <c r="B21" s="32" t="n"/>
-      <c r="C21" s="32" t="n"/>
-      <c r="D21" s="32" t="n"/>
-      <c r="E21" s="32" t="n"/>
-      <c r="F21" s="32" t="n"/>
-      <c r="G21" s="32" t="n"/>
-      <c r="H21" s="32" t="n"/>
-      <c r="I21" s="32" t="n"/>
-      <c r="J21" s="32" t="n"/>
-      <c r="K21" s="32" t="n"/>
-      <c r="L21" s="32" t="n"/>
-      <c r="M21" s="32" t="n"/>
+      <c r="B21" s="36" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="36" t="n"/>
+      <c r="F21" s="36" t="n"/>
+      <c r="G21" s="36" t="n"/>
+      <c r="H21" s="36" t="n"/>
+      <c r="I21" s="36" t="n"/>
+      <c r="J21" s="36" t="n"/>
+      <c r="K21" s="36" t="n"/>
+      <c r="L21" s="36" t="n"/>
+      <c r="M21" s="36" t="n"/>
       <c r="N21" s="4" t="n"/>
       <c r="O21" s="4" t="n"/>
       <c r="P21" s="4" t="n"/>
       <c r="Q21" s="4" t="n"/>
     </row>
-    <row r="22">
-      <c r="A22" s="31" t="inlineStr">
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="35" t="inlineStr">
         <is>
           <t>PAPELERÍA Y OFICINA - PRESUP.</t>
         </is>
       </c>
-      <c r="B22" s="32" t="n"/>
-      <c r="C22" s="32" t="n"/>
-      <c r="D22" s="32" t="n"/>
-      <c r="E22" s="32" t="n"/>
-      <c r="F22" s="32" t="n"/>
-      <c r="G22" s="32" t="n"/>
-      <c r="H22" s="32" t="n"/>
-      <c r="I22" s="32" t="n"/>
-      <c r="J22" s="32" t="n"/>
-      <c r="K22" s="32" t="n"/>
-      <c r="L22" s="32" t="n"/>
-      <c r="M22" s="32" t="n"/>
-      <c r="N22" s="33">
+      <c r="B22" s="36" t="n"/>
+      <c r="C22" s="36" t="n"/>
+      <c r="D22" s="36" t="n"/>
+      <c r="E22" s="36" t="n"/>
+      <c r="F22" s="36" t="n"/>
+      <c r="G22" s="36" t="n"/>
+      <c r="H22" s="36" t="n"/>
+      <c r="I22" s="36" t="n"/>
+      <c r="J22" s="36" t="n"/>
+      <c r="K22" s="36" t="n"/>
+      <c r="L22" s="36" t="n"/>
+      <c r="M22" s="36" t="n"/>
+      <c r="N22" s="37">
         <f>SUM(B22:M22)</f>
         <v/>
       </c>
-      <c r="O22" s="33">
+      <c r="O22" s="37">
         <f>SUM(B23:M23)</f>
         <v/>
       </c>
-      <c r="P22" s="33">
+      <c r="P22" s="37">
         <f>O22-N22</f>
         <v/>
       </c>
-      <c r="Q22" s="34">
+      <c r="Q22" s="38">
         <f>IF(N22=0,"",O22/N22)</f>
         <v/>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="35" t="inlineStr">
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="39" t="inlineStr">
         <is>
           <t>PAPELERÍA Y OFICINA - REAL</t>
         </is>
       </c>
-      <c r="B23" s="32" t="n"/>
-      <c r="C23" s="32" t="n"/>
-      <c r="D23" s="32" t="n"/>
-      <c r="E23" s="32" t="n"/>
-      <c r="F23" s="32" t="n"/>
-      <c r="G23" s="32" t="n"/>
-      <c r="H23" s="32" t="n"/>
-      <c r="I23" s="32" t="n"/>
-      <c r="J23" s="32" t="n"/>
-      <c r="K23" s="32" t="n"/>
-      <c r="L23" s="32" t="n"/>
-      <c r="M23" s="32" t="n"/>
+      <c r="B23" s="36" t="n"/>
+      <c r="C23" s="36" t="n"/>
+      <c r="D23" s="36" t="n"/>
+      <c r="E23" s="36" t="n"/>
+      <c r="F23" s="36" t="n"/>
+      <c r="G23" s="36" t="n"/>
+      <c r="H23" s="36" t="n"/>
+      <c r="I23" s="36" t="n"/>
+      <c r="J23" s="36" t="n"/>
+      <c r="K23" s="36" t="n"/>
+      <c r="L23" s="36" t="n"/>
+      <c r="M23" s="36" t="n"/>
       <c r="N23" s="4" t="n"/>
       <c r="O23" s="4" t="n"/>
       <c r="P23" s="4" t="n"/>
       <c r="Q23" s="4" t="n"/>
     </row>
-    <row r="24">
-      <c r="A24" s="31" t="inlineStr">
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="35" t="inlineStr">
         <is>
           <t>IMPUESTOS Y DERECHOS - PRESUP.</t>
         </is>
       </c>
-      <c r="B24" s="32" t="n"/>
-      <c r="C24" s="32" t="n"/>
-      <c r="D24" s="32" t="n"/>
-      <c r="E24" s="32" t="n"/>
-      <c r="F24" s="32" t="n"/>
-      <c r="G24" s="32" t="n"/>
-      <c r="H24" s="32" t="n"/>
-      <c r="I24" s="32" t="n"/>
-      <c r="J24" s="32" t="n"/>
-      <c r="K24" s="32" t="n"/>
-      <c r="L24" s="32" t="n"/>
-      <c r="M24" s="32" t="n"/>
-      <c r="N24" s="33">
+      <c r="B24" s="36" t="n"/>
+      <c r="C24" s="36" t="n"/>
+      <c r="D24" s="36" t="n"/>
+      <c r="E24" s="36" t="n"/>
+      <c r="F24" s="36" t="n"/>
+      <c r="G24" s="36" t="n"/>
+      <c r="H24" s="36" t="n"/>
+      <c r="I24" s="36" t="n"/>
+      <c r="J24" s="36" t="n"/>
+      <c r="K24" s="36" t="n"/>
+      <c r="L24" s="36" t="n"/>
+      <c r="M24" s="36" t="n"/>
+      <c r="N24" s="37">
         <f>SUM(B24:M24)</f>
         <v/>
       </c>
-      <c r="O24" s="33">
+      <c r="O24" s="37">
         <f>SUM(B25:M25)</f>
         <v/>
       </c>
-      <c r="P24" s="33">
+      <c r="P24" s="37">
         <f>O24-N24</f>
         <v/>
       </c>
-      <c r="Q24" s="34">
+      <c r="Q24" s="38">
         <f>IF(N24=0,"",O24/N24)</f>
         <v/>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="35" t="inlineStr">
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="39" t="inlineStr">
         <is>
           <t>IMPUESTOS Y DERECHOS - REAL</t>
         </is>
       </c>
-      <c r="B25" s="32" t="n"/>
-      <c r="C25" s="32" t="n"/>
-      <c r="D25" s="32" t="n"/>
-      <c r="E25" s="32" t="n"/>
-      <c r="F25" s="32" t="n"/>
-      <c r="G25" s="32" t="n"/>
-      <c r="H25" s="32" t="n"/>
-      <c r="I25" s="32" t="n"/>
-      <c r="J25" s="32" t="n"/>
-      <c r="K25" s="32" t="n"/>
-      <c r="L25" s="32" t="n"/>
-      <c r="M25" s="32" t="n"/>
+      <c r="B25" s="36" t="n"/>
+      <c r="C25" s="36" t="n"/>
+      <c r="D25" s="36" t="n"/>
+      <c r="E25" s="36" t="n"/>
+      <c r="F25" s="36" t="n"/>
+      <c r="G25" s="36" t="n"/>
+      <c r="H25" s="36" t="n"/>
+      <c r="I25" s="36" t="n"/>
+      <c r="J25" s="36" t="n"/>
+      <c r="K25" s="36" t="n"/>
+      <c r="L25" s="36" t="n"/>
+      <c r="M25" s="36" t="n"/>
       <c r="N25" s="4" t="n"/>
       <c r="O25" s="4" t="n"/>
       <c r="P25" s="4" t="n"/>
       <c r="Q25" s="4" t="n"/>
     </row>
-    <row r="26">
-      <c r="A26" s="31" t="inlineStr">
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="35" t="inlineStr">
         <is>
           <t>OTROS GASTOS - PRESUP.</t>
         </is>
       </c>
-      <c r="B26" s="32" t="n"/>
-      <c r="C26" s="32" t="n"/>
-      <c r="D26" s="32" t="n"/>
-      <c r="E26" s="32" t="n"/>
-      <c r="F26" s="32" t="n"/>
-      <c r="G26" s="32" t="n"/>
-      <c r="H26" s="32" t="n"/>
-      <c r="I26" s="32" t="n"/>
-      <c r="J26" s="32" t="n"/>
-      <c r="K26" s="32" t="n"/>
-      <c r="L26" s="32" t="n"/>
-      <c r="M26" s="32" t="n"/>
-      <c r="N26" s="33">
+      <c r="B26" s="36" t="n"/>
+      <c r="C26" s="36" t="n"/>
+      <c r="D26" s="36" t="n"/>
+      <c r="E26" s="36" t="n"/>
+      <c r="F26" s="36" t="n"/>
+      <c r="G26" s="36" t="n"/>
+      <c r="H26" s="36" t="n"/>
+      <c r="I26" s="36" t="n"/>
+      <c r="J26" s="36" t="n"/>
+      <c r="K26" s="36" t="n"/>
+      <c r="L26" s="36" t="n"/>
+      <c r="M26" s="36" t="n"/>
+      <c r="N26" s="37">
         <f>SUM(B26:M26)</f>
         <v/>
       </c>
-      <c r="O26" s="33">
+      <c r="O26" s="37">
         <f>SUM(B27:M27)</f>
         <v/>
       </c>
-      <c r="P26" s="33">
+      <c r="P26" s="37">
         <f>O26-N26</f>
         <v/>
       </c>
-      <c r="Q26" s="34">
+      <c r="Q26" s="38">
         <f>IF(N26=0,"",O26/N26)</f>
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="35" t="inlineStr">
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="39" t="inlineStr">
         <is>
           <t>OTROS GASTOS - REAL</t>
         </is>
       </c>
-      <c r="B27" s="32" t="n"/>
-      <c r="C27" s="32" t="n"/>
-      <c r="D27" s="32" t="n"/>
-      <c r="E27" s="32" t="n"/>
-      <c r="F27" s="32" t="n"/>
-      <c r="G27" s="32" t="n"/>
-      <c r="H27" s="32" t="n"/>
-      <c r="I27" s="32" t="n"/>
-      <c r="J27" s="32" t="n"/>
-      <c r="K27" s="32" t="n"/>
-      <c r="L27" s="32" t="n"/>
-      <c r="M27" s="32" t="n"/>
+      <c r="B27" s="36" t="n"/>
+      <c r="C27" s="36" t="n"/>
+      <c r="D27" s="36" t="n"/>
+      <c r="E27" s="36" t="n"/>
+      <c r="F27" s="36" t="n"/>
+      <c r="G27" s="36" t="n"/>
+      <c r="H27" s="36" t="n"/>
+      <c r="I27" s="36" t="n"/>
+      <c r="J27" s="36" t="n"/>
+      <c r="K27" s="36" t="n"/>
+      <c r="L27" s="36" t="n"/>
+      <c r="M27" s="36" t="n"/>
       <c r="N27" s="4" t="n"/>
       <c r="O27" s="4" t="n"/>
       <c r="P27" s="4" t="n"/>
@@ -2349,6 +2562,728 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="240">
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="C8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="D8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="E8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="F8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="G8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="H8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="I8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="J8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="K8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="L8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="M8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="C9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="D9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="E9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="F9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="G9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="H9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="I9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="J9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="K9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="L9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="M9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B10" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="C10" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="D10" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="E10" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="F10" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="G10" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="H10" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="I10" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="J10" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="K10" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="L10" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="M10" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="C11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="D11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="E11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="F11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="G11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="H11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="I11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="J11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="K11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="L11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="M11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="C12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="D12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="E12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="F12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="G12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="H12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="I12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="J12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="K12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="L12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="M12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="C13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="D13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="E13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="F13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="G13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="H13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="I13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="J13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="K13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="L13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="M13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B14" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="C14" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="D14" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="E14" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="F14" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="G14" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="H14" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="I14" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="J14" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="K14" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="L14" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="M14" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B15" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="C15" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="D15" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="E15" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="F15" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="G15" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="H15" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="I15" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="J15" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="K15" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="L15" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="M15" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B16" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="C16" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="D16" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="E16" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="F16" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="G16" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="H16" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="I16" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="J16" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="K16" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="L16" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="M16" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B17" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="C17" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="D17" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="E17" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="F17" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="G17" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="H17" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="I17" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="J17" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="K17" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="L17" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="M17" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="C18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="D18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="E18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="F18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="G18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="H18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="I18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="J18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="K18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="L18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="M18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B19" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="C19" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="D19" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="E19" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="F19" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="G19" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="H19" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="I19" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="J19" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="K19" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="L19" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="M19" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B20" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="C20" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="D20" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="E20" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="F20" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="G20" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="H20" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="I20" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="J20" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="K20" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="L20" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="M20" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B21" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="C21" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="D21" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="E21" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="F21" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="G21" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="H21" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="I21" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="J21" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="K21" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="L21" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="M21" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B22" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="C22" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="D22" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="E22" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="F22" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="G22" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="H22" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="I22" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="J22" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="K22" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="L22" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="M22" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B23" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="C23" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="D23" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="E23" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="F23" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="G23" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="H23" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="I23" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="J23" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="K23" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="L23" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="M23" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B24" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="C24" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="D24" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="E24" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="F24" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="G24" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="H24" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="I24" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="J24" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="K24" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="L24" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="M24" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B25" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="C25" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="D25" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="E25" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="F25" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="G25" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="H25" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="I25" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="J25" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="K25" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="L25" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="M25" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B26" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="C26" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="D26" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="E26" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="F26" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="G26" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="H26" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="I26" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="J26" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="K26" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="L26" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="M26" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B27" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="C27" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="D27" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="E27" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="F27" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="G27" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="H27" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="I27" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="J27" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="K27" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="L27" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="M27" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="1"/>
@@ -2386,7 +3321,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="44" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>RESUMEN DEL PRESUPUESTO</t>
         </is>
@@ -2397,30 +3332,30 @@
       <c r="E1" s="1" t="n"/>
       <c r="F1" s="1" t="n"/>
       <c r="G1" s="1" t="n"/>
-      <c r="H1" s="23" t="inlineStr">
+      <c r="H1" s="27" t="inlineStr">
         <is>
           <t>INSERTE SU LOGO
 (clic derecho &gt; Insertar imagen)</t>
         </is>
       </c>
-      <c r="I1" s="36" t="n"/>
-      <c r="J1" s="24" t="n"/>
+      <c r="I1" s="40" t="n"/>
+      <c r="J1" s="28" t="n"/>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="29" t="inlineStr">
         <is>
           <t>Presupuestado vs. real por concepto</t>
         </is>
       </c>
-      <c r="B2" s="26" t="n"/>
-      <c r="C2" s="26" t="n"/>
-      <c r="D2" s="26" t="n"/>
-      <c r="E2" s="26" t="n"/>
-      <c r="F2" s="26" t="n"/>
-      <c r="G2" s="26" t="n"/>
-      <c r="H2" s="27" t="n"/>
-      <c r="I2" s="37" t="n"/>
-      <c r="J2" s="28" t="n"/>
+      <c r="B2" s="30" t="n"/>
+      <c r="C2" s="30" t="n"/>
+      <c r="D2" s="30" t="n"/>
+      <c r="E2" s="30" t="n"/>
+      <c r="F2" s="30" t="n"/>
+      <c r="G2" s="30" t="n"/>
+      <c r="H2" s="31" t="n"/>
+      <c r="I2" s="41" t="n"/>
+      <c r="J2" s="32" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n"/>
@@ -2434,56 +3369,56 @@
       <c r="I3" s="4" t="n"/>
       <c r="J3" s="4" t="n"/>
     </row>
-    <row r="4" ht="20" customHeight="1">
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="4" t="n"/>
-      <c r="B4" s="38" t="inlineStr">
+      <c r="B4" s="42" t="inlineStr">
         <is>
           <t>VENTAS PRESUPUESTADAS</t>
         </is>
       </c>
-      <c r="C4" s="39" t="n"/>
-      <c r="D4" s="38" t="inlineStr">
+      <c r="C4" s="43" t="n"/>
+      <c r="D4" s="42" t="inlineStr">
         <is>
           <t>VENTAS REALES</t>
         </is>
       </c>
-      <c r="E4" s="39" t="n"/>
-      <c r="F4" s="38" t="inlineStr">
+      <c r="E4" s="43" t="n"/>
+      <c r="F4" s="42" t="inlineStr">
         <is>
           <t>GASTO PRESUPUESTADO</t>
         </is>
       </c>
-      <c r="G4" s="39" t="n"/>
-      <c r="H4" s="38" t="inlineStr">
+      <c r="G4" s="43" t="n"/>
+      <c r="H4" s="42" t="inlineStr">
         <is>
           <t>GASTO REAL</t>
         </is>
       </c>
-      <c r="I4" s="39" t="n"/>
+      <c r="I4" s="43" t="n"/>
       <c r="J4" s="4" t="n"/>
     </row>
-    <row r="5" ht="36" customHeight="1">
+    <row r="5" ht="46" customHeight="1">
       <c r="A5" s="4" t="n"/>
-      <c r="B5" s="40">
+      <c r="B5" s="44">
         <f>C9</f>
         <v/>
       </c>
-      <c r="C5" s="41" t="n"/>
-      <c r="D5" s="40">
+      <c r="C5" s="45" t="n"/>
+      <c r="D5" s="44">
         <f>D9</f>
         <v/>
       </c>
-      <c r="E5" s="41" t="n"/>
-      <c r="F5" s="40">
+      <c r="E5" s="45" t="n"/>
+      <c r="F5" s="44">
         <f>SUM(C10:C18)</f>
         <v/>
       </c>
-      <c r="G5" s="41" t="n"/>
-      <c r="H5" s="40">
+      <c r="G5" s="45" t="n"/>
+      <c r="H5" s="44">
         <f>SUM(D10:D18)</f>
         <v/>
       </c>
-      <c r="I5" s="41" t="n"/>
+      <c r="I5" s="45" t="n"/>
       <c r="J5" s="4" t="n"/>
     </row>
     <row r="6">
@@ -2498,9 +3433,12 @@
       <c r="I6" s="4" t="n"/>
       <c r="J6" s="4" t="n"/>
     </row>
-    <row r="7">
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="4" t="n"/>
-      <c r="B7" s="4" t="n"/>
+      <c r="B7" s="46">
+        <f>IF(SUM(C9:C18)=0,"Captura el presupuesto y el real en la hoja FORMATO para ver el análisis automático.","Mayor sobre-ejercicio: "&amp;IF(MAX(E9:E18)&lt;=0,"ninguno",INDEX(B9:B18,MATCH(MAX(E9:E18),E9:E18,0)))&amp;". Ejecución global de ventas: "&amp;TEXT(IFERROR(D9/C9,0),"0%")&amp;".")</f>
+        <v/>
+      </c>
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="n"/>
@@ -2512,27 +3450,27 @@
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="4" t="n"/>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>CONCEPTO</t>
         </is>
       </c>
-      <c r="C8" s="30" t="inlineStr">
+      <c r="C8" s="34" t="inlineStr">
         <is>
           <t>PRESUPUESTO</t>
         </is>
       </c>
-      <c r="D8" s="30" t="inlineStr">
+      <c r="D8" s="34" t="inlineStr">
         <is>
           <t>REAL</t>
         </is>
       </c>
-      <c r="E8" s="30" t="inlineStr">
+      <c r="E8" s="34" t="inlineStr">
         <is>
           <t>VARIACIÓN</t>
         </is>
       </c>
-      <c r="F8" s="30" t="inlineStr">
+      <c r="F8" s="34" t="inlineStr">
         <is>
           <t>% EJEC.</t>
         </is>
@@ -2544,24 +3482,24 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="n"/>
-      <c r="B9" s="35" t="inlineStr">
+      <c r="B9" s="39" t="inlineStr">
         <is>
           <t>VENTAS</t>
         </is>
       </c>
-      <c r="C9" s="33">
+      <c r="C9" s="37">
         <f>FORMATO!N8</f>
         <v/>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="37">
         <f>FORMATO!O8</f>
         <v/>
       </c>
-      <c r="E9" s="33">
+      <c r="E9" s="37">
         <f>D9-C9</f>
         <v/>
       </c>
-      <c r="F9" s="34">
+      <c r="F9" s="38">
         <f>IF(C9=0,"",D9/C9)</f>
         <v/>
       </c>
@@ -2572,24 +3510,24 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n"/>
-      <c r="B10" s="35" t="inlineStr">
+      <c r="B10" s="39" t="inlineStr">
         <is>
           <t>COSTO DE VENTAS</t>
         </is>
       </c>
-      <c r="C10" s="33">
+      <c r="C10" s="37">
         <f>FORMATO!N10</f>
         <v/>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="37">
         <f>FORMATO!O10</f>
         <v/>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="37">
         <f>D10-C10</f>
         <v/>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="38">
         <f>IF(C10=0,"",D10/C10)</f>
         <v/>
       </c>
@@ -2600,24 +3538,24 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="n"/>
-      <c r="B11" s="35" t="inlineStr">
+      <c r="B11" s="39" t="inlineStr">
         <is>
           <t>SUELDOS Y SALARIOS</t>
         </is>
       </c>
-      <c r="C11" s="33">
+      <c r="C11" s="37">
         <f>FORMATO!N12</f>
         <v/>
       </c>
-      <c r="D11" s="33">
+      <c r="D11" s="37">
         <f>FORMATO!O12</f>
         <v/>
       </c>
-      <c r="E11" s="33">
+      <c r="E11" s="37">
         <f>D11-C11</f>
         <v/>
       </c>
-      <c r="F11" s="34">
+      <c r="F11" s="38">
         <f>IF(C11=0,"",D11/C11)</f>
         <v/>
       </c>
@@ -2628,24 +3566,24 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="n"/>
-      <c r="B12" s="35" t="inlineStr">
+      <c r="B12" s="39" t="inlineStr">
         <is>
           <t>RENTA</t>
         </is>
       </c>
-      <c r="C12" s="33">
+      <c r="C12" s="37">
         <f>FORMATO!N14</f>
         <v/>
       </c>
-      <c r="D12" s="33">
+      <c r="D12" s="37">
         <f>FORMATO!O14</f>
         <v/>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="37">
         <f>D12-C12</f>
         <v/>
       </c>
-      <c r="F12" s="34">
+      <c r="F12" s="38">
         <f>IF(C12=0,"",D12/C12)</f>
         <v/>
       </c>
@@ -2656,24 +3594,24 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="n"/>
-      <c r="B13" s="35" t="inlineStr">
+      <c r="B13" s="39" t="inlineStr">
         <is>
           <t>SERVICIOS</t>
         </is>
       </c>
-      <c r="C13" s="33">
+      <c r="C13" s="37">
         <f>FORMATO!N16</f>
         <v/>
       </c>
-      <c r="D13" s="33">
+      <c r="D13" s="37">
         <f>FORMATO!O16</f>
         <v/>
       </c>
-      <c r="E13" s="33">
+      <c r="E13" s="37">
         <f>D13-C13</f>
         <v/>
       </c>
-      <c r="F13" s="34">
+      <c r="F13" s="38">
         <f>IF(C13=0,"",D13/C13)</f>
         <v/>
       </c>
@@ -2684,24 +3622,24 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="n"/>
-      <c r="B14" s="35" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>PUBLICIDAD Y MERCADOTECNIA</t>
         </is>
       </c>
-      <c r="C14" s="33">
+      <c r="C14" s="37">
         <f>FORMATO!N18</f>
         <v/>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="37">
         <f>FORMATO!O18</f>
         <v/>
       </c>
-      <c r="E14" s="33">
+      <c r="E14" s="37">
         <f>D14-C14</f>
         <v/>
       </c>
-      <c r="F14" s="34">
+      <c r="F14" s="38">
         <f>IF(C14=0,"",D14/C14)</f>
         <v/>
       </c>
@@ -2712,24 +3650,24 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="n"/>
-      <c r="B15" s="35" t="inlineStr">
+      <c r="B15" s="39" t="inlineStr">
         <is>
           <t>MANTENIMIENTO</t>
         </is>
       </c>
-      <c r="C15" s="33">
+      <c r="C15" s="37">
         <f>FORMATO!N20</f>
         <v/>
       </c>
-      <c r="D15" s="33">
+      <c r="D15" s="37">
         <f>FORMATO!O20</f>
         <v/>
       </c>
-      <c r="E15" s="33">
+      <c r="E15" s="37">
         <f>D15-C15</f>
         <v/>
       </c>
-      <c r="F15" s="34">
+      <c r="F15" s="38">
         <f>IF(C15=0,"",D15/C15)</f>
         <v/>
       </c>
@@ -2740,24 +3678,24 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="n"/>
-      <c r="B16" s="35" t="inlineStr">
+      <c r="B16" s="39" t="inlineStr">
         <is>
           <t>PAPELERÍA Y OFICINA</t>
         </is>
       </c>
-      <c r="C16" s="33">
+      <c r="C16" s="37">
         <f>FORMATO!N22</f>
         <v/>
       </c>
-      <c r="D16" s="33">
+      <c r="D16" s="37">
         <f>FORMATO!O22</f>
         <v/>
       </c>
-      <c r="E16" s="33">
+      <c r="E16" s="37">
         <f>D16-C16</f>
         <v/>
       </c>
-      <c r="F16" s="34">
+      <c r="F16" s="38">
         <f>IF(C16=0,"",D16/C16)</f>
         <v/>
       </c>
@@ -2768,24 +3706,24 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="n"/>
-      <c r="B17" s="35" t="inlineStr">
+      <c r="B17" s="39" t="inlineStr">
         <is>
           <t>IMPUESTOS Y DERECHOS</t>
         </is>
       </c>
-      <c r="C17" s="33">
+      <c r="C17" s="37">
         <f>FORMATO!N24</f>
         <v/>
       </c>
-      <c r="D17" s="33">
+      <c r="D17" s="37">
         <f>FORMATO!O24</f>
         <v/>
       </c>
-      <c r="E17" s="33">
+      <c r="E17" s="37">
         <f>D17-C17</f>
         <v/>
       </c>
-      <c r="F17" s="34">
+      <c r="F17" s="38">
         <f>IF(C17=0,"",D17/C17)</f>
         <v/>
       </c>
@@ -2796,24 +3734,24 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="n"/>
-      <c r="B18" s="35" t="inlineStr">
+      <c r="B18" s="39" t="inlineStr">
         <is>
           <t>OTROS GASTOS</t>
         </is>
       </c>
-      <c r="C18" s="33">
+      <c r="C18" s="37">
         <f>FORMATO!N26</f>
         <v/>
       </c>
-      <c r="D18" s="33">
+      <c r="D18" s="37">
         <f>FORMATO!O26</f>
         <v/>
       </c>
-      <c r="E18" s="33">
+      <c r="E18" s="37">
         <f>D18-C18</f>
         <v/>
       </c>
-      <c r="F18" s="34">
+      <c r="F18" s="38">
         <f>IF(C18=0,"",D18/C18)</f>
         <v/>
       </c>
@@ -2824,10 +3762,11 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="H1:J2"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B7:I7"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="D5:E5"/>
@@ -2871,7 +3810,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="n"/>
-      <c r="B1" s="42" t="inlineStr">
+      <c r="B1" s="47" t="inlineStr">
         <is>
           <t>AYUDA Y PREGUNTAS FRECUENTES</t>
         </is>
@@ -2882,7 +3821,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n"/>
-      <c r="B2" s="43" t="inlineStr">
+      <c r="B2" s="48" t="inlineStr">
         <is>
           <t>PRESUPUESTO ANUAL</t>
         </is>
@@ -2919,12 +3858,12 @@
     <row r="6" ht="38" customHeight="1">
       <c r="A6" s="4" t="n"/>
       <c r="B6" s="4" t="n"/>
-      <c r="C6" s="44" t="inlineStr">
+      <c r="C6" s="49" t="inlineStr">
         <is>
           <t>¿Cómo leo la variación?</t>
         </is>
       </c>
-      <c r="D6" s="45" t="inlineStr">
+      <c r="D6" s="50" t="inlineStr">
         <is>
           <t>Real - Presupuesto. En gastos, positiva significa que te pasaste; en ventas, positiva es favorable.</t>
         </is>
@@ -2934,12 +3873,12 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="4" t="n"/>
       <c r="B7" s="4" t="n"/>
-      <c r="C7" s="44" t="inlineStr">
+      <c r="C7" s="49" t="inlineStr">
         <is>
           <t>¿Puedo agregar conceptos?</t>
         </is>
       </c>
-      <c r="D7" s="45" t="inlineStr">
+      <c r="D7" s="50" t="inlineStr">
         <is>
           <t>Cambia el nombre de uno de los 10 conceptos disponibles.</t>
         </is>
@@ -2949,12 +3888,12 @@
     <row r="8" ht="53" customHeight="1">
       <c r="A8" s="4" t="n"/>
       <c r="B8" s="4" t="n"/>
-      <c r="C8" s="44" t="inlineStr">
+      <c r="C8" s="49" t="inlineStr">
         <is>
           <t>¿Por qué no puedo escribir en algunas celdas?</t>
         </is>
       </c>
-      <c r="D8" s="45" t="inlineStr">
+      <c r="D8" s="50" t="inlineStr">
         <is>
           <t>La hoja está protegida para que no se borren fórmulas por accidente. Solo se editan las celdas de captura (color crema). Si necesitas modificar algo más: pestaña Revisar &gt; Desproteger hoja (no tiene contraseña).</t>
         </is>
@@ -2964,12 +3903,12 @@
     <row r="9" ht="38" customHeight="1">
       <c r="A9" s="4" t="n"/>
       <c r="B9" s="4" t="n"/>
-      <c r="C9" s="44" t="inlineStr">
+      <c r="C9" s="49" t="inlineStr">
         <is>
           <t>¿Cómo agrego mi logotipo?</t>
         </is>
       </c>
-      <c r="D9" s="45" t="inlineStr">
+      <c r="D9" s="50" t="inlineStr">
         <is>
           <t>Haz clic en el recuadro punteado de la esquina superior derecha del formato y usa Insertar &gt; Imágenes. Ajusta el tamaño sin salirte del recuadro.</t>
         </is>
@@ -2979,12 +3918,12 @@
     <row r="10" ht="38" customHeight="1">
       <c r="A10" s="4" t="n"/>
       <c r="B10" s="4" t="n"/>
-      <c r="C10" s="44" t="inlineStr">
+      <c r="C10" s="49" t="inlineStr">
         <is>
           <t>¿Cómo lo imprimo o lo convierto a PDF?</t>
         </is>
       </c>
-      <c r="D10" s="45" t="inlineStr">
+      <c r="D10" s="50" t="inlineStr">
         <is>
           <t>Archivo &gt; Imprimir (ya está ajustado a una hoja de ancho). Para PDF elige 'Microsoft Print to PDF' o Archivo &gt; Exportar &gt; PDF.</t>
         </is>
@@ -2994,12 +3933,12 @@
     <row r="11" ht="38" customHeight="1">
       <c r="A11" s="4" t="n"/>
       <c r="B11" s="4" t="n"/>
-      <c r="C11" s="44" t="inlineStr">
+      <c r="C11" s="49" t="inlineStr">
         <is>
           <t>¿Con qué versiones de Excel funciona?</t>
         </is>
       </c>
-      <c r="D11" s="45" t="inlineStr">
+      <c r="D11" s="50" t="inlineStr">
         <is>
           <t>Excel 2016, 2019, 2021 y Microsoft 365 (Windows y Mac). Funciona en LibreOffice y Google Sheets, aunque algunas gráficas y formatos pueden verse distintos.</t>
         </is>
@@ -3009,14 +3948,14 @@
     <row r="12" ht="38" customHeight="1">
       <c r="A12" s="4" t="n"/>
       <c r="B12" s="4" t="n"/>
-      <c r="C12" s="44" t="inlineStr">
-        <is>
-          <t>¿Por qué la letra se ve diferente?</t>
-        </is>
-      </c>
-      <c r="D12" s="45" t="inlineStr">
-        <is>
-          <t>El diseño usa la fuente Abadi, incluida en Microsoft 365. Si tu versión no la tiene, Excel la sustituye por otra; no afecta el funcionamiento.</t>
+      <c r="C12" s="49" t="inlineStr">
+        <is>
+          <t>¿Puedo cambiar la letra?</t>
+        </is>
+      </c>
+      <c r="D12" s="50" t="inlineStr">
+        <is>
+          <t>El diseño usa la fuente Arial, disponible en Windows, Mac y Google Sheets. Si necesitas otra, selecciona todo (Ctrl+E) y cambia la fuente; no afecta el funcionamiento.</t>
         </is>
       </c>
       <c r="E12" s="4" t="n"/>
@@ -3024,12 +3963,12 @@
     <row r="13" ht="38" customHeight="1">
       <c r="A13" s="4" t="n"/>
       <c r="B13" s="4" t="n"/>
-      <c r="C13" s="44" t="inlineStr">
+      <c r="C13" s="49" t="inlineStr">
         <is>
           <t>¿Puedo usarlo en varias empresas o por varios años?</t>
         </is>
       </c>
-      <c r="D13" s="45" t="inlineStr">
+      <c r="D13" s="50" t="inlineStr">
         <is>
           <t>Sí. Guarda una copia del archivo por empresa o por periodo (Archivo &gt; Guardar como) y deja el original en blanco como plantilla maestra.</t>
         </is>
@@ -3057,12 +3996,12 @@
     <row r="16" ht="21" customHeight="1">
       <c r="A16" s="4" t="n"/>
       <c r="B16" s="4" t="n"/>
-      <c r="C16" s="46" t="inlineStr">
+      <c r="C16" s="51" t="inlineStr">
         <is>
           <t>PRESUPUESTO</t>
         </is>
       </c>
-      <c r="D16" s="47" t="inlineStr">
+      <c r="D16" s="52" t="inlineStr">
         <is>
           <t>Plan de ingresos y gastos.</t>
         </is>
@@ -3072,12 +4011,12 @@
     <row r="17" ht="21" customHeight="1">
       <c r="A17" s="4" t="n"/>
       <c r="B17" s="4" t="n"/>
-      <c r="C17" s="46" t="inlineStr">
+      <c r="C17" s="51" t="inlineStr">
         <is>
           <t>VARIACIÓN</t>
         </is>
       </c>
-      <c r="D17" s="47" t="inlineStr">
+      <c r="D17" s="52" t="inlineStr">
         <is>
           <t>Diferencia entre lo real y lo presupuestado.</t>
         </is>
@@ -3087,12 +4026,12 @@
     <row r="18" ht="21" customHeight="1">
       <c r="A18" s="4" t="n"/>
       <c r="B18" s="4" t="n"/>
-      <c r="C18" s="46" t="inlineStr">
+      <c r="C18" s="51" t="inlineStr">
         <is>
           <t>% DE EJECUCIÓN</t>
         </is>
       </c>
-      <c r="D18" s="47" t="inlineStr">
+      <c r="D18" s="52" t="inlineStr">
         <is>
           <t>Real / presupuesto.</t>
         </is>
@@ -3119,12 +4058,12 @@
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="4" t="n"/>
-      <c r="B21" s="48" t="inlineStr">
+      <c r="B21" s="53" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="C21" s="49" t="inlineStr">
+      <c r="C21" s="54" t="inlineStr">
         <is>
           <t>Presupuesto aprobado</t>
         </is>
@@ -3134,12 +4073,12 @@
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="4" t="n"/>
-      <c r="B22" s="48" t="inlineStr">
+      <c r="B22" s="53" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="C22" s="49" t="inlineStr">
+      <c r="C22" s="54" t="inlineStr">
         <is>
           <t>Real capturado al cierre de cada mes</t>
         </is>
@@ -3149,12 +4088,12 @@
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="4" t="n"/>
-      <c r="B23" s="48" t="inlineStr">
+      <c r="B23" s="53" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="C23" s="49" t="inlineStr">
+      <c r="C23" s="54" t="inlineStr">
         <is>
           <t>Variaciones &gt;10% explicadas</t>
         </is>
@@ -3164,12 +4103,12 @@
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="4" t="n"/>
-      <c r="B24" s="48" t="inlineStr">
+      <c r="B24" s="53" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="C24" s="49" t="inlineStr">
+      <c r="C24" s="54" t="inlineStr">
         <is>
           <t>Reforecast trimestral</t>
         </is>
